--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-23T09:57:04.000Z</t>
+          <t>2026-08-23T10:57:04.000Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-23T02:57:57.000-07:00</t>
+          <t>2026-08-23T03:57:57.000-07:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-23T09:57:57.000Z</t>
+          <t>2026-08-23T10:57:57.000Z</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>55</v>
+        <v>218</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:55.000Z</t>
+          <t>2026-08-23T10:53:55.000Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-23T02:53:53.000-07:00</t>
+          <t>2026-08-23T03:53:53.000-07:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:53.000Z</t>
+          <t>2026-08-23T10:53:53.000Z</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -688,22 +688,22 @@
         <v>70</v>
       </c>
       <c r="O3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:35.000Z</t>
+          <t>2026-08-23T10:53:35.000Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-23T02:53:53.000-07:00</t>
+          <t>2026-08-23T03:53:53.000-07:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:53.000Z</t>
+          <t>2026-08-23T10:53:53.000Z</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:34.000Z</t>
+          <t>2026-08-23T10:53:34.000Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-23T02:53:53.000-07:00</t>
+          <t>2026-08-23T03:53:53.000-07:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:53.000Z</t>
+          <t>2026-08-23T10:53:53.000Z</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O5" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:15.000Z</t>
+          <t>2026-08-23T10:53:15.000Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-23T02:53:53.000-07:00</t>
+          <t>2026-08-23T03:53:53.000-07:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:53.000Z</t>
+          <t>2026-08-23T10:53:53.000Z</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
         <v>43</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:05.000Z</t>
+          <t>2026-08-23T10:53:05.000Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-23T02:53:53.000-07:00</t>
+          <t>2026-08-23T03:53:53.000-07:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:53.000Z</t>
+          <t>2026-08-23T10:53:53.000Z</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,25 +1057,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:04.000Z</t>
+          <t>2026-08-23T10:53:04.000Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-23T02:53:53.000-07:00</t>
+          <t>2026-08-23T03:53:53.000-07:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-08-23T09:53:53.000Z</t>
+          <t>2026-08-23T10:53:53.000Z</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:55.000Z</t>
+          <t>2026-08-23T10:52:55.000Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-23T02:52:52.000-07:00</t>
+          <t>2026-08-23T03:52:52.000-07:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:52.000Z</t>
+          <t>2026-08-23T10:52:52.000Z</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>324</v>
+        <v>232</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:45.000Z</t>
+          <t>2026-08-23T10:52:45.000Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-23T02:52:52.000-07:00</t>
+          <t>2026-08-23T03:52:52.000-07:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:52.000Z</t>
+          <t>2026-08-23T10:52:52.000Z</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:35.000Z</t>
+          <t>2026-08-23T10:52:35.000Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-23T02:52:52.000-07:00</t>
+          <t>2026-08-23T03:52:52.000-07:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:52.000Z</t>
+          <t>2026-08-23T10:52:52.000Z</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R11" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T11" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:35.000Z</t>
+          <t>2026-08-23T10:52:35.000Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-23T02:52:52.000-07:00</t>
+          <t>2026-08-23T03:52:52.000-07:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:52.000Z</t>
+          <t>2026-08-23T10:52:52.000Z</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,25 +1522,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>332</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:34.000Z</t>
+          <t>2026-08-23T10:52:34.000Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-23T02:52:52.000-07:00</t>
+          <t>2026-08-23T03:52:52.000-07:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-08-23T09:52:52.000Z</t>
+          <t>2026-08-23T10:52:52.000Z</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:25.000Z</t>
+          <t>2026-08-23T10:50:25.000Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-23T02:50:50.000-07:00</t>
+          <t>2026-08-23T03:50:50.000-07:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:50.000Z</t>
+          <t>2026-08-23T10:50:50.000Z</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>24</v>
+        <v>191</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:24.000Z</t>
+          <t>2026-08-23T10:50:24.000Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-23T02:50:50.000-07:00</t>
+          <t>2026-08-23T03:50:50.000-07:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:50.000Z</t>
+          <t>2026-08-23T10:50:50.000Z</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O15" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>336</v>
+        <v>54</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:15.000Z</t>
+          <t>2026-08-23T10:50:15.000Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-08-23T02:50:50.000-07:00</t>
+          <t>2026-08-23T03:50:50.000-07:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:50.000Z</t>
+          <t>2026-08-23T10:50:50.000Z</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,25 +1894,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O16" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:05.000Z</t>
+          <t>2026-08-23T10:50:05.000Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-08-23T02:50:50.000-07:00</t>
+          <t>2026-08-23T03:50:50.000-07:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-08-23T09:50:50.000Z</t>
+          <t>2026-08-23T10:50:50.000Z</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O17" t="n">
         <v>28</v>
@@ -1996,16 +1996,16 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-23T09:49:55.000Z</t>
+          <t>2026-08-23T10:49:55.000Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-08-23T02:49:49.000-07:00</t>
+          <t>2026-08-23T03:49:49.000-07:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-08-23T09:49:49.000Z</t>
+          <t>2026-08-23T10:49:49.000Z</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="O18" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>24</v>
+        <v>236</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-23T09:49:44.000Z</t>
+          <t>2026-08-23T10:49:44.000Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-23T02:49:49.000-07:00</t>
+          <t>2026-08-23T03:49:49.000-07:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-08-23T09:49:49.000Z</t>
+          <t>2026-08-23T10:49:49.000Z</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2176,7 +2176,7 @@
         <v>59</v>
       </c>
       <c r="O19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2185,13 +2185,13 @@
         <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-23T09:49:34.000Z</t>
+          <t>2026-08-23T10:49:34.000Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-08-23T02:49:49.000-07:00</t>
+          <t>2026-08-23T03:49:49.000-07:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-08-23T09:49:49.000Z</t>
+          <t>2026-08-23T10:49:49.000Z</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,25 +2266,25 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-23T09:48:54.000Z</t>
+          <t>2026-08-23T10:48:54.000Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-08-23T02:48:48.000-07:00</t>
+          <t>2026-08-23T03:48:48.000-07:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08-23T09:48:48.000Z</t>
+          <t>2026-08-23T10:48:48.000Z</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,25 +2359,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-23T09:48:54.000Z</t>
+          <t>2026-08-23T10:48:54.000Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-08-23T02:48:48.000-07:00</t>
+          <t>2026-08-23T03:48:48.000-07:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08-23T09:48:48.000Z</t>
+          <t>2026-08-23T10:48:48.000Z</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,25 +2452,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O22" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-23T09:48:15.000Z</t>
+          <t>2026-08-23T10:48:15.000Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-23T02:48:48.000-07:00</t>
+          <t>2026-08-23T03:48:48.000-07:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-23T09:48:48.000Z</t>
+          <t>2026-08-23T10:48:48.000Z</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2548,22 +2548,22 @@
         <v>79</v>
       </c>
       <c r="O23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-23T09:47:34.000Z</t>
+          <t>2026-08-23T10:47:34.000Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-08-23T02:47:47.000-07:00</t>
+          <t>2026-08-23T03:47:47.000-07:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-23T09:47:47.000Z</t>
+          <t>2026-08-23T10:47:47.000Z</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2638,25 +2638,25 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O24" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-23T09:42:54.000Z</t>
+          <t>2026-08-23T10:42:54.000Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-08-23T02:42:42.000-07:00</t>
+          <t>2026-08-23T03:42:42.000-07:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-23T09:42:42.000Z</t>
+          <t>2026-08-23T10:42:42.000Z</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O25" t="n">
         <v>81</v>
@@ -2743,13 +2743,13 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-23T09:42:44.000Z</t>
+          <t>2026-08-23T10:42:44.000Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-08-23T02:42:42.000-07:00</t>
+          <t>2026-08-23T03:42:42.000-07:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-23T09:42:42.000Z</t>
+          <t>2026-08-23T10:42:42.000Z</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,25 +2824,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O26" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>343</v>
+        <v>105</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:24.000Z</t>
+          <t>2026-08-23T10:41:24.000Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-08-23T02:41:41.000-07:00</t>
+          <t>2026-08-23T03:41:41.000-07:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:41.000Z</t>
+          <t>2026-08-23T10:41:41.000Z</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O27" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="S27" t="n">
         <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>34</v>
+        <v>353</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:24.000Z</t>
+          <t>2026-08-23T10:41:24.000Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-08-23T02:41:41.000-07:00</t>
+          <t>2026-08-23T03:41:41.000-07:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:41.000Z</t>
+          <t>2026-08-23T10:41:41.000Z</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O28" t="n">
         <v>48</v>
@@ -3019,16 +3019,16 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>358</v>
+        <v>253</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>28</v>
+        <v>331</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:14.000Z</t>
+          <t>2026-08-23T10:41:14.000Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-08-23T02:41:41.000-07:00</t>
+          <t>2026-08-23T03:41:41.000-07:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:41.000Z</t>
+          <t>2026-08-23T10:41:41.000Z</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3106,22 +3106,22 @@
         <v>58</v>
       </c>
       <c r="O29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:05.000Z</t>
+          <t>2026-08-23T10:41:05.000Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-08-23T02:41:41.000-07:00</t>
+          <t>2026-08-23T03:41:41.000-07:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-23T09:41:41.000Z</t>
+          <t>2026-08-23T10:41:41.000Z</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,25 +3196,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O30" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-23T09:40:54.000Z</t>
+          <t>2026-08-23T10:40:54.000Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-23T02:40:40.000-07:00</t>
+          <t>2026-08-23T03:40:40.000-07:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-23T09:40:40.000Z</t>
+          <t>2026-08-23T10:40:40.000Z</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O31" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
       </c>
       <c r="T31" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-23T09:40:45.000Z</t>
+          <t>2026-08-23T10:40:45.000Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-23T02:40:40.000-07:00</t>
+          <t>2026-08-23T03:40:40.000-07:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-23T09:40:40.000Z</t>
+          <t>2026-08-23T10:40:40.000Z</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3382,25 +3382,25 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T32" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:54.000Z</t>
+          <t>2026-08-23T10:39:54.000Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-23T02:39:39.000-07:00</t>
+          <t>2026-08-23T03:39:39.000-07:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:39.000Z</t>
+          <t>2026-08-23T10:39:39.000Z</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O33" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:45.000Z</t>
+          <t>2026-08-23T10:39:45.000Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-08-23T02:39:39.000-07:00</t>
+          <t>2026-08-23T03:39:39.000-07:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:39.000Z</t>
+          <t>2026-08-23T10:39:39.000Z</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,25 +3568,25 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O34" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R34" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T34" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:19.000Z</t>
+          <t>2026-08-23T10:39:19.000Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-08-23T02:39:39.000-07:00</t>
+          <t>2026-08-23T03:39:39.000-07:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:39.000Z</t>
+          <t>2026-08-23T10:39:39.000Z</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O35" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3673,13 +3673,13 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>158</v>
+        <v>231</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:09.000Z</t>
+          <t>2026-08-23T10:39:09.000Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-23T02:39:39.000-07:00</t>
+          <t>2026-08-23T03:39:39.000-07:00</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-23T09:39:39.000Z</t>
+          <t>2026-08-23T10:39:39.000Z</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3763,16 +3763,16 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:59.000Z</t>
+          <t>2026-08-23T10:38:59.000Z</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O37" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:49.000Z</t>
+          <t>2026-08-23T10:38:49.000Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3940,25 +3940,25 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O38" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:44.000Z</t>
+          <t>2026-08-23T10:38:44.000Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,25 +4033,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:39.000Z</t>
+          <t>2026-08-23T10:38:39.000Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:29.000Z</t>
+          <t>2026-08-23T10:38:29.000Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4222,7 +4222,7 @@
         <v>59</v>
       </c>
       <c r="O41" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -4231,13 +4231,13 @@
         <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="n">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:25.000Z</t>
+          <t>2026-08-23T10:38:25.000Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O42" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -4324,13 +4324,13 @@
         <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:24.000Z</t>
+          <t>2026-08-23T10:38:24.000Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4408,7 +4408,7 @@
         <v>53</v>
       </c>
       <c r="O43" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -4417,13 +4417,13 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:19.000Z</t>
+          <t>2026-08-23T10:38:19.000Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-23T02:38:38.000-07:00</t>
+          <t>2026-08-23T03:38:38.000-07:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-08-23T09:38:38.000Z</t>
+          <t>2026-08-23T10:38:38.000Z</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O44" t="n">
         <v>63</v>
@@ -4507,16 +4507,16 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:59.000Z</t>
+          <t>2026-08-23T10:37:59.000Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,25 +4591,25 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O45" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:35.000Z</t>
+          <t>2026-08-23T10:37:35.000Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4684,25 +4684,25 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O46" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:35.000Z</t>
+          <t>2026-08-23T10:37:35.000Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4786,16 +4786,16 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R47" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T47" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:25.000Z</t>
+          <t>2026-08-23T10:37:25.000Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4873,22 +4873,22 @@
         <v>76</v>
       </c>
       <c r="O48" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
         <v>139</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T48" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:19.000Z</t>
+          <t>2026-08-23T10:37:19.000Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4963,25 +4963,25 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O49" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:14.000Z</t>
+          <t>2026-08-23T10:37:14.000Z</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,25 +5056,25 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O50" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="S50" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T50" t="n">
-        <v>92</v>
+        <v>344</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:05.000Z</t>
+          <t>2026-08-23T10:37:05.000Z</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
+        <v>76</v>
+      </c>
+      <c r="O51" t="n">
+        <v>36</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" t="n">
+        <v>57</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="n">
         <v>68</v>
-      </c>
-      <c r="O51" t="n">
-        <v>50</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>85</v>
-      </c>
-      <c r="S51" t="n">
-        <v>8</v>
-      </c>
-      <c r="T51" t="n">
-        <v>79</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:04.000Z</t>
+          <t>2026-08-23T10:37:04.000Z</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-08-23T02:37:37.000-07:00</t>
+          <t>2026-08-23T03:37:37.000-07:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-23T09:37:37.000Z</t>
+          <t>2026-08-23T10:37:37.000Z</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O52" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R52" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="S52" t="n">
         <v>11</v>
       </c>
       <c r="T52" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-23T09:36:34.000Z</t>
+          <t>2026-08-23T10:36:34.000Z</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-23T02:36:36.000-07:00</t>
+          <t>2026-08-23T03:36:36.000-07:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-08-23T09:36:36.000Z</t>
+          <t>2026-08-23T10:36:36.000Z</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5335,25 +5335,25 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O53" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="S53" t="n">
         <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-23T09:36:15.000Z</t>
+          <t>2026-08-23T10:36:15.000Z</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-08-23T02:36:36.000-07:00</t>
+          <t>2026-08-23T03:36:36.000-07:00</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-08-23T09:36:36.000Z</t>
+          <t>2026-08-23T10:36:36.000Z</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,25 +5428,25 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O54" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R54" t="n">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T54" t="n">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-23T09:35:49.000Z</t>
+          <t>2026-08-23T10:35:49.000Z</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-08-23T02:35:35.000-07:00</t>
+          <t>2026-08-23T03:35:35.000-07:00</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-23T09:35:35.000Z</t>
+          <t>2026-08-23T10:35:35.000Z</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O55" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="S55" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-23T09:35:39.000Z</t>
+          <t>2026-08-23T10:35:39.000Z</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-08-23T02:35:35.000-07:00</t>
+          <t>2026-08-23T03:35:35.000-07:00</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-23T09:35:35.000Z</t>
+          <t>2026-08-23T10:35:35.000Z</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O56" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T56" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:44.000Z</t>
+          <t>2026-08-23T10:34:44.000Z</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-08-23T02:34:34.000-07:00</t>
+          <t>2026-08-23T03:34:34.000-07:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:34.000Z</t>
+          <t>2026-08-23T10:34:34.000Z</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5710,22 +5710,22 @@
         <v>63</v>
       </c>
       <c r="O57" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T57" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:24.000Z</t>
+          <t>2026-08-23T10:34:24.000Z</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-08-23T02:34:34.000-07:00</t>
+          <t>2026-08-23T03:34:34.000-07:00</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:34.000Z</t>
+          <t>2026-08-23T10:34:34.000Z</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O58" t="n">
         <v>82</v>
@@ -5812,13 +5812,13 @@
         <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>18</v>
+        <v>291</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>340</v>
+        <v>23</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:14.000Z</t>
+          <t>2026-08-23T10:34:14.000Z</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-08-23T02:34:34.000-07:00</t>
+          <t>2026-08-23T03:34:34.000-07:00</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:34.000Z</t>
+          <t>2026-08-23T10:34:34.000Z</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5902,16 +5902,16 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>102</v>
+      </c>
+      <c r="S59" t="n">
         <v>3</v>
       </c>
-      <c r="R59" t="n">
-        <v>49</v>
-      </c>
-      <c r="S59" t="n">
-        <v>7</v>
-      </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:05.000Z</t>
+          <t>2026-08-23T10:34:05.000Z</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-08-23T02:34:34.000-07:00</t>
+          <t>2026-08-23T03:34:34.000-07:00</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-08-23T09:34:34.000Z</t>
+          <t>2026-08-23T10:34:34.000Z</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5989,7 +5989,7 @@
         <v>76</v>
       </c>
       <c r="O60" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         <v>9</v>
       </c>
       <c r="R60" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
       </c>
       <c r="T60" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:55.000Z</t>
+          <t>2026-08-23T10:33:55.000Z</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-08-23T02:33:33.000-07:00</t>
+          <t>2026-08-23T03:33:33.000-07:00</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:33.000Z</t>
+          <t>2026-08-23T10:33:33.000Z</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6079,25 +6079,25 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R61" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:45.000Z</t>
+          <t>2026-08-23T10:33:45.000Z</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-08-23T02:33:33.000-07:00</t>
+          <t>2026-08-23T03:33:33.000-07:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:33.000Z</t>
+          <t>2026-08-23T10:33:33.000Z</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O62" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:44.000Z</t>
+          <t>2026-08-23T10:33:44.000Z</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-08-23T02:33:33.000-07:00</t>
+          <t>2026-08-23T03:33:33.000-07:00</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:33.000Z</t>
+          <t>2026-08-23T10:33:33.000Z</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O63" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>320</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:35.000Z</t>
+          <t>2026-08-23T10:33:35.000Z</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-08-23T02:33:33.000-07:00</t>
+          <t>2026-08-23T03:33:33.000-07:00</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:33.000Z</t>
+          <t>2026-08-23T10:33:33.000Z</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>12</v>
       </c>
       <c r="R64" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T64" t="n">
         <v>52</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:34.000Z</t>
+          <t>2026-08-23T10:33:34.000Z</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-08-23T02:33:33.000-07:00</t>
+          <t>2026-08-23T03:33:33.000-07:00</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:33.000Z</t>
+          <t>2026-08-23T10:33:33.000Z</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6451,25 +6451,25 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O65" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>301</v>
+        <v>33</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
       </c>
       <c r="T65" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:25.000Z</t>
+          <t>2026-08-23T10:33:25.000Z</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-08-23T02:33:33.000-07:00</t>
+          <t>2026-08-23T03:33:33.000-07:00</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-08-23T09:33:33.000Z</t>
+          <t>2026-08-23T10:33:33.000Z</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6547,7 +6547,7 @@
         <v>70</v>
       </c>
       <c r="O66" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -6556,13 +6556,13 @@
         <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T66" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-08-23T09:32:54.000Z</t>
+          <t>2026-08-23T10:32:54.000Z</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-08-23T02:32:32.000-07:00</t>
+          <t>2026-08-23T03:32:32.000-07:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-08-23T09:32:32.000Z</t>
+          <t>2026-08-23T10:32:32.000Z</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,25 +6637,25 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="O67" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-23T09:28:24.000Z</t>
+          <t>2026-08-23T10:28:24.000Z</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-08-23T02:28:28.000-07:00</t>
+          <t>2026-08-23T03:28:28.000-07:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-23T09:28:28.000Z</t>
+          <t>2026-08-23T10:28:28.000Z</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O68" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-23T09:27:44.000Z</t>
+          <t>2026-08-23T10:27:44.000Z</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-08-23T02:27:27.000-07:00</t>
+          <t>2026-08-23T03:27:27.000-07:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-23T09:27:27.000Z</t>
+          <t>2026-08-23T10:27:27.000Z</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O69" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-08-23T09:27:34.000Z</t>
+          <t>2026-08-23T10:27:34.000Z</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-08-23T02:27:27.000-07:00</t>
+          <t>2026-08-23T03:27:27.000-07:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-23T09:27:27.000Z</t>
+          <t>2026-08-23T10:27:27.000Z</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O70" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -6928,13 +6928,13 @@
         <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-08-23T09:27:34.000Z</t>
+          <t>2026-08-23T10:27:34.000Z</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-08-23T02:27:27.000-07:00</t>
+          <t>2026-08-23T03:27:27.000-07:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-23T09:27:27.000Z</t>
+          <t>2026-08-23T10:27:27.000Z</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,25 +7009,25 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O71" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T71" t="n">
-        <v>66</v>
+        <v>351</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-08-23T09:26:44.000Z</t>
+          <t>2026-08-23T10:26:44.000Z</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-08-23T02:26:26.000-07:00</t>
+          <t>2026-08-23T03:26:26.000-07:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-23T09:26:26.000Z</t>
+          <t>2026-08-23T10:26:26.000Z</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O72" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -7114,13 +7114,13 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>358</v>
+        <v>30</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>47</v>
+        <v>331</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-08-23T09:26:15.000Z</t>
+          <t>2026-08-23T10:26:15.000Z</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-08-23T02:26:26.000-07:00</t>
+          <t>2026-08-23T03:26:26.000-07:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-23T09:26:26.000Z</t>
+          <t>2026-08-23T10:26:26.000Z</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O73" t="n">
         <v>21</v>
@@ -7207,13 +7207,13 @@
         <v>15</v>
       </c>
       <c r="R73" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="S73" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T73" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-08-23T09:26:05.000Z</t>
+          <t>2026-08-23T10:26:05.000Z</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-08-23T02:26:26.000-07:00</t>
+          <t>2026-08-23T03:26:26.000-07:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-23T09:26:26.000Z</t>
+          <t>2026-08-23T10:26:26.000Z</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,25 +7288,25 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O74" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-08-23T09:25:55.000Z</t>
+          <t>2026-08-23T10:25:55.000Z</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-08-23T02:25:25.000-07:00</t>
+          <t>2026-08-23T03:25:25.000-07:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-23T09:25:25.000Z</t>
+          <t>2026-08-23T10:25:25.000Z</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7384,22 +7384,22 @@
         <v>54</v>
       </c>
       <c r="O75" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-08-23T09:24:24.000Z</t>
+          <t>2026-08-23T10:24:24.000Z</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-08-23T02:24:24.000-07:00</t>
+          <t>2026-08-23T03:24:24.000-07:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-23T09:24:24.000Z</t>
+          <t>2026-08-23T10:24:24.000Z</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,25 +7474,25 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O76" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R76" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:19.000Z</t>
+          <t>2026-08-23T10:23:19.000Z</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-08-23T02:23:23.000-07:00</t>
+          <t>2026-08-23T03:23:23.000-07:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:23.000Z</t>
+          <t>2026-08-23T10:23:23.000Z</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O77" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -7579,13 +7579,13 @@
         <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="S77" t="n">
         <v>7</v>
       </c>
       <c r="T77" t="n">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:14.000Z</t>
+          <t>2026-08-23T10:23:14.000Z</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-08-23T02:23:23.000-07:00</t>
+          <t>2026-08-23T03:23:23.000-07:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:23.000Z</t>
+          <t>2026-08-23T10:23:23.000Z</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O78" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -7672,13 +7672,13 @@
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T78" t="n">
-        <v>176</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:09.000Z</t>
+          <t>2026-08-23T10:23:09.000Z</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-08-23T02:23:23.000-07:00</t>
+          <t>2026-08-23T03:23:23.000-07:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:23.000Z</t>
+          <t>2026-08-23T10:23:23.000Z</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,25 +7753,25 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O79" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R79" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:05.000Z</t>
+          <t>2026-08-23T10:23:05.000Z</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-08-23T02:23:23.000-07:00</t>
+          <t>2026-08-23T03:23:23.000-07:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-23T09:23:23.000Z</t>
+          <t>2026-08-23T10:23:23.000Z</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O80" t="n">
         <v>37</v>
@@ -7855,16 +7855,16 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T80" t="n">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-08-23T09:22:34.000Z</t>
+          <t>2026-08-23T10:22:34.000Z</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-08-23T02:22:22.000-07:00</t>
+          <t>2026-08-23T03:22:22.000-07:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-23T09:22:22.000Z</t>
+          <t>2026-08-23T10:22:22.000Z</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7939,25 +7939,25 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O81" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="n">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-08-23T09:22:24.000Z</t>
+          <t>2026-08-23T10:22:24.000Z</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-08-23T02:22:22.000-07:00</t>
+          <t>2026-08-23T03:22:22.000-07:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-23T09:22:22.000Z</t>
+          <t>2026-08-23T10:22:22.000Z</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,25 +8032,25 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O82" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
       </c>
       <c r="T82" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-08-23T09:20:45.000Z</t>
+          <t>2026-08-23T10:20:45.000Z</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-08-23T02:20:20.000-07:00</t>
+          <t>2026-08-23T03:20:20.000-07:00</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-23T09:20:20.000Z</t>
+          <t>2026-08-23T10:20:20.000Z</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,25 +8125,25 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O83" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T83" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-08-23T09:20:39.000Z</t>
+          <t>2026-08-23T10:20:39.000Z</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-08-23T02:20:20.000-07:00</t>
+          <t>2026-08-23T03:20:20.000-07:00</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-23T09:20:20.000Z</t>
+          <t>2026-08-23T10:20:20.000Z</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,25 +8218,25 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O84" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>355</v>
+        <v>43</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T84" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:25.000Z</t>
+          <t>2026-08-23T10:19:25.000Z</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-08-23T02:19:19.000-07:00</t>
+          <t>2026-08-23T03:19:19.000-07:00</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:19.000Z</t>
+          <t>2026-08-23T10:19:19.000Z</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O85" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -8323,13 +8323,13 @@
         <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:24.000Z</t>
+          <t>2026-08-23T10:19:24.000Z</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-08-23T02:19:19.000-07:00</t>
+          <t>2026-08-23T03:19:19.000-07:00</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:19.000Z</t>
+          <t>2026-08-23T10:19:19.000Z</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O86" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R86" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="S86" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T86" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:14.000Z</t>
+          <t>2026-08-23T10:19:14.000Z</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-08-23T02:19:19.000-07:00</t>
+          <t>2026-08-23T03:19:19.000-07:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:19.000Z</t>
+          <t>2026-08-23T10:19:19.000Z</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8500,7 +8500,7 @@
         <v>74</v>
       </c>
       <c r="O87" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
@@ -8509,13 +8509,13 @@
         <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:04.000Z</t>
+          <t>2026-08-23T10:19:04.000Z</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-08-23T02:19:19.000-07:00</t>
+          <t>2026-08-23T03:19:19.000-07:00</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-08-23T09:19:19.000Z</t>
+          <t>2026-08-23T10:19:19.000Z</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O88" t="n">
         <v>38</v>
@@ -8602,13 +8602,13 @@
         <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T88" t="n">
-        <v>343</v>
+        <v>70</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-08-23T09:17:49.000Z</t>
+          <t>2026-08-23T10:17:49.000Z</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-08-23T02:17:17.000-07:00</t>
+          <t>2026-08-23T03:17:17.000-07:00</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-23T09:17:17.000Z</t>
+          <t>2026-08-23T10:17:17.000Z</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O89" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T89" t="n">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:54.000Z</t>
+          <t>2026-08-23T10:16:54.000Z</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-08-23T02:16:16.000-07:00</t>
+          <t>2026-08-23T03:16:16.000-07:00</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:16.000Z</t>
+          <t>2026-08-23T10:16:16.000Z</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,25 +8776,25 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O90" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T90" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:34.000Z</t>
+          <t>2026-08-23T10:16:34.000Z</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-08-23T02:16:16.000-07:00</t>
+          <t>2026-08-23T03:16:16.000-07:00</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:16.000Z</t>
+          <t>2026-08-23T10:16:16.000Z</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O91" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -8881,13 +8881,13 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T91" t="n">
-        <v>221</v>
+        <v>55</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:24.000Z</t>
+          <t>2026-08-23T10:16:24.000Z</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-08-23T02:16:16.000-07:00</t>
+          <t>2026-08-23T03:16:16.000-07:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:16.000Z</t>
+          <t>2026-08-23T10:16:16.000Z</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8962,25 +8962,25 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O92" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T92" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:14.000Z</t>
+          <t>2026-08-23T10:16:14.000Z</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-08-23T02:16:16.000-07:00</t>
+          <t>2026-08-23T03:16:16.000-07:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:16.000Z</t>
+          <t>2026-08-23T10:16:16.000Z</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O93" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -9067,13 +9067,13 @@
         <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T93" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:04.000Z</t>
+          <t>2026-08-23T10:16:04.000Z</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-08-23T02:16:16.000-07:00</t>
+          <t>2026-08-23T03:16:16.000-07:00</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-23T09:16:16.000Z</t>
+          <t>2026-08-23T10:16:16.000Z</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,25 +9148,25 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O94" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-23T09:15:24.000Z</t>
+          <t>2026-08-23T10:15:24.000Z</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-08-23T02:15:15.000-07:00</t>
+          <t>2026-08-23T03:15:15.000-07:00</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-23T09:15:15.000Z</t>
+          <t>2026-08-23T10:15:15.000Z</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O95" t="n">
         <v>39</v>
@@ -9250,16 +9250,16 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T95" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:54.000Z</t>
+          <t>2026-08-23T10:14:54.000Z</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-08-23T02:14:14.000-07:00</t>
+          <t>2026-08-23T03:14:14.000-07:00</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9337,22 +9337,22 @@
         <v>67</v>
       </c>
       <c r="O96" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="S96" t="n">
         <v>8</v>
       </c>
       <c r="T96" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:24.000Z</t>
+          <t>2026-08-23T10:14:24.000Z</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-08-23T02:14:14.000-07:00</t>
+          <t>2026-08-23T03:14:14.000-07:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9436,16 +9436,16 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R97" t="n">
-        <v>18</v>
+        <v>326</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T97" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-08-23T02:14:14.000-07:00</t>
+          <t>2026-08-23T03:14:14.000-07:00</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9529,10 +9529,10 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R98" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="S98" t="n">
         <v>7</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:11.000Z</t>
+          <t>2026-08-23T10:14:11.000Z</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-08-23T02:14:14.000-07:00</t>
+          <t>2026-08-23T03:14:14.000-07:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O99" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -9625,13 +9625,13 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>209</v>
+        <v>326</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:05.000Z</t>
+          <t>2026-08-23T10:14:05.000Z</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-08-23T02:14:14.000-07:00</t>
+          <t>2026-08-23T03:14:14.000-07:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9706,25 +9706,25 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O100" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:04.000Z</t>
+          <t>2026-08-23T10:14:04.000Z</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-08-23T02:14:14.000-07:00</t>
+          <t>2026-08-23T03:14:14.000-07:00</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-23T09:14:14.000Z</t>
+          <t>2026-08-23T10:14:14.000Z</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9799,25 +9799,25 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O101" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
       </c>
       <c r="T101" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:45.000Z</t>
+          <t>2026-08-23T10:13:45.000Z</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-08-23T02:13:13.000-07:00</t>
+          <t>2026-08-23T03:13:13.000-07:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:13.000Z</t>
+          <t>2026-08-23T10:13:13.000Z</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,25 +9892,25 @@
         </is>
       </c>
       <c r="N102" t="n">
+        <v>63</v>
+      </c>
+      <c r="O102" t="n">
         <v>68</v>
       </c>
-      <c r="O102" t="n">
-        <v>52</v>
-      </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R102" t="n">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T102" t="n">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:34.000Z</t>
+          <t>2026-08-23T10:13:34.000Z</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-08-23T02:13:13.000-07:00</t>
+          <t>2026-08-23T03:13:13.000-07:00</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:13.000Z</t>
+          <t>2026-08-23T10:13:13.000Z</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O103" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R103" t="n">
-        <v>317</v>
+        <v>118</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T103" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:15.000Z</t>
+          <t>2026-08-23T10:13:15.000Z</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-08-23T02:13:13.000-07:00</t>
+          <t>2026-08-23T03:13:13.000-07:00</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:13.000Z</t>
+          <t>2026-08-23T10:13:13.000Z</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,25 +10078,25 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O104" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R104" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="S104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T104" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:14.000Z</t>
+          <t>2026-08-23T10:13:14.000Z</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-08-23T02:13:13.000-07:00</t>
+          <t>2026-08-23T03:13:13.000-07:00</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:13.000Z</t>
+          <t>2026-08-23T10:13:13.000Z</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10171,10 +10171,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O105" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>6</v>
       </c>
       <c r="R105" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T105" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:04.000Z</t>
+          <t>2026-08-23T10:13:04.000Z</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-08-23T02:13:13.000-07:00</t>
+          <t>2026-08-23T03:13:13.000-07:00</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-08-23T09:13:13.000Z</t>
+          <t>2026-08-23T10:13:13.000Z</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O106" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -10276,13 +10276,13 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T106" t="n">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-08-23T09:12:54.000Z</t>
+          <t>2026-08-23T10:12:54.000Z</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-08-23T02:12:12.000-07:00</t>
+          <t>2026-08-23T03:12:12.000-07:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-08-23T09:12:12.000Z</t>
+          <t>2026-08-23T10:12:12.000Z</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O107" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T107" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:54.000Z</t>
+          <t>2026-08-23T10:11:54.000Z</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-08-23T02:11:11.000-07:00</t>
+          <t>2026-08-23T03:11:11.000-07:00</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:11.000Z</t>
+          <t>2026-08-23T10:11:11.000Z</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O108" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -10462,13 +10462,13 @@
         <v>5</v>
       </c>
       <c r="R108" t="n">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="S108" t="n">
         <v>7</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:44.000Z</t>
+          <t>2026-08-23T10:11:44.000Z</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-08-23T02:11:11.000-07:00</t>
+          <t>2026-08-23T03:11:11.000-07:00</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:11.000Z</t>
+          <t>2026-08-23T10:11:11.000Z</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O109" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R109" t="n">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T109" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:14.000Z</t>
+          <t>2026-08-23T10:11:14.000Z</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-08-23T02:11:11.000-07:00</t>
+          <t>2026-08-23T03:11:11.000-07:00</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:11.000Z</t>
+          <t>2026-08-23T10:11:11.000Z</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,25 +10636,25 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="O110" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>332</v>
+        <v>183</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T110" t="n">
-        <v>285</v>
+        <v>36</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:14.000Z</t>
+          <t>2026-08-23T10:11:14.000Z</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-08-23T02:11:11.000-07:00</t>
+          <t>2026-08-23T03:11:11.000-07:00</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:11.000Z</t>
+          <t>2026-08-23T10:11:11.000Z</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,25 +10729,25 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O111" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R111" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S111" t="n">
         <v>6</v>
       </c>
       <c r="T111" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:04.000Z</t>
+          <t>2026-08-23T10:11:04.000Z</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-08-23T02:11:11.000-07:00</t>
+          <t>2026-08-23T03:11:11.000-07:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:11.000Z</t>
+          <t>2026-08-23T10:11:11.000Z</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O112" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="S112" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T112" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:04.000Z</t>
+          <t>2026-08-23T10:11:04.000Z</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-08-23T02:11:11.000-07:00</t>
+          <t>2026-08-23T03:11:11.000-07:00</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-23T09:11:11.000Z</t>
+          <t>2026-08-23T10:11:11.000Z</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,25 +10915,25 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O113" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>303</v>
+        <v>172</v>
       </c>
       <c r="S113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T113" t="n">
-        <v>300</v>
+        <v>148</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-08-23T09:09:54.000Z</t>
+          <t>2026-08-23T10:09:54.000Z</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-08-23T02:09:09.000-07:00</t>
+          <t>2026-08-23T03:09:09.000-07:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-23T09:09:09.000Z</t>
+          <t>2026-08-23T10:09:09.000Z</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11017,16 +11017,16 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T114" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-08-23T09:09:14.000Z</t>
+          <t>2026-08-23T10:09:14.000Z</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-08-23T02:09:09.000-07:00</t>
+          <t>2026-08-23T03:09:09.000-07:00</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-23T09:09:09.000Z</t>
+          <t>2026-08-23T10:09:09.000Z</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,22 +11101,22 @@
         </is>
       </c>
       <c r="N115" t="n">
+        <v>64</v>
+      </c>
+      <c r="O115" t="n">
         <v>65</v>
       </c>
-      <c r="O115" t="n">
-        <v>61</v>
-      </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="S115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T115" t="n">
         <v>326</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:54.000Z</t>
+          <t>2026-08-23T10:08:54.000Z</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,25 +11194,25 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O116" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
       </c>
       <c r="T116" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:44.000Z</t>
+          <t>2026-08-23T10:08:44.000Z</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11290,7 +11290,7 @@
         <v>55</v>
       </c>
       <c r="O117" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -11299,13 +11299,13 @@
         <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="S117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T117" t="n">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:24.000Z</t>
+          <t>2026-08-23T10:08:24.000Z</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O118" t="n">
         <v>69</v>
@@ -11389,16 +11389,16 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R118" t="n">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T118" t="n">
-        <v>15</v>
+        <v>348</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:24.000Z</t>
+          <t>2026-08-23T10:08:24.000Z</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,10 +11473,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O119" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -11485,7 +11485,7 @@
         <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S119" t="n">
         <v>3</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:14.000Z</t>
+          <t>2026-08-23T10:08:14.000Z</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O120" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,10 +11578,10 @@
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T120" t="n">
         <v>359</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:14.000Z</t>
+          <t>2026-08-23T10:08:14.000Z</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O121" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -11671,13 +11671,13 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="S121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T121" t="n">
-        <v>93</v>
+        <v>349</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:14.000Z</t>
+          <t>2026-08-23T10:08:14.000Z</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,10 +11752,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O122" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -11764,13 +11764,13 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="S122" t="n">
         <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:04.000Z</t>
+          <t>2026-08-23T10:08:04.000Z</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-08-23T02:08:08.000-07:00</t>
+          <t>2026-08-23T03:08:08.000-07:00</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-23T09:08:08.000Z</t>
+          <t>2026-08-23T10:08:08.000Z</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11845,25 +11845,25 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="O123" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>101</v>
+        <v>316</v>
       </c>
       <c r="S123" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T123" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:54.000Z</t>
+          <t>2026-08-23T10:07:54.000Z</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-08-23T02:07:07.000-07:00</t>
+          <t>2026-08-23T03:07:07.000-07:00</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:07.000Z</t>
+          <t>2026-08-23T10:07:07.000Z</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11938,25 +11938,25 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="O124" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R124" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T124" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:54.000Z</t>
+          <t>2026-08-23T10:07:54.000Z</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-08-23T02:07:07.000-07:00</t>
+          <t>2026-08-23T03:07:07.000-07:00</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:07.000Z</t>
+          <t>2026-08-23T10:07:07.000Z</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,25 +12031,25 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O125" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>356</v>
+        <v>31</v>
       </c>
       <c r="S125" t="n">
         <v>6</v>
       </c>
       <c r="T125" t="n">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:14.000Z</t>
+          <t>2026-08-23T10:07:14.000Z</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-08-23T02:07:07.000-07:00</t>
+          <t>2026-08-23T03:07:07.000-07:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:07.000Z</t>
+          <t>2026-08-23T10:07:07.000Z</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,25 +12124,25 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O126" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R126" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="S126" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T126" t="n">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:14.000Z</t>
+          <t>2026-08-23T10:07:14.000Z</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-08-23T02:07:07.000-07:00</t>
+          <t>2026-08-23T03:07:07.000-07:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-23T09:07:07.000Z</t>
+          <t>2026-08-23T10:07:07.000Z</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O127" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P127" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
         <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>325</v>
+        <v>9</v>
       </c>
       <c r="S127" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-08-23T09:06:34.000Z</t>
+          <t>2026-08-23T10:06:34.000Z</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-08-23T02:06:06.000-07:00</t>
+          <t>2026-08-23T03:06:06.000-07:00</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-23T09:06:06.000Z</t>
+          <t>2026-08-23T10:06:06.000Z</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12310,25 +12310,25 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O128" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>277</v>
+        <v>142</v>
       </c>
       <c r="S128" t="n">
         <v>4</v>
       </c>
       <c r="T128" t="n">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-08-23T09:06:25.000Z</t>
+          <t>2026-08-23T10:06:25.000Z</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-08-23T02:06:06.000-07:00</t>
+          <t>2026-08-23T03:06:06.000-07:00</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-23T09:06:06.000Z</t>
+          <t>2026-08-23T10:06:06.000Z</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,25 +12403,25 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O129" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T129" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-08-23T09:06:04.000Z</t>
+          <t>2026-08-23T10:06:04.000Z</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-08-23T02:06:06.000-07:00</t>
+          <t>2026-08-23T03:06:06.000-07:00</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-23T09:06:06.000Z</t>
+          <t>2026-08-23T10:06:06.000Z</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O130" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -12508,13 +12508,13 @@
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>352</v>
+        <v>42</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
       </c>
       <c r="T130" t="n">
-        <v>321</v>
+        <v>40</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:54.000Z</t>
+          <t>2026-08-23T10:05:54.000Z</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-08-23T02:05:05.000-07:00</t>
+          <t>2026-08-23T03:05:05.000-07:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:05.000Z</t>
+          <t>2026-08-23T10:05:05.000Z</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,25 +12589,25 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O131" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R131" t="n">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T131" t="n">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:54.000Z</t>
+          <t>2026-08-23T10:05:54.000Z</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-08-23T02:05:05.000-07:00</t>
+          <t>2026-08-23T03:05:05.000-07:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:05.000Z</t>
+          <t>2026-08-23T10:05:05.000Z</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O132" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
@@ -12694,13 +12694,13 @@
         <v>3</v>
       </c>
       <c r="R132" t="n">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="S132" t="n">
         <v>6</v>
       </c>
       <c r="T132" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:44.000Z</t>
+          <t>2026-08-23T10:05:44.000Z</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-08-23T02:05:05.000-07:00</t>
+          <t>2026-08-23T03:05:05.000-07:00</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:05.000Z</t>
+          <t>2026-08-23T10:05:05.000Z</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12778,7 +12778,7 @@
         <v>59</v>
       </c>
       <c r="O133" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -12787,13 +12787,13 @@
         <v>2</v>
       </c>
       <c r="R133" t="n">
-        <v>187</v>
+        <v>25</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T133" t="n">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:44.000Z</t>
+          <t>2026-08-23T10:05:44.000Z</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-08-23T02:05:05.000-07:00</t>
+          <t>2026-08-23T03:05:05.000-07:00</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:05.000Z</t>
+          <t>2026-08-23T10:05:05.000Z</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O134" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -12880,13 +12880,13 @@
         <v>6</v>
       </c>
       <c r="R134" t="n">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="S134" t="n">
         <v>9</v>
       </c>
       <c r="T134" t="n">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:14.000Z</t>
+          <t>2026-08-23T10:05:14.000Z</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-08-23T02:05:05.000-07:00</t>
+          <t>2026-08-23T03:05:05.000-07:00</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-23T09:05:05.000Z</t>
+          <t>2026-08-23T10:05:05.000Z</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12964,22 +12964,22 @@
         <v>71</v>
       </c>
       <c r="O135" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T135" t="n">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-08-23T09:04:14.000Z</t>
+          <t>2026-08-23T10:04:14.000Z</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-08-23T02:04:04.000-07:00</t>
+          <t>2026-08-23T03:04:04.000-07:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-23T09:04:04.000Z</t>
+          <t>2026-08-23T10:04:04.000Z</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,25 +13054,25 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O136" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R136" t="n">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T136" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-08-23T09:04:04.000Z</t>
+          <t>2026-08-23T10:04:04.000Z</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-08-23T02:04:04.000-07:00</t>
+          <t>2026-08-23T03:04:04.000-07:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-23T09:04:04.000Z</t>
+          <t>2026-08-23T10:04:04.000Z</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13156,16 +13156,16 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="S137" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T137" t="n">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:54.000Z</t>
+          <t>2026-08-23T10:03:54.000Z</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13243,22 +13243,22 @@
         <v>59</v>
       </c>
       <c r="O138" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P138" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R138" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="S138" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T138" t="n">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:51.000Z</t>
+          <t>2026-08-23T10:03:51.000Z</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,25 +13333,25 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O139" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R139" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="S139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T139" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:45.000Z</t>
+          <t>2026-08-23T10:03:45.000Z</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13429,22 +13429,22 @@
         <v>74</v>
       </c>
       <c r="O140" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R140" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="S140" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T140" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:14.000Z</t>
+          <t>2026-08-23T10:03:14.000Z</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O141" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -13531,13 +13531,13 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="S141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T141" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:05.000Z</t>
+          <t>2026-08-23T10:03:05.000Z</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,25 +13612,25 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O142" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R142" t="n">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="S142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T142" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:04.000Z</t>
+          <t>2026-08-23T10:03:04.000Z</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,25 +13705,25 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O143" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="S143" t="n">
         <v>4</v>
       </c>
       <c r="T143" t="n">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:04.000Z</t>
+          <t>2026-08-23T10:03:04.000Z</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-08-23T02:03:03.000-07:00</t>
+          <t>2026-08-23T03:03:03.000-07:00</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-23T09:03:03.000Z</t>
+          <t>2026-08-23T10:03:03.000Z</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13798,25 +13798,25 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O144" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R144" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
       </c>
       <c r="T144" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-08-23T09:02:55.000Z</t>
+          <t>2026-08-23T10:02:55.000Z</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-08-23T02:02:02.000-07:00</t>
+          <t>2026-08-23T03:02:02.000-07:00</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-23T09:02:02.000Z</t>
+          <t>2026-08-23T10:02:02.000Z</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13894,22 +13894,22 @@
         <v>81</v>
       </c>
       <c r="O145" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R145" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="S145" t="n">
         <v>11</v>
       </c>
       <c r="T145" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-08-23T09:02:04.000Z</t>
+          <t>2026-08-23T10:02:04.000Z</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-08-23T02:02:02.000-07:00</t>
+          <t>2026-08-23T03:02:02.000-07:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-23T09:02:02.000Z</t>
+          <t>2026-08-23T10:02:02.000Z</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13984,10 +13984,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O146" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13996,13 +13996,13 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="S146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T146" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-08-23T09:02:04.000Z</t>
+          <t>2026-08-23T10:02:04.000Z</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-08-23T02:02:02.000-07:00</t>
+          <t>2026-08-23T03:02:02.000-07:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-23T09:02:02.000Z</t>
+          <t>2026-08-23T10:02:02.000Z</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,10 +14077,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O147" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -14092,10 +14092,10 @@
         <v>321</v>
       </c>
       <c r="S147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T147" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:54.000Z</t>
+          <t>2026-08-23T10:01:54.000Z</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-08-23T02:01:01.000-07:00</t>
+          <t>2026-08-23T03:01:01.000-07:00</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:01.000Z</t>
+          <t>2026-08-23T10:01:01.000Z</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14173,22 +14173,22 @@
         <v>61</v>
       </c>
       <c r="O148" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R148" t="n">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="S148" t="n">
         <v>12</v>
       </c>
       <c r="T148" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:54.000Z</t>
+          <t>2026-08-23T10:01:54.000Z</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-08-23T02:01:01.000-07:00</t>
+          <t>2026-08-23T03:01:01.000-07:00</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:01.000Z</t>
+          <t>2026-08-23T10:01:01.000Z</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O149" t="n">
         <v>23</v>
@@ -14272,16 +14272,16 @@
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R149" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="S149" t="n">
         <v>12</v>
       </c>
       <c r="T149" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:45.000Z</t>
+          <t>2026-08-23T10:01:45.000Z</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-08-23T02:01:01.000-07:00</t>
+          <t>2026-08-23T03:01:01.000-07:00</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:01.000Z</t>
+          <t>2026-08-23T10:01:01.000Z</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,25 +14356,25 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O150" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
+        <v>1</v>
+      </c>
+      <c r="R150" t="n">
+        <v>246</v>
+      </c>
+      <c r="S150" t="n">
         <v>4</v>
       </c>
-      <c r="R150" t="n">
-        <v>261</v>
-      </c>
-      <c r="S150" t="n">
-        <v>5</v>
-      </c>
       <c r="T150" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:25.000Z</t>
+          <t>2026-08-23T10:01:25.000Z</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-08-23T02:01:01.000-07:00</t>
+          <t>2026-08-23T03:01:01.000-07:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-23T09:01:01.000Z</t>
+          <t>2026-08-23T10:01:01.000Z</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,25 +14449,25 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O151" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R151" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="S151" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T151" t="n">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:45.000Z</t>
+          <t>2026-08-23T10:00:45.000Z</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,25 +14542,25 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O152" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R152" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S152" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T152" t="n">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:34.000Z</t>
+          <t>2026-08-23T10:00:34.000Z</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,25 +14635,25 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O153" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" t="n">
-        <v>295</v>
+        <v>357</v>
       </c>
       <c r="S153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T153" t="n">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:14.000Z</t>
+          <t>2026-08-23T10:00:14.000Z</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,25 +14728,25 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O154" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="S154" t="n">
         <v>4</v>
       </c>
       <c r="T154" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:04.000Z</t>
+          <t>2026-08-23T10:00:04.000Z</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-23T02:00:00.000-07:00</t>
+          <t>2026-08-23T03:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O155" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -14833,13 +14833,13 @@
         <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="S155" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T155" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-08-23T02:59:00.000-07:00</t>
+          <t>2026-08-23T03:59:00.000-07:00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-23T09:59:00.000Z</t>
+          <t>2026-08-23T10:59:00.000Z</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14914,7 +14914,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O156" t="n">
         <v>39</v>
@@ -14923,16 +14923,16 @@
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R156" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S156" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T156" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-08-23T02:59:00.000-07:00</t>
+          <t>2026-08-23T03:59:00.000-07:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-23T09:59:00.000Z</t>
+          <t>2026-08-23T10:59:00.000Z</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O157" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15019,13 +15019,13 @@
         <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="S157" t="n">
         <v>7</v>
       </c>
       <c r="T157" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-08-23T09:00:00.000Z</t>
+          <t>2026-08-23T10:00:00.000Z</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-08-23T02:59:00.000-07:00</t>
+          <t>2026-08-23T03:59:00.000-07:00</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00.000Z</t>
+          <t>2026-08-23T11:00:00.000Z</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-23T03:00:00.000-07:00</t>
+          <t>2026-08-23T04:00:00.000-07:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-23T09:59:00.000Z</t>
+          <t>2026-08-23T10:59:00.000Z</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15112,13 +15112,13 @@
         <v>1</v>
       </c>
       <c r="R158" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
       </c>
       <c r="T158" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/23/2026 22:42 MDT</t>
+          <t>8/23/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/23/2026 22:42 MDT</t>
+          <t>8/23/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/23/2026 22:42 MDT</t>
+          <t>8/23/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/23/2026 22:42 MDT</t>
+          <t>8/23/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/23/2026 22:42 MDT</t>
+          <t>8/23/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/23/2026 22:42 MDT</t>
+          <t>8/23/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -697,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O4" t="n">
         <v>49</v>
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>353</v>
+        <v>63</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
         <v>47</v>
@@ -976,13 +976,13 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/23/2026 22:41 MDT</t>
+          <t>8/23/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,25 +1057,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>119</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>65</v>
-      </c>
-      <c r="S7" t="n">
-        <v>9</v>
-      </c>
       <c r="T7" t="n">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/23/2026 22:40 MDT</t>
+          <t>8/23/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/23/2026 22:40 MDT</t>
+          <t>8/23/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/23/2026 22:40 MDT</t>
+          <t>8/23/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/23/2026 22:40 MDT</t>
+          <t>8/23/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/23/2026 22:40 MDT</t>
+          <t>8/23/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/23/2026 22:40 MDT</t>
+          <t>8/23/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>153</v>
@@ -1261,7 +1261,7 @@
         <v>18</v>
       </c>
       <c r="T9" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,25 +1522,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O12" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="S12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/23/2026 22:39 MDT</t>
+          <t>8/23/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,25 +1615,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O13" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1720,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1804,22 +1804,22 @@
         <v>75</v>
       </c>
       <c r="O15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>22</v>
+        <v>322</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>305</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,25 +1894,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O16" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R16" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="S16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T16" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,13 +1999,13 @@
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>257</v>
+        <v>323</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T18" t="n">
-        <v>258</v>
+        <v>306</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2173,25 +2173,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="T19" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,25 +2266,25 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O20" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/23/2026 22:38 MDT</t>
+          <t>8/23/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,25 +2359,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,25 +2452,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O22" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>275</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2548,22 +2548,22 @@
         <v>75</v>
       </c>
       <c r="O23" t="n">
+        <v>23</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
         <v>21</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>18</v>
-      </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2638,25 +2638,25 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O24" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,25 +2731,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S25" t="n">
         <v>16</v>
       </c>
       <c r="T25" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O26" t="n">
         <v>42</v>
@@ -2833,16 +2833,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R26" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="S26" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="T26" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O27" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
       </c>
       <c r="T27" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,25 +3010,25 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O28" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/23/2026 22:37 MDT</t>
+          <t>8/23/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>231</v>
+        <v>16</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/23/2026 22:36 MDT</t>
+          <t>8/23/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/23/2026 22:36 MDT</t>
+          <t>8/23/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/23/2026 22:36 MDT</t>
+          <t>8/23/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3199,22 +3199,22 @@
         <v>60</v>
       </c>
       <c r="O30" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/23/2026 22:36 MDT</t>
+          <t>8/23/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/23/2026 22:36 MDT</t>
+          <t>8/23/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/23/2026 22:36 MDT</t>
+          <t>8/23/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3301,13 +3301,13 @@
         <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T31" t="n">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/23/2026 22:35 MDT</t>
+          <t>8/23/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/23/2026 22:35 MDT</t>
+          <t>8/23/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/23/2026 22:35 MDT</t>
+          <t>8/23/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3385,22 +3385,22 @@
         <v>58</v>
       </c>
       <c r="O32" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="n">
-        <v>326</v>
+        <v>186</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/23/2026 22:35 MDT</t>
+          <t>8/23/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/23/2026 22:35 MDT</t>
+          <t>8/23/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/23/2026 22:35 MDT</t>
+          <t>8/23/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,25 +3475,25 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O33" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T33" t="n">
-        <v>239</v>
+        <v>338</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,25 +3568,25 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O34" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>348</v>
+        <v>287</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O35" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="S35" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="T35" t="n">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3754,25 +3754,25 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O36" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R36" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/23/2026 22:34 MDT</t>
+          <t>8/23/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3850,7 +3850,7 @@
         <v>81</v>
       </c>
       <c r="O37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         <v>17</v>
       </c>
       <c r="R37" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S37" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T37" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3940,25 +3940,25 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R38" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="S38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T38" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4042,16 +4042,16 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O40" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T40" t="n">
-        <v>321</v>
+        <v>141</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R41" t="n">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,25 +4312,25 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>62</v>
+      </c>
+      <c r="O42" t="n">
         <v>65</v>
       </c>
-      <c r="O42" t="n">
-        <v>58</v>
-      </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>333</v>
+        <v>85</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="n">
-        <v>138</v>
+        <v>312</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/23/2026 22:33 MDT</t>
+          <t>8/23/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4414,16 +4414,16 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="S43" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="T43" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/23/2026 22:32 MDT</t>
+          <t>8/23/2026 23:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/23/2026 22:32 MDT</t>
+          <t>8/23/2026 23:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/23/2026 22:32 MDT</t>
+          <t>8/23/2026 23:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O44" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -4510,13 +4510,13 @@
         <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/23/2026 22:28 MDT</t>
+          <t>8/23/2026 23:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/23/2026 22:28 MDT</t>
+          <t>8/23/2026 23:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/23/2026 22:28 MDT</t>
+          <t>8/23/2026 23:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O45" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4603,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>248</v>
+        <v>337</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>349</v>
+        <v>56</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4693,16 +4693,16 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
       </c>
       <c r="T46" t="n">
-        <v>349</v>
+        <v>203</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4789,13 +4789,13 @@
         <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S47" t="n">
         <v>6</v>
       </c>
       <c r="T47" t="n">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/23/2026 22:27 MDT</t>
+          <t>8/23/2026 23:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4870,25 +4870,25 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O48" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>354</v>
+        <v>11</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T48" t="n">
-        <v>355</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4963,25 +4963,25 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="O49" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>202</v>
+        <v>57</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T49" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,25 +5056,25 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T50" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/23/2026 22:26 MDT</t>
+          <t>8/23/2026 23:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O51" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R51" t="n">
-        <v>357</v>
+        <v>62</v>
       </c>
       <c r="S51" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/23/2026 22:25 MDT</t>
+          <t>8/23/2026 23:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/23/2026 22:25 MDT</t>
+          <t>8/23/2026 23:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/23/2026 22:25 MDT</t>
+          <t>8/23/2026 23:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O52" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/23/2026 22:24 MDT</t>
+          <t>8/23/2026 23:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/23/2026 22:24 MDT</t>
+          <t>8/23/2026 23:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/23/2026 22:24 MDT</t>
+          <t>8/23/2026 23:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5338,7 +5338,7 @@
         <v>68</v>
       </c>
       <c r="O53" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -5347,10 +5347,10 @@
         <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="n">
         <v>4</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,25 +5428,25 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O54" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R54" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="S54" t="n">
         <v>21</v>
       </c>
       <c r="T54" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O55" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -5533,13 +5533,13 @@
         <v>13</v>
       </c>
       <c r="R55" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="S55" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T55" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O56" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="S56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T56" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/23/2026 22:23 MDT</t>
+          <t>8/23/2026 23:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,25 +5707,25 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O57" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T57" t="n">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/23/2026 22:22 MDT</t>
+          <t>8/23/2026 23:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/23/2026 22:22 MDT</t>
+          <t>8/23/2026 23:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/23/2026 22:22 MDT</t>
+          <t>8/23/2026 23:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,25 +5800,25 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O58" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P58" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="R58" t="n">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="S58" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T58" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/23/2026 22:22 MDT</t>
+          <t>8/23/2026 23:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/23/2026 22:22 MDT</t>
+          <t>8/23/2026 23:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/23/2026 22:22 MDT</t>
+          <t>8/23/2026 23:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5896,22 +5896,22 @@
         <v>66</v>
       </c>
       <c r="O59" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="n">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/23/2026 22:20 MDT</t>
+          <t>8/23/2026 23:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/23/2026 22:20 MDT</t>
+          <t>8/23/2026 23:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/23/2026 22:20 MDT</t>
+          <t>8/23/2026 23:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5986,25 +5986,25 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O60" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T60" t="n">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/23/2026 22:20 MDT</t>
+          <t>8/23/2026 23:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/23/2026 22:20 MDT</t>
+          <t>8/23/2026 23:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/23/2026 22:20 MDT</t>
+          <t>8/23/2026 23:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -6091,13 +6091,13 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>199</v>
+        <v>347</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O62" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T62" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O63" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="S63" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="T63" t="n">
-        <v>86</v>
+        <v>248</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,25 +6358,25 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O64" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/23/2026 22:19 MDT</t>
+          <t>8/23/2026 23:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O65" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -6463,13 +6463,13 @@
         <v>7</v>
       </c>
       <c r="R65" t="n">
+        <v>17</v>
+      </c>
+      <c r="S65" t="n">
+        <v>21</v>
+      </c>
+      <c r="T65" t="n">
         <v>50</v>
-      </c>
-      <c r="S65" t="n">
-        <v>20</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/23/2026 22:17 MDT</t>
+          <t>8/23/2026 23:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/23/2026 22:17 MDT</t>
+          <t>8/23/2026 23:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/23/2026 22:17 MDT</t>
+          <t>8/23/2026 23:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6544,25 +6544,25 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="O66" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="P66" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>328</v>
+        <v>225</v>
       </c>
       <c r="S66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T66" t="n">
-        <v>222</v>
+        <v>352</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O67" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -6649,13 +6649,13 @@
         <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>125</v>
+        <v>355</v>
       </c>
       <c r="S67" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="T67" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6733,7 +6733,7 @@
         <v>58</v>
       </c>
       <c r="O68" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>203</v>
+        <v>104</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,25 +6823,25 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O69" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="S69" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T69" t="n">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6916,25 +6916,25 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O70" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R70" t="n">
+        <v>143</v>
+      </c>
+      <c r="S70" t="n">
+        <v>21</v>
+      </c>
+      <c r="T70" t="n">
         <v>152</v>
-      </c>
-      <c r="S70" t="n">
-        <v>19</v>
-      </c>
-      <c r="T70" t="n">
-        <v>170</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/23/2026 22:16 MDT</t>
+          <t>8/23/2026 23:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,25 +7009,25 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O71" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="n">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/23/2026 22:15 MDT</t>
+          <t>8/23/2026 23:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/23/2026 22:15 MDT</t>
+          <t>8/23/2026 23:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/23/2026 22:15 MDT</t>
+          <t>8/23/2026 23:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O72" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -7114,13 +7114,13 @@
         <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T72" t="n">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,25 +7195,25 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O73" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T73" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O74" t="n">
         <v>23</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>38</v>
+      </c>
+      <c r="S74" t="n">
         <v>5</v>
       </c>
-      <c r="R74" t="n">
-        <v>70</v>
-      </c>
-      <c r="S74" t="n">
-        <v>11</v>
-      </c>
       <c r="T74" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O75" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="P75" t="n">
         <v>0.01</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="R75" t="n">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="S75" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="T75" t="n">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,25 +7474,25 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -7579,13 +7579,13 @@
         <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
       </c>
       <c r="T77" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/23/2026 22:14 MDT</t>
+          <t>8/23/2026 23:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7660,22 +7660,22 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O78" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>17</v>
+        <v>338</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="n">
         <v>32</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,25 +7753,25 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O79" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R79" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O80" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="S80" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="T80" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7939,25 +7939,25 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O81" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R81" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T81" t="n">
-        <v>280</v>
+        <v>93</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8035,22 +8035,22 @@
         <v>80</v>
       </c>
       <c r="O82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R82" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="S82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T82" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/23/2026 22:13 MDT</t>
+          <t>8/23/2026 23:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O83" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>43</v>
+        <v>298</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/23/2026 22:12 MDT</t>
+          <t>8/23/2026 23:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/23/2026 22:12 MDT</t>
+          <t>8/23/2026 23:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/23/2026 22:12 MDT</t>
+          <t>8/23/2026 23:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,25 +8218,25 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O84" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T84" t="n">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,25 +8311,25 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O85" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R85" t="n">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,10 +8404,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O86" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T86" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,10 +8497,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O87" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
@@ -8509,13 +8509,13 @@
         <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>336</v>
+        <v>9</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="n">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,25 +8590,25 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T88" t="n">
-        <v>123</v>
+        <v>312</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O89" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T89" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/23/2026 22:11 MDT</t>
+          <t>8/23/2026 23:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,25 +8776,25 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O90" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/23/2026 22:09 MDT</t>
+          <t>8/23/2026 23:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/23/2026 22:09 MDT</t>
+          <t>8/23/2026 23:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/23/2026 22:09 MDT</t>
+          <t>8/23/2026 23:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8872,22 +8872,22 @@
         <v>57</v>
       </c>
       <c r="O91" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="P91" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="S91" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T91" t="n">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/23/2026 22:09 MDT</t>
+          <t>8/23/2026 23:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/23/2026 22:09 MDT</t>
+          <t>8/23/2026 23:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/23/2026 22:09 MDT</t>
+          <t>8/23/2026 23:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8962,25 +8962,25 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O92" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T92" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,25 +9055,25 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O93" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T93" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,25 +9148,25 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O94" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>48</v>
+        <v>353</v>
       </c>
       <c r="S94" t="n">
         <v>14</v>
       </c>
       <c r="T94" t="n">
-        <v>323</v>
+        <v>44</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9253,13 +9253,13 @@
         <v>8</v>
       </c>
       <c r="R95" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="S95" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T95" t="n">
-        <v>351</v>
+        <v>58</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9334,25 +9334,25 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O96" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S96" t="n">
         <v>2</v>
       </c>
       <c r="T96" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,25 +9427,25 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O97" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="S97" t="n">
         <v>3</v>
       </c>
       <c r="T97" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9520,10 +9520,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O98" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
@@ -9532,13 +9532,13 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T98" t="n">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,25 +9613,25 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O99" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="S99" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="T99" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/23/2026 22:08 MDT</t>
+          <t>8/23/2026 23:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9709,7 +9709,7 @@
         <v>83</v>
       </c>
       <c r="O100" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -9718,13 +9718,13 @@
         <v>5</v>
       </c>
       <c r="R100" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T100" t="n">
-        <v>38</v>
+        <v>264</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9802,22 +9802,22 @@
         <v>60</v>
       </c>
       <c r="O101" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R101" t="n">
-        <v>30</v>
+        <v>357</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
       </c>
       <c r="T101" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,25 +9892,25 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O102" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="P102" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="S102" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T102" t="n">
-        <v>347</v>
+        <v>208</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,22 +9985,22 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O103" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R103" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S103" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T103" t="n">
         <v>191</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/23/2026 22:07 MDT</t>
+          <t>8/23/2026 23:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,25 +10078,25 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O104" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Q104" t="n">
         <v>2</v>
       </c>
       <c r="R104" t="n">
-        <v>47</v>
+        <v>338</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T104" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O105" t="n">
         <v>49</v>
@@ -10180,16 +10180,16 @@
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T105" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10264,25 +10264,25 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O106" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R106" t="n">
-        <v>352</v>
+        <v>262</v>
       </c>
       <c r="S106" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T106" t="n">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/23/2026 22:06 MDT</t>
+          <t>8/23/2026 23:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O107" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T107" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10453,22 +10453,22 @@
         <v>68</v>
       </c>
       <c r="O108" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R108" t="n">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="S108" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T108" t="n">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O109" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="S109" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T109" t="n">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,25 +10636,25 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O110" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>350</v>
+        <v>139</v>
       </c>
       <c r="S110" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T110" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,25 +10729,25 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="O111" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P111" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R111" t="n">
-        <v>302</v>
+        <v>154</v>
       </c>
       <c r="S111" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="T111" t="n">
-        <v>342</v>
+        <v>201</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/23/2026 22:05 MDT</t>
+          <t>8/23/2026 23:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10825,22 +10825,22 @@
         <v>71</v>
       </c>
       <c r="O112" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T112" t="n">
-        <v>310</v>
+        <v>14</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/23/2026 22:04 MDT</t>
+          <t>8/23/2026 23:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/23/2026 22:04 MDT</t>
+          <t>8/23/2026 23:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/23/2026 22:04 MDT</t>
+          <t>8/23/2026 23:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,25 +10915,25 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O113" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T113" t="n">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/23/2026 22:04 MDT</t>
+          <t>8/23/2026 23:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/23/2026 22:04 MDT</t>
+          <t>8/23/2026 23:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/23/2026 22:04 MDT</t>
+          <t>8/23/2026 23:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11011,22 +11011,22 @@
         <v>68</v>
       </c>
       <c r="O114" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T114" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O115" t="n">
         <v>42</v>
@@ -11110,16 +11110,16 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>351</v>
+        <v>58</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T115" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O116" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -11206,13 +11206,13 @@
         <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="S116" t="n">
         <v>9</v>
       </c>
       <c r="T116" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O117" t="n">
         <v>27</v>
@@ -11296,16 +11296,16 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R117" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="S117" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="T117" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,25 +11380,25 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O118" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T118" t="n">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,25 +11473,25 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O119" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R119" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="S119" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T119" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,25 +11566,25 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O120" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T120" t="n">
-        <v>93</v>
+        <v>239</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/23/2026 22:03 MDT</t>
+          <t>8/23/2026 23:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,25 +11659,25 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O121" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R121" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T121" t="n">
-        <v>35</v>
+        <v>348</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,25 +11752,25 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O122" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R122" t="n">
+        <v>246</v>
+      </c>
+      <c r="S122" t="n">
+        <v>20</v>
+      </c>
+      <c r="T122" t="n">
         <v>245</v>
-      </c>
-      <c r="S122" t="n">
-        <v>18</v>
-      </c>
-      <c r="T122" t="n">
-        <v>251</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11845,25 +11845,25 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O123" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R123" t="n">
-        <v>34</v>
+        <v>343</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T123" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/23/2026 22:02 MDT</t>
+          <t>8/23/2026 23:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O124" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>349</v>
+        <v>119</v>
       </c>
       <c r="S124" t="n">
         <v>2</v>
       </c>
       <c r="T124" t="n">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,10 +12031,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O125" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -12043,13 +12043,13 @@
         <v>5</v>
       </c>
       <c r="R125" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T125" t="n">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O126" t="n">
         <v>22</v>
@@ -12133,16 +12133,16 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T126" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O127" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="S127" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T127" t="n">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/23/2026 22:01 MDT</t>
+          <t>8/23/2026 23:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12310,25 +12310,25 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O128" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R128" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S128" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,25 +12403,25 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O129" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,25 +12496,25 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O130" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>263</v>
+        <v>69</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
       </c>
       <c r="T130" t="n">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,25 +12589,25 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O131" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" t="n">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="S131" t="n">
         <v>3</v>
       </c>
       <c r="T131" t="n">
-        <v>346</v>
+        <v>88</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O132" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
@@ -12694,13 +12694,13 @@
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>314</v>
+        <v>56</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>234</v>
+        <v>111</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,10 +12775,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O133" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -12787,16 +12787,16 @@
         <v>9</v>
       </c>
       <c r="R133" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="S133" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T133" t="n">
         <v>5</v>
       </c>
       <c r="U133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O134" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -12886,10 +12886,10 @@
         <v>13</v>
       </c>
       <c r="T134" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U134" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12964,7 +12964,7 @@
         <v>73</v>
       </c>
       <c r="O135" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -12979,10 +12979,10 @@
         <v>14</v>
       </c>
       <c r="T135" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="U135" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,28 +13054,28 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O136" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R136" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="S136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T136" t="n">
         <v>51</v>
       </c>
       <c r="U136" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/23/2026 22:49 MDT</t>
+          <t>8/23/2026 23:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/23/2026 22:49 MDT</t>
+          <t>8/23/2026 23:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O137" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -13168,7 +13168,7 @@
         <v>60</v>
       </c>
       <c r="U137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/23/2026 22:59 MDT</t>
+          <t>8/23/2026 23:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/23/2026 22:59 MDT</t>
+          <t>8/23/2026 23:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13258,10 +13258,10 @@
         <v>17</v>
       </c>
       <c r="T138" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U138" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/23/2026 22:48 MDT</t>
+          <t>8/23/2026 23:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/23/2026 22:48 MDT</t>
+          <t>8/23/2026 23:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,28 +13333,28 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O139" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R139" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T139" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U139" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/23/2026 22:59 MDT</t>
+          <t>8/23/2026 23:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/23/2026 22:59 MDT</t>
+          <t>8/23/2026 23:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,28 +13426,28 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O140" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R140" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="S140" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="T140" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U140" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/23/2026 22:48 MDT</t>
+          <t>8/23/2026 23:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/23/2026 22:48 MDT</t>
+          <t>8/23/2026 23:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O141" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -13540,7 +13540,7 @@
         <v>69</v>
       </c>
       <c r="U141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,28 +13612,28 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O142" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R142" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="S142" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T142" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="U142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,10 +13705,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O143" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -13717,16 +13717,16 @@
         <v>6</v>
       </c>
       <c r="R143" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="S143" t="n">
+        <v>13</v>
+      </c>
+      <c r="T143" t="n">
+        <v>38</v>
+      </c>
+      <c r="U143" t="n">
         <v>14</v>
-      </c>
-      <c r="T143" t="n">
-        <v>34</v>
-      </c>
-      <c r="U143" t="n">
-        <v>17</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/23/2026 22:48 MDT</t>
+          <t>8/23/2026 23:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/23/2026 22:48 MDT</t>
+          <t>8/23/2026 23:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13801,25 +13801,25 @@
         <v>80</v>
       </c>
       <c r="O144" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R144" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T144" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="U144" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13891,28 +13891,28 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O145" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R145" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="S145" t="n">
         <v>18</v>
       </c>
       <c r="T145" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="U145" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O146" t="n">
         <v>37</v>
@@ -14002,10 +14002,10 @@
         <v>7</v>
       </c>
       <c r="T146" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="U146" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,28 +14077,28 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O147" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R147" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="S147" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="T147" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="U147" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/23/2026 22:49 MDT</t>
+          <t>8/23/2026 23:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/23/2026 22:49 MDT</t>
+          <t>8/23/2026 23:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O148" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14188,10 +14188,10 @@
         <v>8</v>
       </c>
       <c r="T148" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="U148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/23/2026 22:59 MDT</t>
+          <t>8/23/2026 23:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/23/2026 22:59 MDT</t>
+          <t>8/23/2026 23:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14263,10 +14263,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O149" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -14275,13 +14275,13 @@
         <v>2</v>
       </c>
       <c r="R149" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>7</v>
       </c>
       <c r="T149" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="U149" t="n">
         <v>2</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/23/2026 22:57 MDT</t>
+          <t>8/23/2026 23:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/23/2026 22:57 MDT</t>
+          <t>8/23/2026 23:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O150" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -14368,16 +14368,16 @@
         <v>3</v>
       </c>
       <c r="R150" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>9</v>
       </c>
       <c r="T150" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="U150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,28 +14449,28 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O151" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R151" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T151" t="n">
         <v>49</v>
       </c>
       <c r="U151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,28 +14542,28 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O152" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R152" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T152" t="n">
         <v>57</v>
       </c>
       <c r="U152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,28 +14635,28 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O153" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R153" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="S153" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T153" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="U153" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/23/2026 22:53 MDT</t>
+          <t>8/23/2026 23:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O154" t="n">
         <v>32</v>
@@ -14740,16 +14740,16 @@
         <v>8</v>
       </c>
       <c r="R154" t="n">
-        <v>30</v>
+        <v>350</v>
       </c>
       <c r="S154" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T154" t="n">
         <v>54</v>
       </c>
       <c r="U154" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/23/2026 22:52 MDT</t>
+          <t>8/23/2026 23:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14821,28 +14821,28 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O155" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R155" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="S155" t="n">
+        <v>14</v>
+      </c>
+      <c r="T155" t="n">
+        <v>35</v>
+      </c>
+      <c r="U155" t="n">
         <v>13</v>
-      </c>
-      <c r="T155" t="n">
-        <v>33</v>
-      </c>
-      <c r="U155" t="n">
-        <v>16</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/23/2026 22:47 MDT</t>
+          <t>8/23/2026 23:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/23/2026 22:47 MDT</t>
+          <t>8/23/2026 23:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14914,10 +14914,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O156" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -14932,10 +14932,10 @@
         <v>13</v>
       </c>
       <c r="T156" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/23/2026 22:49 MDT</t>
+          <t>8/23/2026 23:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/23/2026 22:49 MDT</t>
+          <t>8/23/2026 23:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O157" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15019,7 +15019,7 @@
         <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -15028,7 +15028,7 @@
         <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/23/2026 22:00 MDT</t>
+          <t>8/23/2026 23:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/23/2026 23:00 MDT</t>
+          <t>8/24/2026 0:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/23/2026 22:50 MDT</t>
+          <t>8/23/2026 23:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O158" t="n">
         <v>41</v>
@@ -15112,16 +15112,16 @@
         <v>3</v>
       </c>
       <c r="R158" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T158" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="U158" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V158" t="inlineStr">
         <is>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/24/2026 2:42 MDT</t>
+          <t>8/24/2026 3:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/24/2026 2:42 MDT</t>
+          <t>8/24/2026 3:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/24/2026 2:42 MDT</t>
+          <t>8/24/2026 3:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O2" t="n">
         <v>64</v>
       </c>
-      <c r="O2" t="n">
-        <v>62</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>56</v>
+        <v>340</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/24/2026 2:42 MDT</t>
+          <t>8/24/2026 3:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/24/2026 2:42 MDT</t>
+          <t>8/24/2026 3:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/24/2026 2:42 MDT</t>
+          <t>8/24/2026 3:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -697,13 +697,13 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>350</v>
+        <v>29</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         <v>32</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O5" t="n">
         <v>62</v>
@@ -883,13 +883,13 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -967,22 +967,22 @@
         <v>56</v>
       </c>
       <c r="O6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/24/2026 2:41 MDT</t>
+          <t>8/24/2026 3:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O7" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1069,13 +1069,13 @@
         <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/24/2026 2:40 MDT</t>
+          <t>8/24/2026 3:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/24/2026 2:40 MDT</t>
+          <t>8/24/2026 3:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/24/2026 2:40 MDT</t>
+          <t>8/24/2026 3:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>31</v>
+        <v>346</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>170</v>
+        <v>348</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/24/2026 2:40 MDT</t>
+          <t>8/24/2026 3:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/24/2026 2:40 MDT</t>
+          <t>8/24/2026 3:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/24/2026 2:40 MDT</t>
+          <t>8/24/2026 3:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1246,7 +1246,7 @@
         <v>78</v>
       </c>
       <c r="O9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="S9" t="n">
         <v>17</v>
       </c>
       <c r="T9" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1348,13 +1348,13 @@
         <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>347</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,25 +1522,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/24/2026 2:39 MDT</t>
+          <t>8/24/2026 3:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O14" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>98</v>
+        <v>157</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O15" t="n">
         <v>46</v>
@@ -1810,16 +1810,16 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,25 +1894,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O16" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T16" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1990,22 +1990,22 @@
         <v>62</v>
       </c>
       <c r="O17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>341</v>
+        <v>262</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2173,25 +2173,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O19" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>342</v>
+        <v>292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2269,22 +2269,22 @@
         <v>53</v>
       </c>
       <c r="O20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/24/2026 2:38 MDT</t>
+          <t>8/24/2026 3:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2371,13 +2371,13 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,25 +2452,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O22" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2548,19 +2548,19 @@
         <v>71</v>
       </c>
       <c r="O23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T23" t="n">
         <v>12</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2638,25 +2638,25 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O24" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,25 +2731,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,25 +2824,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O26" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>198</v>
+        <v>110</v>
       </c>
       <c r="S26" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>227</v>
+        <v>116</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O27" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3022,13 +3022,13 @@
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/24/2026 2:37 MDT</t>
+          <t>8/24/2026 3:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T29" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/24/2026 2:36 MDT</t>
+          <t>8/24/2026 3:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/24/2026 2:36 MDT</t>
+          <t>8/24/2026 3:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/24/2026 2:36 MDT</t>
+          <t>8/24/2026 3:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,25 +3196,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O30" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>92</v>
+        <v>270</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/24/2026 2:36 MDT</t>
+          <t>8/24/2026 3:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/24/2026 2:36 MDT</t>
+          <t>8/24/2026 3:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/24/2026 2:36 MDT</t>
+          <t>8/24/2026 3:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T31" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/24/2026 2:35 MDT</t>
+          <t>8/24/2026 3:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/24/2026 2:35 MDT</t>
+          <t>8/24/2026 3:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/24/2026 2:35 MDT</t>
+          <t>8/24/2026 3:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O32" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -3394,13 +3394,13 @@
         <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S32" t="n">
         <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/24/2026 2:35 MDT</t>
+          <t>8/24/2026 3:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/24/2026 2:35 MDT</t>
+          <t>8/24/2026 3:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/24/2026 2:35 MDT</t>
+          <t>8/24/2026 3:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O33" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3487,13 +3487,13 @@
         <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T33" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O34" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O35" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>327</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>14</v>
+        <v>311</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3754,25 +3754,25 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O36" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/24/2026 2:34 MDT</t>
+          <t>8/24/2026 3:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,25 +3847,25 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O37" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S37" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="T37" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3949,16 +3949,16 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R38" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T38" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,25 +4033,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O39" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O40" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="S40" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="T40" t="n">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -4231,13 +4231,13 @@
         <v>11</v>
       </c>
       <c r="R41" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T41" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,16 +4312,16 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O42" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>98</v>
@@ -4330,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/24/2026 2:33 MDT</t>
+          <t>8/24/2026 3:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4417,13 +4417,13 @@
         <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T43" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/24/2026 2:32 MDT</t>
+          <t>8/24/2026 3:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/24/2026 2:32 MDT</t>
+          <t>8/24/2026 3:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/24/2026 2:32 MDT</t>
+          <t>8/24/2026 3:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O44" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>10</v>
+        <v>256</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/24/2026 2:28 MDT</t>
+          <t>8/24/2026 3:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/24/2026 2:28 MDT</t>
+          <t>8/24/2026 3:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/24/2026 2:28 MDT</t>
+          <t>8/24/2026 3:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O45" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4603,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>232</v>
+        <v>65</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T45" t="n">
-        <v>52</v>
+        <v>329</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4687,22 +4687,22 @@
         <v>68</v>
       </c>
       <c r="O46" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>237</v>
+      </c>
+      <c r="S46" t="n">
         <v>5</v>
       </c>
-      <c r="R46" t="n">
-        <v>246</v>
-      </c>
-      <c r="S46" t="n">
-        <v>6</v>
-      </c>
       <c r="T46" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O47" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4789,13 +4789,13 @@
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/24/2026 2:27 MDT</t>
+          <t>8/24/2026 3:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4870,25 +4870,25 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O48" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T48" t="n">
-        <v>39</v>
+        <v>343</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4963,25 +4963,25 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O49" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="T49" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,25 +5056,25 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R50" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/24/2026 2:26 MDT</t>
+          <t>8/24/2026 3:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O51" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/24/2026 2:25 MDT</t>
+          <t>8/24/2026 3:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/24/2026 2:25 MDT</t>
+          <t>8/24/2026 3:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/24/2026 2:25 MDT</t>
+          <t>8/24/2026 3:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O52" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>184</v>
+        <v>247</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/24/2026 2:24 MDT</t>
+          <t>8/24/2026 3:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/24/2026 2:24 MDT</t>
+          <t>8/24/2026 3:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/24/2026 2:24 MDT</t>
+          <t>8/24/2026 3:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5335,25 +5335,25 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O53" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>51</v>
+        <v>283</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,25 +5428,25 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O54" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R54" t="n">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="S54" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="T54" t="n">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>341</v>
+        <v>25</v>
       </c>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O56" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R56" t="n">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="S56" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T56" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/24/2026 2:23 MDT</t>
+          <t>8/24/2026 3:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,25 +5707,25 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O57" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>273</v>
+        <v>70</v>
       </c>
       <c r="S57" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T57" t="n">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/24/2026 2:22 MDT</t>
+          <t>8/24/2026 3:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/24/2026 2:22 MDT</t>
+          <t>8/24/2026 3:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/24/2026 2:22 MDT</t>
+          <t>8/24/2026 3:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,25 +5800,25 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O58" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q58" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R58" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
       </c>
       <c r="T58" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/24/2026 2:22 MDT</t>
+          <t>8/24/2026 3:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/24/2026 2:22 MDT</t>
+          <t>8/24/2026 3:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/24/2026 2:22 MDT</t>
+          <t>8/24/2026 3:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5893,25 +5893,25 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O59" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="n">
-        <v>18</v>
+        <v>343</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/24/2026 2:20 MDT</t>
+          <t>8/24/2026 3:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/24/2026 2:20 MDT</t>
+          <t>8/24/2026 3:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/24/2026 2:20 MDT</t>
+          <t>8/24/2026 3:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5986,25 +5986,25 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O60" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R60" t="n">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T60" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/24/2026 2:20 MDT</t>
+          <t>8/24/2026 3:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/24/2026 2:20 MDT</t>
+          <t>8/24/2026 3:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/24/2026 2:20 MDT</t>
+          <t>8/24/2026 3:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -6091,13 +6091,13 @@
         <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>354</v>
+        <v>14</v>
       </c>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T61" t="n">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="O62" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O63" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R63" t="n">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T63" t="n">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,25 +6358,25 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O64" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/24/2026 2:19 MDT</t>
+          <t>8/24/2026 3:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6451,25 +6451,25 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O65" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/24/2026 2:17 MDT</t>
+          <t>8/24/2026 3:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/24/2026 2:17 MDT</t>
+          <t>8/24/2026 3:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/24/2026 2:17 MDT</t>
+          <t>8/24/2026 3:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6547,22 +6547,22 @@
         <v>82</v>
       </c>
       <c r="O66" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R66" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T66" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,25 +6637,25 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O67" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O68" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T68" t="n">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O69" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6916,25 +6916,25 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O70" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="S70" t="n">
         <v>17</v>
       </c>
       <c r="T70" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/24/2026 2:16 MDT</t>
+          <t>8/24/2026 3:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,25 +7009,25 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O71" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>308</v>
+        <v>7</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/24/2026 2:15 MDT</t>
+          <t>8/24/2026 3:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/24/2026 2:15 MDT</t>
+          <t>8/24/2026 3:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/24/2026 2:15 MDT</t>
+          <t>8/24/2026 3:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,25 +7102,25 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O72" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T72" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,25 +7195,25 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O73" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O74" t="n">
         <v>28</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R74" t="n">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T74" t="n">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O75" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>126</v>
+        <v>294</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T75" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>278</v>
+        <v>190</v>
       </c>
       <c r="S76" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,25 +7567,25 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O77" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R77" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="S77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T77" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/24/2026 2:14 MDT</t>
+          <t>8/24/2026 3:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7663,7 +7663,7 @@
         <v>65</v>
       </c>
       <c r="O78" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -7672,13 +7672,13 @@
         <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
       </c>
       <c r="T78" t="n">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7756,22 +7756,22 @@
         <v>61</v>
       </c>
       <c r="O79" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R79" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T79" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O80" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R80" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
       </c>
       <c r="T80" t="n">
-        <v>205</v>
+        <v>355</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7939,25 +7939,25 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O81" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T81" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,22 +8032,22 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O82" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T82" t="n">
         <v>243</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/24/2026 2:13 MDT</t>
+          <t>8/24/2026 3:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O83" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
       </c>
       <c r="T83" t="n">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/24/2026 2:12 MDT</t>
+          <t>8/24/2026 3:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/24/2026 2:12 MDT</t>
+          <t>8/24/2026 3:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/24/2026 2:12 MDT</t>
+          <t>8/24/2026 3:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O84" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,25 +8311,25 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O85" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R85" t="n">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="S85" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="T85" t="n">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O86" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T86" t="n">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O87" t="n">
         <v>28</v>
@@ -8506,16 +8506,16 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R87" t="n">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="S87" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T87" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="O88" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
@@ -8602,13 +8602,13 @@
         <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T88" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O89" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T89" t="n">
-        <v>319</v>
+        <v>41</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/24/2026 2:11 MDT</t>
+          <t>8/24/2026 3:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,25 +8776,25 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O90" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T90" t="n">
-        <v>38</v>
+        <v>306</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/24/2026 2:09 MDT</t>
+          <t>8/24/2026 3:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/24/2026 2:09 MDT</t>
+          <t>8/24/2026 3:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/24/2026 2:09 MDT</t>
+          <t>8/24/2026 3:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8869,25 +8869,25 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="O91" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R91" t="n">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="S91" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T91" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/24/2026 2:09 MDT</t>
+          <t>8/24/2026 3:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/24/2026 2:09 MDT</t>
+          <t>8/24/2026 3:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/24/2026 2:09 MDT</t>
+          <t>8/24/2026 3:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8962,25 +8962,25 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O92" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>345</v>
+        <v>281</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T92" t="n">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O93" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
         <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,25 +9148,25 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O94" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>43</v>
+        <v>301</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9241,25 +9241,25 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O95" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T95" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9334,25 +9334,25 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O96" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O97" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -9439,13 +9439,13 @@
         <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="S97" t="n">
         <v>2</v>
       </c>
       <c r="T97" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9532,13 +9532,13 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T98" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,25 +9613,25 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O99" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T99" t="n">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/24/2026 2:08 MDT</t>
+          <t>8/24/2026 3:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9709,22 +9709,22 @@
         <v>80</v>
       </c>
       <c r="O100" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R100" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T100" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9811,13 +9811,13 @@
         <v>3</v>
       </c>
       <c r="R101" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T101" t="n">
-        <v>19</v>
+        <v>339</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O102" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
@@ -9904,13 +9904,13 @@
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="S102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T102" t="n">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O103" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R103" t="n">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="S103" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T103" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/24/2026 2:07 MDT</t>
+          <t>8/24/2026 3:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O104" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -10090,13 +10090,13 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>321</v>
+        <v>235</v>
       </c>
       <c r="S104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10174,22 +10174,22 @@
         <v>71</v>
       </c>
       <c r="O105" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="S105" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="T105" t="n">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O106" t="n">
         <v>36</v>
@@ -10273,16 +10273,16 @@
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R106" t="n">
-        <v>46</v>
+        <v>268</v>
       </c>
       <c r="S106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T106" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/24/2026 2:06 MDT</t>
+          <t>8/24/2026 3:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,25 +10357,25 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="O107" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R107" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T107" t="n">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10450,25 +10450,25 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="O108" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R108" t="n">
-        <v>185</v>
+        <v>351</v>
       </c>
       <c r="S108" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T108" t="n">
-        <v>17</v>
+        <v>351</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O109" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R109" t="n">
-        <v>29</v>
+        <v>348</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T109" t="n">
-        <v>58</v>
+        <v>347</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,25 +10636,25 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O110" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="S110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T110" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,25 +10729,25 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O111" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R111" t="n">
-        <v>70</v>
+        <v>351</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T111" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/24/2026 2:05 MDT</t>
+          <t>8/24/2026 3:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O112" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T112" t="n">
-        <v>4</v>
+        <v>254</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/24/2026 2:04 MDT</t>
+          <t>8/24/2026 3:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/24/2026 2:04 MDT</t>
+          <t>8/24/2026 3:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/24/2026 2:04 MDT</t>
+          <t>8/24/2026 3:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O113" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -10927,13 +10927,13 @@
         <v>2</v>
       </c>
       <c r="R113" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T113" t="n">
-        <v>276</v>
+        <v>33</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/24/2026 2:04 MDT</t>
+          <t>8/24/2026 3:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/24/2026 2:04 MDT</t>
+          <t>8/24/2026 3:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/24/2026 2:04 MDT</t>
+          <t>8/24/2026 3:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11008,25 +11008,25 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O114" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T114" t="n">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,25 +11101,25 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O115" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="S115" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T115" t="n">
-        <v>7</v>
+        <v>337</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,25 +11194,25 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R116" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T116" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11287,25 +11287,25 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O117" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R117" t="n">
-        <v>358</v>
+        <v>2</v>
       </c>
       <c r="S117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T117" t="n">
-        <v>353</v>
+        <v>5</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,25 +11380,25 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O118" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="S118" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T118" t="n">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11476,22 +11476,22 @@
         <v>79</v>
       </c>
       <c r="O119" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R119" t="n">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="S119" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T119" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O120" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>2</v>
       </c>
       <c r="R120" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="S120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T120" t="n">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/24/2026 2:03 MDT</t>
+          <t>8/24/2026 3:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11662,22 +11662,22 @@
         <v>66</v>
       </c>
       <c r="O121" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S121" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T121" t="n">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,25 +11752,25 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O122" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>85</v>
+      </c>
+      <c r="S122" t="n">
         <v>10</v>
       </c>
-      <c r="R122" t="n">
-        <v>295</v>
-      </c>
-      <c r="S122" t="n">
-        <v>24</v>
-      </c>
       <c r="T122" t="n">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11848,7 +11848,7 @@
         <v>57</v>
       </c>
       <c r="O123" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
@@ -11857,13 +11857,13 @@
         <v>3</v>
       </c>
       <c r="R123" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T123" t="n">
-        <v>11</v>
+        <v>352</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/24/2026 2:02 MDT</t>
+          <t>8/24/2026 3:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11941,7 +11941,7 @@
         <v>54</v>
       </c>
       <c r="O124" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>100</v>
+        <v>359</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12040,16 +12040,16 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R125" t="n">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="S125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T125" t="n">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O126" t="n">
         <v>21</v>
@@ -12133,16 +12133,16 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R126" t="n">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="S126" t="n">
         <v>6</v>
       </c>
       <c r="T126" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O127" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R127" t="n">
-        <v>114</v>
+        <v>315</v>
       </c>
       <c r="S127" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="T127" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/24/2026 2:01 MDT</t>
+          <t>8/24/2026 3:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12313,22 +12313,22 @@
         <v>79</v>
       </c>
       <c r="O128" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R128" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="S128" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T128" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,25 +12403,25 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O129" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="S129" t="n">
         <v>7</v>
       </c>
       <c r="T129" t="n">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,25 +12496,25 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O130" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R130" t="n">
-        <v>314</v>
+        <v>230</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T130" t="n">
-        <v>336</v>
+        <v>224</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O131" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -12601,13 +12601,13 @@
         <v>1</v>
       </c>
       <c r="R131" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="S131" t="n">
         <v>3</v>
       </c>
       <c r="T131" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,25 +12682,25 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O132" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T132" t="n">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O133" t="n">
         <v>26</v>
@@ -12787,7 +12787,7 @@
         <v>10</v>
       </c>
       <c r="R133" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="S133" t="n">
         <v>17</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O134" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -12880,13 +12880,13 @@
         <v>5</v>
       </c>
       <c r="R134" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="S134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T134" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12964,7 +12964,7 @@
         <v>71</v>
       </c>
       <c r="O135" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
         <v>13</v>
       </c>
       <c r="T135" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,25 +13054,25 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O136" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T136" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/24/2026 2:49 MDT</t>
+          <t>8/24/2026 3:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/24/2026 2:49 MDT</t>
+          <t>8/24/2026 3:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13150,7 +13150,7 @@
         <v>59</v>
       </c>
       <c r="O137" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
         <v>9</v>
       </c>
       <c r="T137" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/24/2026 2:59 MDT</t>
+          <t>8/24/2026 3:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/24/2026 2:59 MDT</t>
+          <t>8/24/2026 3:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13240,25 +13240,25 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O138" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R138" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="S138" t="n">
         <v>11</v>
       </c>
       <c r="T138" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/24/2026 2:48 MDT</t>
+          <t>8/24/2026 3:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/24/2026 2:48 MDT</t>
+          <t>8/24/2026 3:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O139" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -13351,7 +13351,7 @@
         <v>21</v>
       </c>
       <c r="T139" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/24/2026 2:59 MDT</t>
+          <t>8/24/2026 3:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/24/2026 2:59 MDT</t>
+          <t>8/24/2026 3:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,25 +13426,25 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O140" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R140" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="S140" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="T140" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/24/2026 2:48 MDT</t>
+          <t>8/24/2026 3:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/24/2026 2:48 MDT</t>
+          <t>8/24/2026 3:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,25 +13519,25 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O141" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R141" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="S141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T141" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O142" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -13630,7 +13630,7 @@
         <v>7</v>
       </c>
       <c r="T142" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,10 +13705,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O143" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -13717,13 +13717,13 @@
         <v>5</v>
       </c>
       <c r="R143" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T143" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/24/2026 2:48 MDT</t>
+          <t>8/24/2026 3:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/24/2026 2:48 MDT</t>
+          <t>8/24/2026 3:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13801,22 +13801,22 @@
         <v>75</v>
       </c>
       <c r="O144" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T144" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13903,13 +13903,13 @@
         <v>8</v>
       </c>
       <c r="R145" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="S145" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T145" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13984,10 +13984,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O146" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13996,13 +13996,13 @@
         <v>3</v>
       </c>
       <c r="R146" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="S146" t="n">
         <v>6</v>
       </c>
       <c r="T146" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,25 +14077,25 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O147" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R147" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="S147" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T147" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/24/2026 2:49 MDT</t>
+          <t>8/24/2026 3:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/24/2026 2:49 MDT</t>
+          <t>8/24/2026 3:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O148" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14188,7 +14188,7 @@
         <v>7</v>
       </c>
       <c r="T148" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/24/2026 2:59 MDT</t>
+          <t>8/24/2026 3:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/24/2026 2:59 MDT</t>
+          <t>8/24/2026 3:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14263,10 +14263,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O149" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -14275,13 +14275,13 @@
         <v>2</v>
       </c>
       <c r="R149" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="S149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T149" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/24/2026 2:57 MDT</t>
+          <t>8/24/2026 3:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/24/2026 2:57 MDT</t>
+          <t>8/24/2026 3:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O150" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -14371,10 +14371,10 @@
         <v>350</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T150" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,10 +14449,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O151" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -14461,13 +14461,13 @@
         <v>2</v>
       </c>
       <c r="R151" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>3</v>
       </c>
       <c r="T151" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14545,7 +14545,7 @@
         <v>59</v>
       </c>
       <c r="O152" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -14560,7 +14560,7 @@
         <v>7</v>
       </c>
       <c r="T152" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O153" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -14647,13 +14647,13 @@
         <v>5</v>
       </c>
       <c r="R153" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T153" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/24/2026 2:53 MDT</t>
+          <t>8/24/2026 3:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,25 +14728,25 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O154" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R154" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="S154" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T154" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/24/2026 2:52 MDT</t>
+          <t>8/24/2026 3:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O155" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -14833,13 +14833,13 @@
         <v>6</v>
       </c>
       <c r="R155" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="S155" t="n">
         <v>13</v>
       </c>
       <c r="T155" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/24/2026 2:47 MDT</t>
+          <t>8/24/2026 3:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/24/2026 2:47 MDT</t>
+          <t>8/24/2026 3:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14914,25 +14914,25 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O156" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R156" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="S156" t="n">
         <v>13</v>
       </c>
       <c r="T156" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/24/2026 2:49 MDT</t>
+          <t>8/24/2026 3:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/24/2026 2:49 MDT</t>
+          <t>8/24/2026 3:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O157" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15019,13 +15019,13 @@
         <v>2</v>
       </c>
       <c r="R157" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="S157" t="n">
         <v>3</v>
       </c>
       <c r="T157" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/24/2026 2:00 MDT</t>
+          <t>8/24/2026 3:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/24/2026 3:00 MDT</t>
+          <t>8/24/2026 4:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/24/2026 2:50 MDT</t>
+          <t>8/24/2026 3:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15103,7 +15103,7 @@
         <v>61</v>
       </c>
       <c r="O158" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -15112,13 +15112,13 @@
         <v>3</v>
       </c>
       <c r="R158" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="S158" t="n">
         <v>9</v>
       </c>
       <c r="T158" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/24/2026 4:42 MDT</t>
+          <t>8/24/2026 5:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/24/2026 4:42 MDT</t>
+          <t>8/24/2026 5:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/24/2026 4:42 MDT</t>
+          <t>8/24/2026 5:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O2" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>353</v>
+        <v>28</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/24/2026 4:42 MDT</t>
+          <t>8/24/2026 5:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/24/2026 4:42 MDT</t>
+          <t>8/24/2026 5:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/24/2026 4:42 MDT</t>
+          <t>8/24/2026 5:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="O3" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>40</v>
+        <v>318</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O5" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -883,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,25 +964,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O6" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/24/2026 4:41 MDT</t>
+          <t>8/24/2026 5:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,25 +1057,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>293</v>
+        <v>182</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/24/2026 4:40 MDT</t>
+          <t>8/24/2026 5:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/24/2026 4:40 MDT</t>
+          <t>8/24/2026 5:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/24/2026 4:40 MDT</t>
+          <t>8/24/2026 5:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>15</v>
+        <v>298</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/24/2026 4:40 MDT</t>
+          <t>8/24/2026 5:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/24/2026 4:40 MDT</t>
+          <t>8/24/2026 5:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/24/2026 4:40 MDT</t>
+          <t>8/24/2026 5:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T9" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O11" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>92</v>
+      </c>
+      <c r="S11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" t="n">
-        <v>330</v>
-      </c>
-      <c r="S11" t="n">
-        <v>13</v>
-      </c>
       <c r="T11" t="n">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="O12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/24/2026 4:39 MDT</t>
+          <t>8/24/2026 5:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,25 +1615,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O13" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1711,22 +1711,22 @@
         <v>62</v>
       </c>
       <c r="O14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,25 +1894,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O16" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O17" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,13 +1999,13 @@
         <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>62</v>
       </c>
       <c r="O18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="S18" t="n">
         <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2176,22 +2176,22 @@
         <v>62</v>
       </c>
       <c r="O19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,25 +2266,25 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>59</v>
+      </c>
+      <c r="O20" t="n">
         <v>54</v>
       </c>
-      <c r="O20" t="n">
-        <v>64</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/24/2026 4:38 MDT</t>
+          <t>8/24/2026 5:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2362,7 +2362,7 @@
         <v>58</v>
       </c>
       <c r="O21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2371,13 +2371,13 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>271</v>
+        <v>218</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2455,22 +2455,22 @@
         <v>50</v>
       </c>
       <c r="O22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2557,13 +2557,13 @@
         <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2641,22 +2641,22 @@
         <v>65</v>
       </c>
       <c r="O24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,25 +2731,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="S25" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,25 +2824,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T26" t="n">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2920,22 +2920,22 @@
         <v>69</v>
       </c>
       <c r="O27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T27" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3013,22 +3013,22 @@
         <v>64</v>
       </c>
       <c r="O28" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/24/2026 4:37 MDT</t>
+          <t>8/24/2026 5:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O29" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/24/2026 4:36 MDT</t>
+          <t>8/24/2026 5:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/24/2026 4:36 MDT</t>
+          <t>8/24/2026 5:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/24/2026 4:36 MDT</t>
+          <t>8/24/2026 5:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O30" t="n">
         <v>45</v>
@@ -3205,16 +3205,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/24/2026 4:36 MDT</t>
+          <t>8/24/2026 5:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/24/2026 4:36 MDT</t>
+          <t>8/24/2026 5:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/24/2026 4:36 MDT</t>
+          <t>8/24/2026 5:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3292,22 +3292,22 @@
         <v>74</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R31" t="n">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
       </c>
       <c r="T31" t="n">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/24/2026 4:35 MDT</t>
+          <t>8/24/2026 5:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/24/2026 4:35 MDT</t>
+          <t>8/24/2026 5:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/24/2026 4:35 MDT</t>
+          <t>8/24/2026 5:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3385,22 +3385,22 @@
         <v>55</v>
       </c>
       <c r="O32" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/24/2026 4:35 MDT</t>
+          <t>8/24/2026 5:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/24/2026 4:35 MDT</t>
+          <t>8/24/2026 5:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/24/2026 4:35 MDT</t>
+          <t>8/24/2026 5:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,22 +3475,22 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O33" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
         <v>144</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O34" t="n">
         <v>63</v>
@@ -3577,16 +3577,16 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O35" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3757,22 +3757,22 @@
         <v>73</v>
       </c>
       <c r="O36" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/24/2026 4:34 MDT</t>
+          <t>8/24/2026 5:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,19 +3847,19 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O37" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R37" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3943,22 +3943,22 @@
         <v>80</v>
       </c>
       <c r="O38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R38" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="S38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T38" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,25 +4033,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O39" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O40" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>22</v>
+        <v>309</v>
       </c>
       <c r="S40" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>303</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R41" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T41" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,25 +4312,25 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="O42" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/24/2026 4:33 MDT</t>
+          <t>8/24/2026 5:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O43" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -4417,10 +4417,10 @@
         <v>9</v>
       </c>
       <c r="R43" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T43" t="n">
         <v>225</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/24/2026 4:32 MDT</t>
+          <t>8/24/2026 5:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/24/2026 4:32 MDT</t>
+          <t>8/24/2026 5:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/24/2026 4:32 MDT</t>
+          <t>8/24/2026 5:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O44" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/24/2026 4:28 MDT</t>
+          <t>8/24/2026 5:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/24/2026 4:28 MDT</t>
+          <t>8/24/2026 5:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/24/2026 4:28 MDT</t>
+          <t>8/24/2026 5:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O45" t="n">
         <v>95</v>
@@ -4603,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4684,25 +4684,25 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O46" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R46" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T46" t="n">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4777,25 +4777,25 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O47" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
       </c>
       <c r="T47" t="n">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/24/2026 4:27 MDT</t>
+          <t>8/24/2026 5:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O48" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4882,13 +4882,13 @@
         <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>355</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4966,22 +4966,22 @@
         <v>87</v>
       </c>
       <c r="O49" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O50" t="n">
         <v>20</v>
@@ -5068,13 +5068,13 @@
         <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/24/2026 4:26 MDT</t>
+          <t>8/24/2026 5:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O51" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/24/2026 4:25 MDT</t>
+          <t>8/24/2026 5:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/24/2026 4:25 MDT</t>
+          <t>8/24/2026 5:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/24/2026 4:25 MDT</t>
+          <t>8/24/2026 5:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O52" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/24/2026 4:24 MDT</t>
+          <t>8/24/2026 5:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/24/2026 4:24 MDT</t>
+          <t>8/24/2026 5:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/24/2026 4:24 MDT</t>
+          <t>8/24/2026 5:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O53" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -5347,13 +5347,13 @@
         <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O54" t="n">
         <v>57</v>
@@ -5437,16 +5437,16 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R54" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T54" t="n">
-        <v>156</v>
+        <v>66</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O55" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -5533,13 +5533,13 @@
         <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>332</v>
+        <v>253</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="n">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O56" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="S56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T56" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/24/2026 4:23 MDT</t>
+          <t>8/24/2026 5:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,25 +5707,25 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O57" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R57" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="S57" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="T57" t="n">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/24/2026 4:22 MDT</t>
+          <t>8/24/2026 5:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/24/2026 4:22 MDT</t>
+          <t>8/24/2026 5:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/24/2026 4:22 MDT</t>
+          <t>8/24/2026 5:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5803,22 +5803,22 @@
         <v>80</v>
       </c>
       <c r="O58" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T58" t="n">
-        <v>205</v>
+        <v>344</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/24/2026 4:22 MDT</t>
+          <t>8/24/2026 5:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/24/2026 4:22 MDT</t>
+          <t>8/24/2026 5:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/24/2026 4:22 MDT</t>
+          <t>8/24/2026 5:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5893,25 +5893,25 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O59" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="n">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/24/2026 4:20 MDT</t>
+          <t>8/24/2026 5:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/24/2026 4:20 MDT</t>
+          <t>8/24/2026 5:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/24/2026 4:20 MDT</t>
+          <t>8/24/2026 5:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5986,25 +5986,25 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="S60" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T60" t="n">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/24/2026 4:20 MDT</t>
+          <t>8/24/2026 5:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/24/2026 4:20 MDT</t>
+          <t>8/24/2026 5:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/24/2026 4:20 MDT</t>
+          <t>8/24/2026 5:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6079,25 +6079,25 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O61" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>343</v>
+        <v>24</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="n">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O62" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R62" t="n">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T62" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O63" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R63" t="n">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T63" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,25 +6358,25 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O64" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/24/2026 4:19 MDT</t>
+          <t>8/24/2026 5:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6454,22 +6454,22 @@
         <v>69</v>
       </c>
       <c r="O65" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>353</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/24/2026 4:17 MDT</t>
+          <t>8/24/2026 5:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/24/2026 4:17 MDT</t>
+          <t>8/24/2026 5:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/24/2026 4:17 MDT</t>
+          <t>8/24/2026 5:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O66" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -6556,13 +6556,13 @@
         <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T66" t="n">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O67" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -6649,13 +6649,13 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
       </c>
       <c r="T67" t="n">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O68" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="n">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O69" t="n">
         <v>56</v>
@@ -6835,13 +6835,13 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6919,22 +6919,22 @@
         <v>91</v>
       </c>
       <c r="O70" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/24/2026 4:16 MDT</t>
+          <t>8/24/2026 5:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O71" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -7021,13 +7021,13 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
       </c>
       <c r="T71" t="n">
-        <v>348</v>
+        <v>311</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/24/2026 4:15 MDT</t>
+          <t>8/24/2026 5:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/24/2026 4:15 MDT</t>
+          <t>8/24/2026 5:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/24/2026 4:15 MDT</t>
+          <t>8/24/2026 5:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7111,16 +7111,16 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T72" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O73" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -7207,13 +7207,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>325</v>
+        <v>66</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O74" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
@@ -7300,13 +7300,13 @@
         <v>6</v>
       </c>
       <c r="R74" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T74" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
+        <v>76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>72</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
         <v>75</v>
       </c>
-      <c r="O75" t="n">
-        <v>82</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>3</v>
-      </c>
-      <c r="R75" t="n">
-        <v>214</v>
-      </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T75" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O76" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,25 +7567,25 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O77" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="S77" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T77" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/24/2026 4:14 MDT</t>
+          <t>8/24/2026 5:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7663,22 +7663,22 @@
         <v>63</v>
       </c>
       <c r="O78" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="n">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7762,16 +7762,16 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R79" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O80" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T80" t="n">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O81" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -7951,13 +7951,13 @@
         <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,25 +8032,25 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R82" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
       </c>
       <c r="T82" t="n">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/24/2026 4:13 MDT</t>
+          <t>8/24/2026 5:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,25 +8125,25 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O83" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
       </c>
       <c r="T83" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/24/2026 4:12 MDT</t>
+          <t>8/24/2026 5:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/24/2026 4:12 MDT</t>
+          <t>8/24/2026 5:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/24/2026 4:12 MDT</t>
+          <t>8/24/2026 5:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8221,7 +8221,7 @@
         <v>59</v>
       </c>
       <c r="O84" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8314,22 +8314,22 @@
         <v>68</v>
       </c>
       <c r="O85" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>119</v>
+        <v>355</v>
       </c>
       <c r="S85" t="n">
         <v>9</v>
       </c>
       <c r="T85" t="n">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O86" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R86" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T86" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,25 +8497,25 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O87" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="S87" t="n">
         <v>13</v>
       </c>
       <c r="T87" t="n">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,25 +8590,25 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O88" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
       </c>
       <c r="T88" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O89" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T89" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/24/2026 4:11 MDT</t>
+          <t>8/24/2026 5:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O90" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
       </c>
       <c r="T90" t="n">
-        <v>321</v>
+        <v>167</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/24/2026 4:09 MDT</t>
+          <t>8/24/2026 5:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/24/2026 4:09 MDT</t>
+          <t>8/24/2026 5:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/24/2026 4:09 MDT</t>
+          <t>8/24/2026 5:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="O91" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -8881,13 +8881,13 @@
         <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="S91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T91" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/24/2026 4:09 MDT</t>
+          <t>8/24/2026 5:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/24/2026 4:09 MDT</t>
+          <t>8/24/2026 5:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/24/2026 4:09 MDT</t>
+          <t>8/24/2026 5:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8962,25 +8962,25 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O92" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
       </c>
       <c r="T92" t="n">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,25 +9055,25 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O93" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R93" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T93" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,25 +9148,25 @@
         </is>
       </c>
       <c r="N94" t="n">
+        <v>56</v>
+      </c>
+      <c r="O94" t="n">
         <v>60</v>
       </c>
-      <c r="O94" t="n">
-        <v>56</v>
-      </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
         <v>99</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T94" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9244,22 +9244,22 @@
         <v>64</v>
       </c>
       <c r="O95" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="S95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T95" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9334,25 +9334,25 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O96" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O97" t="n">
         <v>81</v>
@@ -9436,16 +9436,16 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T97" t="n">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9520,25 +9520,25 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O98" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T98" t="n">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,25 +9613,25 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O99" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T99" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/24/2026 4:08 MDT</t>
+          <t>8/24/2026 5:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9706,25 +9706,25 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O100" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T100" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9799,25 +9799,25 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O101" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>23</v>
+        <v>261</v>
       </c>
       <c r="S101" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O102" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
@@ -9904,13 +9904,13 @@
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>328</v>
+        <v>64</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O103" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R103" t="n">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="S103" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T103" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/24/2026 4:07 MDT</t>
+          <t>8/24/2026 5:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O104" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -10090,13 +10090,13 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="S104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T104" t="n">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10171,25 +10171,25 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O105" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R105" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="S105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T105" t="n">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10264,25 +10264,25 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O106" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R106" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="S106" t="n">
         <v>16</v>
       </c>
       <c r="T106" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/24/2026 4:06 MDT</t>
+          <t>8/24/2026 5:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10360,7 +10360,7 @@
         <v>55</v>
       </c>
       <c r="O107" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T107" t="n">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10450,25 +10450,25 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O108" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>338</v>
+        <v>191</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T108" t="n">
-        <v>238</v>
+        <v>355</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O109" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
-        <v>343</v>
+        <v>235</v>
       </c>
       <c r="S109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T109" t="n">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,25 +10636,25 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O110" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T110" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O111" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         <v>4</v>
       </c>
       <c r="R111" t="n">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="S111" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="T111" t="n">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/24/2026 4:05 MDT</t>
+          <t>8/24/2026 5:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10825,22 +10825,22 @@
         <v>72</v>
       </c>
       <c r="O112" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T112" t="n">
-        <v>286</v>
+        <v>1</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/24/2026 4:04 MDT</t>
+          <t>8/24/2026 5:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/24/2026 4:04 MDT</t>
+          <t>8/24/2026 5:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/24/2026 4:04 MDT</t>
+          <t>8/24/2026 5:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10918,7 +10918,7 @@
         <v>62</v>
       </c>
       <c r="O113" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -10927,13 +10927,13 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T113" t="n">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/24/2026 4:04 MDT</t>
+          <t>8/24/2026 5:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/24/2026 4:04 MDT</t>
+          <t>8/24/2026 5:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/24/2026 4:04 MDT</t>
+          <t>8/24/2026 5:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11017,16 +11017,16 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T114" t="n">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,25 +11101,25 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O115" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T115" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,25 +11194,25 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="S116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T116" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11290,22 +11290,22 @@
         <v>74</v>
       </c>
       <c r="O117" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R117" t="n">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="S117" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11383,7 +11383,7 @@
         <v>58</v>
       </c>
       <c r="O118" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -11392,13 +11392,13 @@
         <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T118" t="n">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,25 +11473,25 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O119" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>305</v>
+        <v>7</v>
       </c>
       <c r="S119" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T119" t="n">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O120" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>2</v>
       </c>
       <c r="R120" t="n">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="S120" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T120" t="n">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/24/2026 4:03 MDT</t>
+          <t>8/24/2026 5:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O121" t="n">
         <v>58</v>
@@ -11668,16 +11668,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
+        <v>15</v>
+      </c>
+      <c r="S121" t="n">
         <v>7</v>
       </c>
-      <c r="S121" t="n">
-        <v>5</v>
-      </c>
       <c r="T121" t="n">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11755,22 +11755,22 @@
         <v>77</v>
       </c>
       <c r="O122" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R122" t="n">
+        <v>72</v>
+      </c>
+      <c r="S122" t="n">
+        <v>9</v>
+      </c>
+      <c r="T122" t="n">
         <v>78</v>
-      </c>
-      <c r="S122" t="n">
-        <v>8</v>
-      </c>
-      <c r="T122" t="n">
-        <v>80</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11854,16 +11854,16 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T123" t="n">
-        <v>336</v>
+        <v>59</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/24/2026 4:02 MDT</t>
+          <t>8/24/2026 5:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11941,7 +11941,7 @@
         <v>54</v>
       </c>
       <c r="O124" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="S124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T124" t="n">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,25 +12031,25 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O125" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R125" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="S125" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T125" t="n">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,25 +12124,25 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O126" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>268</v>
+        <v>351</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T126" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O127" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -12229,13 +12229,13 @@
         <v>10</v>
       </c>
       <c r="R127" t="n">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="S127" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T127" t="n">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/24/2026 4:01 MDT</t>
+          <t>8/24/2026 5:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12313,22 +12313,22 @@
         <v>78</v>
       </c>
       <c r="O128" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>13</v>
+      </c>
+      <c r="T128" t="n">
         <v>11</v>
-      </c>
-      <c r="S128" t="n">
-        <v>10</v>
-      </c>
-      <c r="T128" t="n">
-        <v>20</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,25 +12403,25 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O129" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T129" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12499,7 +12499,7 @@
         <v>69</v>
       </c>
       <c r="O130" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -12508,13 +12508,13 @@
         <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="S130" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T130" t="n">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O131" t="n">
         <v>79</v>
@@ -12598,16 +12598,16 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" t="n">
-        <v>198</v>
+        <v>136</v>
       </c>
       <c r="S131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T131" t="n">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12691,16 +12691,16 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T132" t="n">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O133" t="n">
         <v>27</v>
@@ -12793,7 +12793,7 @@
         <v>17</v>
       </c>
       <c r="T133" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O134" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -12886,7 +12886,7 @@
         <v>10</v>
       </c>
       <c r="T134" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12964,7 +12964,7 @@
         <v>70</v>
       </c>
       <c r="O135" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
         <v>13</v>
       </c>
       <c r="T135" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,22 +13054,22 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O136" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
       </c>
       <c r="Q136" t="n">
+        <v>3</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
         <v>5</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>7</v>
       </c>
       <c r="T136" t="n">
         <v>31</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/24/2026 4:49 MDT</t>
+          <t>8/24/2026 5:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/24/2026 4:49 MDT</t>
+          <t>8/24/2026 5:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O137" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/24/2026 4:59 MDT</t>
+          <t>8/24/2026 5:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/24/2026 4:59 MDT</t>
+          <t>8/24/2026 5:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13252,13 +13252,13 @@
         <v>8</v>
       </c>
       <c r="R138" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T138" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/24/2026 4:48 MDT</t>
+          <t>8/24/2026 5:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/24/2026 4:48 MDT</t>
+          <t>8/24/2026 5:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13336,22 +13336,22 @@
         <v>88</v>
       </c>
       <c r="O139" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R139" t="n">
         <v>170</v>
       </c>
       <c r="S139" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T139" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/24/2026 4:59 MDT</t>
+          <t>8/24/2026 5:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/24/2026 4:59 MDT</t>
+          <t>8/24/2026 5:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,16 +13426,16 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O140" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R140" t="n">
         <v>160</v>
@@ -13444,7 +13444,7 @@
         <v>19</v>
       </c>
       <c r="T140" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/24/2026 4:48 MDT</t>
+          <t>8/24/2026 5:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/24/2026 4:48 MDT</t>
+          <t>8/24/2026 5:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O141" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>7</v>
       </c>
       <c r="R141" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="S141" t="n">
         <v>9</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O142" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -13624,13 +13624,13 @@
         <v>2</v>
       </c>
       <c r="R142" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="S142" t="n">
         <v>6</v>
       </c>
       <c r="T142" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,10 +13705,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O143" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -13717,13 +13717,13 @@
         <v>5</v>
       </c>
       <c r="R143" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="S143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T143" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/24/2026 4:48 MDT</t>
+          <t>8/24/2026 5:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/24/2026 4:48 MDT</t>
+          <t>8/24/2026 5:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13801,7 +13801,7 @@
         <v>74</v>
       </c>
       <c r="O144" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -13810,13 +13810,13 @@
         <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="S144" t="n">
         <v>9</v>
       </c>
       <c r="T144" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O145" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -13903,7 +13903,7 @@
         <v>7</v>
       </c>
       <c r="R145" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="S145" t="n">
         <v>13</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13987,7 +13987,7 @@
         <v>64</v>
       </c>
       <c r="O146" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13999,10 +13999,10 @@
         <v>230</v>
       </c>
       <c r="S146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T146" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,25 +14077,25 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O147" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R147" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="S147" t="n">
         <v>11</v>
       </c>
       <c r="T147" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/24/2026 4:49 MDT</t>
+          <t>8/24/2026 5:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/24/2026 4:49 MDT</t>
+          <t>8/24/2026 5:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O148" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14182,13 +14182,13 @@
         <v>2</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S148" t="n">
         <v>7</v>
       </c>
       <c r="T148" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/24/2026 4:59 MDT</t>
+          <t>8/24/2026 5:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/24/2026 4:59 MDT</t>
+          <t>8/24/2026 5:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14266,7 +14266,7 @@
         <v>59</v>
       </c>
       <c r="O149" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -14281,7 +14281,7 @@
         <v>7</v>
       </c>
       <c r="T149" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/24/2026 4:57 MDT</t>
+          <t>8/24/2026 5:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/24/2026 4:57 MDT</t>
+          <t>8/24/2026 5:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,25 +14356,25 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O150" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T150" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,10 +14449,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O151" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
         <v>2</v>
       </c>
       <c r="R151" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="S151" t="n">
         <v>3</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14545,19 +14545,19 @@
         <v>57</v>
       </c>
       <c r="O152" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T152" t="n">
         <v>21</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O153" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         <v>9</v>
       </c>
       <c r="T153" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/24/2026 4:53 MDT</t>
+          <t>8/24/2026 5:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,10 +14728,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O154" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -14740,13 +14740,13 @@
         <v>6</v>
       </c>
       <c r="R154" t="n">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
       </c>
       <c r="T154" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/24/2026 4:52 MDT</t>
+          <t>8/24/2026 5:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14824,22 +14824,22 @@
         <v>84</v>
       </c>
       <c r="O155" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R155" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T155" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/24/2026 4:47 MDT</t>
+          <t>8/24/2026 5:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/24/2026 4:47 MDT</t>
+          <t>8/24/2026 5:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14914,10 +14914,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O156" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -14932,7 +14932,7 @@
         <v>11</v>
       </c>
       <c r="T156" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/24/2026 4:49 MDT</t>
+          <t>8/24/2026 5:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/24/2026 4:49 MDT</t>
+          <t>8/24/2026 5:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,22 +15007,22 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O157" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R157" t="n">
         <v>20</v>
       </c>
       <c r="S157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T157" t="n">
         <v>29</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/24/2026 4:00 MDT</t>
+          <t>8/24/2026 5:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/24/2026 5:00 MDT</t>
+          <t>8/24/2026 6:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/24/2026 4:50 MDT</t>
+          <t>8/24/2026 5:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15100,10 +15100,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O158" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -15112,13 +15112,13 @@
         <v>3</v>
       </c>
       <c r="R158" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T158" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/25/2026 01:42 MDT</t>
+          <t>8/25/2026 02:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/25/2026 01:42 MDT</t>
+          <t>8/25/2026 02:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/25/2026 01:42 MDT</t>
+          <t>8/25/2026 02:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/25/2026 01:42 MDT</t>
+          <t>8/25/2026 02:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/25/2026 01:42 MDT</t>
+          <t>8/25/2026 02:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/25/2026 01:42 MDT</t>
+          <t>8/25/2026 02:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
+        <v>338</v>
+      </c>
+      <c r="S3" t="n">
         <v>5</v>
       </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
       <c r="T3" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O4" t="n">
         <v>47</v>
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>181</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>311</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
       <c r="T5" t="n">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -967,7 +967,7 @@
         <v>58</v>
       </c>
       <c r="O6" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/25/2026 01:41 MDT</t>
+          <t>8/25/2026 02:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,25 +1057,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>121</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>103</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
       <c r="T7" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/25/2026 01:40 MDT</t>
+          <t>8/25/2026 02:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/25/2026 01:40 MDT</t>
+          <t>8/25/2026 02:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/25/2026 01:40 MDT</t>
+          <t>8/25/2026 02:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="O8" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/25/2026 01:40 MDT</t>
+          <t>8/25/2026 02:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/25/2026 01:40 MDT</t>
+          <t>8/25/2026 02:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/25/2026 01:40 MDT</t>
+          <t>8/25/2026 02:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1348,13 +1348,13 @@
         <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="S10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T10" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>311</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>349</v>
+        <v>145</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/25/2026 01:39 MDT</t>
+          <t>8/25/2026 02:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="S13" t="n">
         <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O15" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1906,13 +1906,13 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O17" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O18" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2173,25 +2173,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O19" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O20" t="n">
         <v>63</v>
@@ -2278,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/25/2026 01:38 MDT</t>
+          <t>8/25/2026 02:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2362,7 +2362,7 @@
         <v>57</v>
       </c>
       <c r="O21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2371,13 +2371,13 @@
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2455,22 +2455,22 @@
         <v>49</v>
       </c>
       <c r="O22" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2548,22 +2548,22 @@
         <v>73</v>
       </c>
       <c r="O23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2638,25 +2638,25 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O24" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T24" t="n">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O25" t="n">
         <v>26</v>
@@ -2740,16 +2740,16 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R25" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,25 +2824,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O27" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,25 +3010,25 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O28" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="S28" t="n">
         <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/25/2026 01:37 MDT</t>
+          <t>8/25/2026 02:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3115,13 +3115,13 @@
         <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/25/2026 01:36 MDT</t>
+          <t>8/25/2026 02:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/25/2026 01:36 MDT</t>
+          <t>8/25/2026 02:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/25/2026 01:36 MDT</t>
+          <t>8/25/2026 02:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O30" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/25/2026 01:36 MDT</t>
+          <t>8/25/2026 02:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/25/2026 01:36 MDT</t>
+          <t>8/25/2026 02:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/25/2026 01:36 MDT</t>
+          <t>8/25/2026 02:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3301,13 +3301,13 @@
         <v>12</v>
       </c>
       <c r="R31" t="n">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="S31" t="n">
         <v>18</v>
       </c>
       <c r="T31" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/25/2026 01:35 MDT</t>
+          <t>8/25/2026 02:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/25/2026 01:35 MDT</t>
+          <t>8/25/2026 02:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/25/2026 01:35 MDT</t>
+          <t>8/25/2026 02:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3385,22 +3385,22 @@
         <v>56</v>
       </c>
       <c r="O32" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
       </c>
       <c r="T32" t="n">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/25/2026 01:35 MDT</t>
+          <t>8/25/2026 02:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/25/2026 01:35 MDT</t>
+          <t>8/25/2026 02:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/25/2026 01:35 MDT</t>
+          <t>8/25/2026 02:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O33" t="n">
         <v>39</v>
@@ -3484,16 +3484,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>232</v>
+        <v>163</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,25 +3568,25 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O34" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O35" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T35" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O36" t="n">
         <v>46</v>
@@ -3766,13 +3766,13 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/25/2026 01:34 MDT</t>
+          <t>8/25/2026 02:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,25 +3847,25 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O37" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="S37" t="n">
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3952,13 +3952,13 @@
         <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="S38" t="n">
         <v>8</v>
       </c>
       <c r="T38" t="n">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,25 +4033,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O39" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O40" t="n">
         <v>37</v>
@@ -4135,16 +4135,16 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>280</v>
+        <v>29</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O41" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R41" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="S41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T41" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O42" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -4324,13 +4324,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
+        <v>106</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>83</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>115</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/25/2026 01:33 MDT</t>
+          <t>8/25/2026 02:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4414,16 +4414,16 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T43" t="n">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/25/2026 01:32 MDT</t>
+          <t>8/25/2026 02:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/25/2026 01:32 MDT</t>
+          <t>8/25/2026 02:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/25/2026 01:32 MDT</t>
+          <t>8/25/2026 02:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -4510,13 +4510,13 @@
         <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S44" t="n">
         <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/25/2026 01:28 MDT</t>
+          <t>8/25/2026 02:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/25/2026 01:28 MDT</t>
+          <t>8/25/2026 02:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/25/2026 01:28 MDT</t>
+          <t>8/25/2026 02:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O45" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4603,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4684,25 +4684,25 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O46" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O47" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
       </c>
       <c r="T47" t="n">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/25/2026 01:27 MDT</t>
+          <t>8/25/2026 02:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4870,25 +4870,25 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O48" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T48" t="n">
-        <v>338</v>
+        <v>15</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O49" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5059,22 +5059,22 @@
         <v>83</v>
       </c>
       <c r="O50" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R50" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="S50" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T50" t="n">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/25/2026 01:26 MDT</t>
+          <t>8/25/2026 02:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O51" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>251</v>
+        <v>26</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
       </c>
       <c r="T51" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/25/2026 01:25 MDT</t>
+          <t>8/25/2026 02:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/25/2026 01:25 MDT</t>
+          <t>8/25/2026 02:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/25/2026 01:25 MDT</t>
+          <t>8/25/2026 02:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O52" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>308</v>
+        <v>152</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="n">
-        <v>334</v>
+        <v>273</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/25/2026 01:24 MDT</t>
+          <t>8/25/2026 02:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/25/2026 01:24 MDT</t>
+          <t>8/25/2026 02:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/25/2026 01:24 MDT</t>
+          <t>8/25/2026 02:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O53" t="n">
         <v>38</v>
@@ -5347,13 +5347,13 @@
         <v>11</v>
       </c>
       <c r="R53" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T53" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,25 +5428,25 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O54" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O55" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>55</v>
+      </c>
+      <c r="S55" t="n">
         <v>3</v>
       </c>
-      <c r="R55" t="n">
-        <v>119</v>
-      </c>
-      <c r="S55" t="n">
-        <v>4</v>
-      </c>
       <c r="T55" t="n">
-        <v>310</v>
+        <v>128</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O56" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>129</v>
+        <v>289</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
       </c>
       <c r="T56" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/25/2026 01:23 MDT</t>
+          <t>8/25/2026 02:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O57" t="n">
         <v>46</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T57" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/25/2026 01:22 MDT</t>
+          <t>8/25/2026 02:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/25/2026 01:22 MDT</t>
+          <t>8/25/2026 02:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/25/2026 01:22 MDT</t>
+          <t>8/25/2026 02:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,25 +5800,25 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O58" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/25/2026 01:22 MDT</t>
+          <t>8/25/2026 02:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/25/2026 01:22 MDT</t>
+          <t>8/25/2026 02:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/25/2026 01:22 MDT</t>
+          <t>8/25/2026 02:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5902,16 +5902,16 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T59" t="n">
-        <v>354</v>
+        <v>8</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/25/2026 01:20 MDT</t>
+          <t>8/25/2026 02:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/25/2026 01:20 MDT</t>
+          <t>8/25/2026 02:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/25/2026 01:20 MDT</t>
+          <t>8/25/2026 02:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5989,22 +5989,22 @@
         <v>74</v>
       </c>
       <c r="O60" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R60" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T60" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/25/2026 01:20 MDT</t>
+          <t>8/25/2026 02:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/25/2026 01:20 MDT</t>
+          <t>8/25/2026 02:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/25/2026 01:20 MDT</t>
+          <t>8/25/2026 02:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O61" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -6091,13 +6091,13 @@
         <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O62" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="S62" t="n">
         <v>6</v>
       </c>
       <c r="T62" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6268,7 +6268,7 @@
         <v>72</v>
       </c>
       <c r="O63" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -6277,13 +6277,13 @@
         <v>20</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S63" t="n">
         <v>29</v>
       </c>
       <c r="T63" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6361,22 +6361,22 @@
         <v>74</v>
       </c>
       <c r="O64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
+        <v>247</v>
+      </c>
+      <c r="S64" t="n">
+        <v>6</v>
+      </c>
+      <c r="T64" t="n">
         <v>281</v>
-      </c>
-      <c r="S64" t="n">
-        <v>7</v>
-      </c>
-      <c r="T64" t="n">
-        <v>270</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/25/2026 01:19 MDT</t>
+          <t>8/25/2026 02:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6454,22 +6454,22 @@
         <v>70</v>
       </c>
       <c r="O65" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R65" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="S65" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T65" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/25/2026 01:17 MDT</t>
+          <t>8/25/2026 02:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/25/2026 01:17 MDT</t>
+          <t>8/25/2026 02:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/25/2026 01:17 MDT</t>
+          <t>8/25/2026 02:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6544,25 +6544,25 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O66" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T66" t="n">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,25 +6637,25 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O67" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>260</v>
+        <v>62</v>
       </c>
       <c r="S67" t="n">
         <v>6</v>
       </c>
       <c r="T67" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O68" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>223</v>
+        <v>347</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6826,22 +6826,22 @@
         <v>61</v>
       </c>
       <c r="O69" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T69" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6919,22 +6919,22 @@
         <v>92</v>
       </c>
       <c r="O70" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T70" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/25/2026 01:16 MDT</t>
+          <t>8/25/2026 02:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
       </c>
       <c r="T71" t="n">
-        <v>351</v>
+        <v>7</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/25/2026 01:15 MDT</t>
+          <t>8/25/2026 02:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/25/2026 01:15 MDT</t>
+          <t>8/25/2026 02:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/25/2026 01:15 MDT</t>
+          <t>8/25/2026 02:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O72" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -7114,13 +7114,13 @@
         <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T72" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O73" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -7207,13 +7207,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,25 +7288,25 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O74" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R74" t="n">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T74" t="n">
-        <v>343</v>
+        <v>283</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O75" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>96</v>
+        <v>284</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T75" t="n">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>19</v>
       </c>
       <c r="R76" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
       </c>
       <c r="T76" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,25 +7567,25 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O77" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R77" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T77" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/25/2026 01:14 MDT</t>
+          <t>8/25/2026 02:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7660,25 +7660,25 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O78" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R78" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
       </c>
       <c r="T78" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,25 +7753,25 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O79" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R79" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S79" t="n">
         <v>11</v>
       </c>
       <c r="T79" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O80" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -7858,13 +7858,13 @@
         <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T80" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O81" t="n">
         <v>36</v>
@@ -7951,13 +7951,13 @@
         <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T81" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,25 +8032,25 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R82" t="n">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="S82" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T82" t="n">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/25/2026 01:13 MDT</t>
+          <t>8/25/2026 02:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,25 +8125,25 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O83" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
       </c>
       <c r="T83" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/25/2026 01:12 MDT</t>
+          <t>8/25/2026 02:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/25/2026 01:12 MDT</t>
+          <t>8/25/2026 02:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/25/2026 01:12 MDT</t>
+          <t>8/25/2026 02:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O84" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="S84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T84" t="n">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O85" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -8323,13 +8323,13 @@
         <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T85" t="n">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O86" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="S86" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T86" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O87" t="n">
         <v>28</v>
@@ -8506,16 +8506,16 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="n">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,25 +8590,25 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O88" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T88" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="O89" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/25/2026 01:11 MDT</t>
+          <t>8/25/2026 02:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8785,16 +8785,16 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R90" t="n">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
       </c>
       <c r="T90" t="n">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/25/2026 01:09 MDT</t>
+          <t>8/25/2026 02:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/25/2026 01:09 MDT</t>
+          <t>8/25/2026 02:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/25/2026 01:09 MDT</t>
+          <t>8/25/2026 02:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O91" t="n">
         <v>74</v>
@@ -8878,16 +8878,16 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T91" t="n">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/25/2026 01:09 MDT</t>
+          <t>8/25/2026 02:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/25/2026 01:09 MDT</t>
+          <t>8/25/2026 02:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/25/2026 01:09 MDT</t>
+          <t>8/25/2026 02:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8971,16 +8971,16 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T92" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,10 +9055,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O93" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -9067,13 +9067,13 @@
         <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T93" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O94" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -9160,13 +9160,13 @@
         <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T94" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9241,25 +9241,25 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O95" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="S95" t="n">
         <v>11</v>
       </c>
       <c r="T95" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9337,7 +9337,7 @@
         <v>53</v>
       </c>
       <c r="O96" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O97" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -9439,13 +9439,13 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T97" t="n">
-        <v>302</v>
+        <v>1</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9520,25 +9520,25 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O98" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T98" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O99" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -9625,13 +9625,13 @@
         <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T99" t="n">
-        <v>143</v>
+        <v>321</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/25/2026 01:08 MDT</t>
+          <t>8/25/2026 02:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9706,16 +9706,16 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O100" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R100" t="n">
         <v>352</v>
@@ -9724,7 +9724,7 @@
         <v>5</v>
       </c>
       <c r="T100" t="n">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9808,16 +9808,16 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9895,22 +9895,22 @@
         <v>65</v>
       </c>
       <c r="O102" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R102" t="n">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="S102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T102" t="n">
-        <v>273</v>
+        <v>341</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O103" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R103" t="n">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="S103" t="n">
         <v>9</v>
       </c>
       <c r="T103" t="n">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/25/2026 01:07 MDT</t>
+          <t>8/25/2026 02:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,25 +10078,25 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O104" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="S104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>4</v>
+        <v>321</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10171,10 +10171,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O105" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T105" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10264,25 +10264,25 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O106" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R106" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S106" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T106" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/25/2026 01:06 MDT</t>
+          <t>8/25/2026 02:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O107" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>46</v>
+        <v>354</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10450,25 +10450,25 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O108" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R108" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="S108" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T108" t="n">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O109" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R109" t="n">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="S109" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T109" t="n">
-        <v>35</v>
+        <v>333</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,25 +10636,25 @@
         </is>
       </c>
       <c r="N110" t="n">
+        <v>59</v>
+      </c>
+      <c r="O110" t="n">
         <v>58</v>
       </c>
-      <c r="O110" t="n">
-        <v>63</v>
-      </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T110" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="N111" t="n">
+        <v>73</v>
+      </c>
+      <c r="O111" t="n">
         <v>75</v>
-      </c>
-      <c r="O111" t="n">
-        <v>72</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
       </c>
       <c r="T111" t="n">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/25/2026 01:05 MDT</t>
+          <t>8/25/2026 02:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,10 +10822,10 @@
         </is>
       </c>
       <c r="N112" t="n">
+        <v>71</v>
+      </c>
+      <c r="O112" t="n">
         <v>74</v>
-      </c>
-      <c r="O112" t="n">
-        <v>60</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -10834,13 +10834,13 @@
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>229</v>
+        <v>339</v>
       </c>
       <c r="S112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/25/2026 01:04 MDT</t>
+          <t>8/25/2026 02:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/25/2026 01:04 MDT</t>
+          <t>8/25/2026 02:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/25/2026 01:04 MDT</t>
+          <t>8/25/2026 02:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,25 +10915,25 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O113" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R113" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T113" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/25/2026 01:04 MDT</t>
+          <t>8/25/2026 02:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/25/2026 01:04 MDT</t>
+          <t>8/25/2026 02:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/25/2026 01:04 MDT</t>
+          <t>8/25/2026 02:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11008,25 +11008,25 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O114" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>320</v>
+        <v>46</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T114" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,10 +11101,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O115" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -11113,13 +11113,13 @@
         <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="S115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T115" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,25 +11194,25 @@
         </is>
       </c>
       <c r="N116" t="n">
+        <v>86</v>
+      </c>
+      <c r="O116" t="n">
+        <v>24</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>3</v>
+      </c>
+      <c r="R116" t="n">
+        <v>77</v>
+      </c>
+      <c r="S116" t="n">
+        <v>6</v>
+      </c>
+      <c r="T116" t="n">
         <v>87</v>
-      </c>
-      <c r="O116" t="n">
-        <v>23</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>2</v>
-      </c>
-      <c r="R116" t="n">
-        <v>94</v>
-      </c>
-      <c r="S116" t="n">
-        <v>7</v>
-      </c>
-      <c r="T116" t="n">
-        <v>55</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11287,25 +11287,25 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O117" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R117" t="n">
+        <v>336</v>
+      </c>
+      <c r="S117" t="n">
+        <v>23</v>
+      </c>
+      <c r="T117" t="n">
         <v>327</v>
-      </c>
-      <c r="S117" t="n">
-        <v>24</v>
-      </c>
-      <c r="T117" t="n">
-        <v>341</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O118" t="n">
         <v>92</v>
@@ -11392,13 +11392,13 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="S118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>275</v>
+        <v>177</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,10 +11473,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O119" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -11491,7 +11491,7 @@
         <v>11</v>
       </c>
       <c r="T119" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="O120" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T120" t="n">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/25/2026 01:03 MDT</t>
+          <t>8/25/2026 02:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,25 +11659,25 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O121" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R121" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S121" t="n">
         <v>13</v>
       </c>
       <c r="T121" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,25 +11752,25 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O122" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>335</v>
+        <v>253</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T122" t="n">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11854,16 +11854,16 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="S123" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T123" t="n">
-        <v>355</v>
+        <v>17</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/25/2026 01:02 MDT</t>
+          <t>8/25/2026 02:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O124" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T124" t="n">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,25 +12031,25 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O125" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R125" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T125" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,10 +12124,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O126" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -12136,13 +12136,13 @@
         <v>2</v>
       </c>
       <c r="R126" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="S126" t="n">
         <v>6</v>
       </c>
       <c r="T126" t="n">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O127" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R127" t="n">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="S127" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T127" t="n">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/25/2026 01:01 MDT</t>
+          <t>8/25/2026 02:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12310,25 +12310,25 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O128" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T128" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12415,13 +12415,13 @@
         <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O130" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -12508,13 +12508,13 @@
         <v>4</v>
       </c>
       <c r="R130" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T130" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O131" t="n">
         <v>79</v>
@@ -12601,13 +12601,13 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="S131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,25 +12682,25 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O132" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="S132" t="n">
         <v>4</v>
       </c>
       <c r="T132" t="n">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,25 +12775,25 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O133" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R133" t="n">
         <v>220</v>
       </c>
       <c r="S133" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T133" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,25 +12868,25 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O134" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R134" t="n">
         <v>330</v>
       </c>
       <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="n">
         <v>13</v>
-      </c>
-      <c r="T134" t="n">
-        <v>23</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12964,7 +12964,7 @@
         <v>68</v>
       </c>
       <c r="O135" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -12973,13 +12973,13 @@
         <v>2</v>
       </c>
       <c r="R135" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="S135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T135" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O136" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/25/2026 01:49 MDT</t>
+          <t>8/25/2026 02:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/25/2026 01:49 MDT</t>
+          <t>8/25/2026 02:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13147,22 +13147,22 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O137" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R137" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="S137" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T137" t="n">
         <v>55</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/25/2026 01:59 MDT</t>
+          <t>8/25/2026 02:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/25/2026 01:59 MDT</t>
+          <t>8/25/2026 02:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13240,10 +13240,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O138" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -13252,13 +13252,13 @@
         <v>7</v>
       </c>
       <c r="R138" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="S138" t="n">
         <v>9</v>
       </c>
       <c r="T138" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/25/2026 01:48 MDT</t>
+          <t>8/25/2026 02:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/25/2026 01:48 MDT</t>
+          <t>8/25/2026 02:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,16 +13333,16 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O139" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R139" t="n">
         <v>220</v>
@@ -13351,7 +13351,7 @@
         <v>6</v>
       </c>
       <c r="T139" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/25/2026 01:59 MDT</t>
+          <t>8/25/2026 02:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/25/2026 01:59 MDT</t>
+          <t>8/25/2026 02:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O140" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -13438,13 +13438,13 @@
         <v>2</v>
       </c>
       <c r="R140" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T140" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/25/2026 01:48 MDT</t>
+          <t>8/25/2026 02:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/25/2026 01:48 MDT</t>
+          <t>8/25/2026 02:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O141" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>6</v>
       </c>
       <c r="R141" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="S141" t="n">
         <v>8</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O142" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -13624,13 +13624,13 @@
         <v>5</v>
       </c>
       <c r="R142" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
       </c>
       <c r="T142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,10 +13705,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O143" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -13717,13 +13717,13 @@
         <v>2</v>
       </c>
       <c r="R143" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/25/2026 01:48 MDT</t>
+          <t>8/25/2026 02:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/25/2026 01:48 MDT</t>
+          <t>8/25/2026 02:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13801,22 +13801,22 @@
         <v>77</v>
       </c>
       <c r="O144" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R144" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S144" t="n">
         <v>23</v>
       </c>
       <c r="T144" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13894,7 +13894,7 @@
         <v>72</v>
       </c>
       <c r="O145" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -13903,13 +13903,13 @@
         <v>5</v>
       </c>
       <c r="R145" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="S145" t="n">
         <v>9</v>
       </c>
       <c r="T145" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13987,7 +13987,7 @@
         <v>64</v>
       </c>
       <c r="O146" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13996,13 +13996,13 @@
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
       </c>
       <c r="T146" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,10 +14077,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O147" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -14092,10 +14092,10 @@
         <v>270</v>
       </c>
       <c r="S147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T147" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/25/2026 01:49 MDT</t>
+          <t>8/25/2026 02:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/25/2026 01:49 MDT</t>
+          <t>8/25/2026 02:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14173,7 +14173,7 @@
         <v>64</v>
       </c>
       <c r="O148" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14188,7 +14188,7 @@
         <v>8</v>
       </c>
       <c r="T148" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/25/2026 01:59 MDT</t>
+          <t>8/25/2026 02:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/25/2026 01:59 MDT</t>
+          <t>8/25/2026 02:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14266,7 +14266,7 @@
         <v>63</v>
       </c>
       <c r="O149" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -14281,7 +14281,7 @@
         <v>11</v>
       </c>
       <c r="T149" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/25/2026 01:57 MDT</t>
+          <t>8/25/2026 02:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/25/2026 01:57 MDT</t>
+          <t>8/25/2026 02:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O150" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -14368,13 +14368,13 @@
         <v>5</v>
       </c>
       <c r="R150" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S150" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T150" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,22 +14449,22 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O151" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R151" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T151" t="n">
         <v>30</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,22 +14542,22 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O152" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
+        <v>3</v>
+      </c>
+      <c r="R152" t="n">
+        <v>30</v>
+      </c>
+      <c r="S152" t="n">
         <v>5</v>
-      </c>
-      <c r="R152" t="n">
-        <v>20</v>
-      </c>
-      <c r="S152" t="n">
-        <v>7</v>
       </c>
       <c r="T152" t="n">
         <v>47</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O153" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -14647,13 +14647,13 @@
         <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="S153" t="n">
         <v>8</v>
       </c>
       <c r="T153" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/25/2026 01:53 MDT</t>
+          <t>8/25/2026 02:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,10 +14728,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O154" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -14743,10 +14743,10 @@
         <v>30</v>
       </c>
       <c r="S154" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T154" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/25/2026 01:52 MDT</t>
+          <t>8/25/2026 02:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O155" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -14833,13 +14833,13 @@
         <v>2</v>
       </c>
       <c r="R155" t="n">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="S155" t="n">
         <v>6</v>
       </c>
       <c r="T155" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/25/2026 01:47 MDT</t>
+          <t>8/25/2026 02:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/25/2026 01:47 MDT</t>
+          <t>8/25/2026 02:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14917,7 +14917,7 @@
         <v>58</v>
       </c>
       <c r="O156" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -14929,10 +14929,10 @@
         <v>200</v>
       </c>
       <c r="S156" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T156" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/25/2026 01:49 MDT</t>
+          <t>8/25/2026 02:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/25/2026 01:49 MDT</t>
+          <t>8/25/2026 02:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,22 +15007,22 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O157" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S157" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T157" t="n">
         <v>41</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/25/2026 01:00 MDT</t>
+          <t>8/25/2026 02:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/25/2026 01:50 MDT</t>
+          <t>8/25/2026 02:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15100,10 +15100,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O158" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -15115,10 +15115,10 @@
         <v>160</v>
       </c>
       <c r="S158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T158" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/25/2026 02:42 MDT</t>
+          <t>8/25/2026 03:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/25/2026 02:42 MDT</t>
+          <t>8/25/2026 03:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/25/2026 02:42 MDT</t>
+          <t>8/25/2026 03:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>320</v>
+        <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>314</v>
+        <v>73</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/25/2026 02:42 MDT</t>
+          <t>8/25/2026 03:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/25/2026 02:42 MDT</t>
+          <t>8/25/2026 03:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/25/2026 02:42 MDT</t>
+          <t>8/25/2026 03:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>338</v>
+        <v>35</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
         <v>34</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>181</v>
+        <v>346</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>304</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>66</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>151</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/25/2026 02:41 MDT</t>
+          <t>8/25/2026 03:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7" t="n">
         <v>46</v>
@@ -1066,16 +1066,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/25/2026 02:40 MDT</t>
+          <t>8/25/2026 03:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/25/2026 02:40 MDT</t>
+          <t>8/25/2026 03:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/25/2026 02:40 MDT</t>
+          <t>8/25/2026 03:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/25/2026 02:40 MDT</t>
+          <t>8/25/2026 03:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/25/2026 02:40 MDT</t>
+          <t>8/25/2026 03:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/25/2026 02:40 MDT</t>
+          <t>8/25/2026 03:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="S9" t="n">
         <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O10" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O11" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>290</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1525,7 +1525,7 @@
         <v>53</v>
       </c>
       <c r="O12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/25/2026 02:39 MDT</t>
+          <t>8/25/2026 03:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="S13" t="n">
         <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>51</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O15" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1906,13 +1906,13 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O17" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O18" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>256</v>
+        <v>39</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2173,25 +2173,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>277</v>
+        <v>352</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O20" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/25/2026 02:38 MDT</t>
+          <t>8/25/2026 03:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,25 +2359,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>290</v>
+        <v>255</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2455,7 +2455,7 @@
         <v>49</v>
       </c>
       <c r="O22" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2464,13 +2464,13 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2548,7 +2548,7 @@
         <v>73</v>
       </c>
       <c r="O23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2557,13 +2557,13 @@
         <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2638,25 +2638,25 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O24" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,25 +2731,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
+        <v>167</v>
+      </c>
+      <c r="S25" t="n">
+        <v>23</v>
+      </c>
+      <c r="T25" t="n">
         <v>159</v>
-      </c>
-      <c r="S25" t="n">
-        <v>21</v>
-      </c>
-      <c r="T25" t="n">
-        <v>164</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,25 +2824,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S26" t="n">
         <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2920,22 +2920,22 @@
         <v>72</v>
       </c>
       <c r="O27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T27" t="n">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3022,13 +3022,13 @@
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/25/2026 02:37 MDT</t>
+          <t>8/25/2026 03:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="S29" t="n">
         <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/25/2026 02:36 MDT</t>
+          <t>8/25/2026 03:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/25/2026 02:36 MDT</t>
+          <t>8/25/2026 03:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/25/2026 02:36 MDT</t>
+          <t>8/25/2026 03:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,25 +3196,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/25/2026 02:36 MDT</t>
+          <t>8/25/2026 03:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/25/2026 02:36 MDT</t>
+          <t>8/25/2026 03:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/25/2026 02:36 MDT</t>
+          <t>8/25/2026 03:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O31" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R31" t="n">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="S31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T31" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/25/2026 02:35 MDT</t>
+          <t>8/25/2026 03:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/25/2026 02:35 MDT</t>
+          <t>8/25/2026 03:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/25/2026 02:35 MDT</t>
+          <t>8/25/2026 03:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3382,25 +3382,25 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O32" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="n">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/25/2026 02:35 MDT</t>
+          <t>8/25/2026 03:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/25/2026 02:35 MDT</t>
+          <t>8/25/2026 03:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/25/2026 02:35 MDT</t>
+          <t>8/25/2026 03:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3478,7 +3478,7 @@
         <v>68</v>
       </c>
       <c r="O33" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3487,13 +3487,13 @@
         <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,25 +3568,25 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O34" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R35" t="n">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="S35" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T35" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3766,13 +3766,13 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/25/2026 02:34 MDT</t>
+          <t>8/25/2026 03:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,25 +3847,25 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="O37" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R37" t="n">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3943,7 +3943,7 @@
         <v>78</v>
       </c>
       <c r="O38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3952,13 +3952,13 @@
         <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,25 +4033,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O39" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4129,22 +4129,22 @@
         <v>73</v>
       </c>
       <c r="O40" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R40" t="n">
-        <v>29</v>
+        <v>272</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O41" t="n">
         <v>29</v>
@@ -4228,16 +4228,16 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R41" t="n">
         <v>44</v>
       </c>
       <c r="S41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T41" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4315,22 +4315,22 @@
         <v>60</v>
       </c>
       <c r="O42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/25/2026 02:33 MDT</t>
+          <t>8/25/2026 03:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4408,22 +4408,22 @@
         <v>67</v>
       </c>
       <c r="O43" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T43" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/25/2026 02:32 MDT</t>
+          <t>8/25/2026 03:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/25/2026 02:32 MDT</t>
+          <t>8/25/2026 03:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/25/2026 02:32 MDT</t>
+          <t>8/25/2026 03:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -4510,13 +4510,13 @@
         <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="S44" t="n">
         <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/25/2026 02:28 MDT</t>
+          <t>8/25/2026 03:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/25/2026 02:28 MDT</t>
+          <t>8/25/2026 03:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/25/2026 02:28 MDT</t>
+          <t>8/25/2026 03:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,25 +4591,25 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O45" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T45" t="n">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O46" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4696,13 +4696,13 @@
         <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>165</v>
+        <v>87</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="n">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/25/2026 02:27 MDT</t>
+          <t>8/25/2026 03:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4870,25 +4870,25 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O48" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T48" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4963,25 +4963,25 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O49" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,22 +5056,22 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R50" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="S50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T50" t="n">
         <v>96</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/25/2026 02:26 MDT</t>
+          <t>8/25/2026 03:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O51" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -5161,13 +5161,13 @@
         <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/25/2026 02:25 MDT</t>
+          <t>8/25/2026 03:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/25/2026 02:25 MDT</t>
+          <t>8/25/2026 03:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/25/2026 02:25 MDT</t>
+          <t>8/25/2026 03:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O52" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T52" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/25/2026 02:24 MDT</t>
+          <t>8/25/2026 03:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/25/2026 02:24 MDT</t>
+          <t>8/25/2026 03:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/25/2026 02:24 MDT</t>
+          <t>8/25/2026 03:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5344,13 +5344,13 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R53" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="S53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O54" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -5440,13 +5440,13 @@
         <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O55" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O56" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>112</v>
+        <v>345</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/25/2026 02:23 MDT</t>
+          <t>8/25/2026 03:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,22 +5707,22 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O57" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T57" t="n">
         <v>353</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/25/2026 02:22 MDT</t>
+          <t>8/25/2026 03:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/25/2026 02:22 MDT</t>
+          <t>8/25/2026 03:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/25/2026 02:22 MDT</t>
+          <t>8/25/2026 03:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,25 +5800,25 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O58" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="S58" t="n">
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/25/2026 02:22 MDT</t>
+          <t>8/25/2026 03:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/25/2026 02:22 MDT</t>
+          <t>8/25/2026 03:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/25/2026 02:22 MDT</t>
+          <t>8/25/2026 03:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5893,25 +5893,25 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O59" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/25/2026 02:20 MDT</t>
+          <t>8/25/2026 03:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/25/2026 02:20 MDT</t>
+          <t>8/25/2026 03:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/25/2026 02:20 MDT</t>
+          <t>8/25/2026 03:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5986,16 +5986,16 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O60" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
         <v>319</v>
@@ -6004,7 +6004,7 @@
         <v>12</v>
       </c>
       <c r="T60" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/25/2026 02:20 MDT</t>
+          <t>8/25/2026 03:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/25/2026 02:20 MDT</t>
+          <t>8/25/2026 03:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/25/2026 02:20 MDT</t>
+          <t>8/25/2026 03:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6088,16 +6088,16 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O62" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T62" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6268,22 +6268,22 @@
         <v>72</v>
       </c>
       <c r="O63" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S63" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T63" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O64" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -6370,13 +6370,13 @@
         <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T64" t="n">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/25/2026 02:19 MDT</t>
+          <t>8/25/2026 03:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6460,16 +6460,16 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R65" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T65" t="n">
-        <v>345</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/25/2026 02:17 MDT</t>
+          <t>8/25/2026 03:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/25/2026 02:17 MDT</t>
+          <t>8/25/2026 03:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/25/2026 02:17 MDT</t>
+          <t>8/25/2026 03:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6547,22 +6547,22 @@
         <v>84</v>
       </c>
       <c r="O66" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T66" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O67" t="n">
         <v>47</v>
@@ -6649,13 +6649,13 @@
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="S67" t="n">
         <v>6</v>
       </c>
       <c r="T67" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O68" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="S68" t="n">
         <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O69" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T69" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O70" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -6928,13 +6928,13 @@
         <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="S70" t="n">
         <v>6</v>
       </c>
       <c r="T70" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/25/2026 02:16 MDT</t>
+          <t>8/25/2026 03:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7012,7 +7012,7 @@
         <v>61</v>
       </c>
       <c r="O71" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -7021,13 +7021,13 @@
         <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="n">
-        <v>7</v>
+        <v>355</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/25/2026 02:15 MDT</t>
+          <t>8/25/2026 03:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/25/2026 02:15 MDT</t>
+          <t>8/25/2026 03:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/25/2026 02:15 MDT</t>
+          <t>8/25/2026 03:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O72" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -7114,13 +7114,13 @@
         <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T72" t="n">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O73" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -7207,13 +7207,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,25 +7288,25 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O74" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="S74" t="n">
         <v>8</v>
       </c>
       <c r="T74" t="n">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O75" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
+        <v>3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>76</v>
+      </c>
+      <c r="S75" t="n">
         <v>4</v>
       </c>
-      <c r="R75" t="n">
-        <v>284</v>
-      </c>
-      <c r="S75" t="n">
-        <v>8</v>
-      </c>
       <c r="T75" t="n">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,25 +7474,25 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R76" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
       </c>
       <c r="T76" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,25 +7567,25 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O77" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="S77" t="n">
         <v>7</v>
       </c>
       <c r="T77" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/25/2026 02:14 MDT</t>
+          <t>8/25/2026 03:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7663,22 +7663,22 @@
         <v>66</v>
       </c>
       <c r="O78" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R78" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T78" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,25 +7753,25 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O79" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R79" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="S79" t="n">
         <v>11</v>
       </c>
       <c r="T79" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O80" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>63</v>
+        <v>352</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T80" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7942,22 +7942,22 @@
         <v>69</v>
       </c>
       <c r="O81" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T81" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -8044,13 +8044,13 @@
         <v>6</v>
       </c>
       <c r="R82" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T82" t="n">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/25/2026 02:13 MDT</t>
+          <t>8/25/2026 03:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O83" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/25/2026 02:12 MDT</t>
+          <t>8/25/2026 03:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/25/2026 02:12 MDT</t>
+          <t>8/25/2026 03:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/25/2026 02:12 MDT</t>
+          <t>8/25/2026 03:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O84" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>257</v>
+        <v>56</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T84" t="n">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,25 +8311,25 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O85" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>338</v>
+        <v>2</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O86" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="S86" t="n">
         <v>7</v>
       </c>
       <c r="T86" t="n">
-        <v>68</v>
+        <v>282</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,25 +8497,25 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O87" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R87" t="n">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T87" t="n">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,25 +8590,25 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O88" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R88" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="S88" t="n">
         <v>6</v>
       </c>
       <c r="T88" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="O89" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R89" t="n">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="S89" t="n">
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/25/2026 02:11 MDT</t>
+          <t>8/25/2026 03:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O90" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>3</v>
       </c>
       <c r="R90" t="n">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T90" t="n">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/25/2026 02:09 MDT</t>
+          <t>8/25/2026 03:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/25/2026 02:09 MDT</t>
+          <t>8/25/2026 03:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/25/2026 02:09 MDT</t>
+          <t>8/25/2026 03:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8872,7 +8872,7 @@
         <v>53</v>
       </c>
       <c r="O91" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -8881,13 +8881,13 @@
         <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
       </c>
       <c r="T91" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/25/2026 02:09 MDT</t>
+          <t>8/25/2026 03:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/25/2026 02:09 MDT</t>
+          <t>8/25/2026 03:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/25/2026 02:09 MDT</t>
+          <t>8/25/2026 03:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8962,25 +8962,25 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O92" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>349</v>
+        <v>309</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T92" t="n">
-        <v>14</v>
+        <v>334</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,25 +9055,25 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O93" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T93" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O94" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -9160,13 +9160,13 @@
         <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="S94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T94" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O95" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -9253,13 +9253,13 @@
         <v>5</v>
       </c>
       <c r="R95" t="n">
+        <v>52</v>
+      </c>
+      <c r="S95" t="n">
+        <v>12</v>
+      </c>
+      <c r="T95" t="n">
         <v>39</v>
-      </c>
-      <c r="S95" t="n">
-        <v>11</v>
-      </c>
-      <c r="T95" t="n">
-        <v>48</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9334,10 +9334,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O96" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O97" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -9439,13 +9439,13 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>198</v>
+        <v>319</v>
       </c>
       <c r="S97" t="n">
         <v>3</v>
       </c>
       <c r="T97" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9520,10 +9520,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O98" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
@@ -9532,13 +9532,13 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>51</v>
+        <v>335</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,25 +9613,25 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O99" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>233</v>
+        <v>340</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T99" t="n">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/25/2026 02:08 MDT</t>
+          <t>8/25/2026 03:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9706,25 +9706,25 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O100" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T100" t="n">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9808,16 +9808,16 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
+        <v>3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>36</v>
+      </c>
+      <c r="S101" t="n">
         <v>5</v>
       </c>
-      <c r="R101" t="n">
-        <v>42</v>
-      </c>
-      <c r="S101" t="n">
-        <v>6</v>
-      </c>
       <c r="T101" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,25 +9892,25 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O102" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T102" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O103" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T103" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/25/2026 02:07 MDT</t>
+          <t>8/25/2026 03:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,25 +10078,25 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O104" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10174,7 +10174,7 @@
         <v>58</v>
       </c>
       <c r="O105" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T105" t="n">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10264,25 +10264,25 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O106" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R106" t="n">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T106" t="n">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/25/2026 02:06 MDT</t>
+          <t>8/25/2026 03:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O107" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10453,7 +10453,7 @@
         <v>66</v>
       </c>
       <c r="O108" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -10462,13 +10462,13 @@
         <v>8</v>
       </c>
       <c r="R108" t="n">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="S108" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="T108" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O109" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R109" t="n">
-        <v>336</v>
+        <v>14</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,25 +10636,25 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O110" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="S110" t="n">
         <v>3</v>
       </c>
       <c r="T110" t="n">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10732,22 +10732,22 @@
         <v>73</v>
       </c>
       <c r="O111" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>287</v>
+        <v>188</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T111" t="n">
-        <v>108</v>
+        <v>266</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/25/2026 02:05 MDT</t>
+          <t>8/25/2026 03:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O112" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>339</v>
+        <v>216</v>
       </c>
       <c r="S112" t="n">
         <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/25/2026 02:04 MDT</t>
+          <t>8/25/2026 03:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/25/2026 02:04 MDT</t>
+          <t>8/25/2026 03:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/25/2026 02:04 MDT</t>
+          <t>8/25/2026 03:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O113" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -10927,13 +10927,13 @@
         <v>2</v>
       </c>
       <c r="R113" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T113" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/25/2026 02:04 MDT</t>
+          <t>8/25/2026 03:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/25/2026 02:04 MDT</t>
+          <t>8/25/2026 03:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/25/2026 02:04 MDT</t>
+          <t>8/25/2026 03:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11008,25 +11008,25 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O114" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="S114" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T114" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,25 +11101,25 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O115" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>46</v>
+        <v>358</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T115" t="n">
-        <v>13</v>
+        <v>351</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O116" t="n">
         <v>24</v>
@@ -11206,13 +11206,13 @@
         <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T116" t="n">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11287,25 +11287,25 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O117" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R117" t="n">
-        <v>336</v>
+        <v>6</v>
       </c>
       <c r="S117" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T117" t="n">
-        <v>327</v>
+        <v>24</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,25 +11380,25 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O118" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T118" t="n">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,25 +11473,25 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O119" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R119" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T119" t="n">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O120" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="S120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/25/2026 02:03 MDT</t>
+          <t>8/25/2026 03:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O121" t="n">
         <v>45</v>
@@ -11668,16 +11668,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R121" t="n">
         <v>1</v>
       </c>
       <c r="S121" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,25 +11752,25 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O122" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R122" t="n">
-        <v>253</v>
+        <v>343</v>
       </c>
       <c r="S122" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T122" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11845,25 +11845,25 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O123" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R123" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="S123" t="n">
         <v>7</v>
       </c>
       <c r="T123" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/25/2026 02:02 MDT</t>
+          <t>8/25/2026 03:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O124" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="S124" t="n">
         <v>2</v>
       </c>
       <c r="T124" t="n">
-        <v>111</v>
+        <v>295</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,25 +12031,25 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O125" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R125" t="n">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T125" t="n">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O126" t="n">
         <v>22</v>
@@ -12133,16 +12133,16 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R126" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O127" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R127" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="S127" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T127" t="n">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/25/2026 02:01 MDT</t>
+          <t>8/25/2026 03:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12310,25 +12310,25 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O128" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>21</v>
       </c>
       <c r="T128" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,10 +12403,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O129" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -12415,13 +12415,13 @@
         <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,25 +12496,25 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O130" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="S130" t="n">
         <v>7</v>
       </c>
       <c r="T130" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O131" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -12601,13 +12601,13 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T131" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,25 +12682,25 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O132" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R132" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T132" t="n">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O133" t="n">
         <v>25</v>
@@ -12784,16 +12784,16 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R133" t="n">
         <v>220</v>
       </c>
       <c r="S133" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T133" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,25 +12868,25 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O134" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R134" t="n">
         <v>330</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O135" t="n">
         <v>41</v>
@@ -12973,13 +12973,13 @@
         <v>2</v>
       </c>
       <c r="R135" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="S135" t="n">
         <v>7</v>
       </c>
       <c r="T135" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O136" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -13072,7 +13072,7 @@
         <v>9</v>
       </c>
       <c r="T136" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/25/2026 02:49 MDT</t>
+          <t>8/25/2026 03:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/25/2026 02:49 MDT</t>
+          <t>8/25/2026 03:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13150,22 +13150,22 @@
         <v>60</v>
       </c>
       <c r="O137" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R137" t="n">
         <v>320</v>
       </c>
       <c r="S137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T137" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/25/2026 02:59 MDT</t>
+          <t>8/25/2026 03:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/25/2026 02:59 MDT</t>
+          <t>8/25/2026 03:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13240,10 +13240,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O138" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -13252,13 +13252,13 @@
         <v>7</v>
       </c>
       <c r="R138" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="S138" t="n">
         <v>9</v>
       </c>
       <c r="T138" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/25/2026 02:48 MDT</t>
+          <t>8/25/2026 03:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/25/2026 02:48 MDT</t>
+          <t>8/25/2026 03:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O139" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -13345,13 +13345,13 @@
         <v>2</v>
       </c>
       <c r="R139" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="S139" t="n">
         <v>6</v>
       </c>
       <c r="T139" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/25/2026 02:59 MDT</t>
+          <t>8/25/2026 03:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/25/2026 02:59 MDT</t>
+          <t>8/25/2026 03:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O140" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -13444,7 +13444,7 @@
         <v>5</v>
       </c>
       <c r="T140" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/25/2026 02:48 MDT</t>
+          <t>8/25/2026 03:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/25/2026 02:48 MDT</t>
+          <t>8/25/2026 03:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O141" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -13531,13 +13531,13 @@
         <v>6</v>
       </c>
       <c r="R141" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="S141" t="n">
         <v>8</v>
       </c>
       <c r="T141" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O142" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -13627,10 +13627,10 @@
         <v>310</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T142" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,7 +13705,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O143" t="n">
         <v>43</v>
@@ -13717,13 +13717,13 @@
         <v>2</v>
       </c>
       <c r="R143" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/25/2026 02:48 MDT</t>
+          <t>8/25/2026 03:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/25/2026 02:48 MDT</t>
+          <t>8/25/2026 03:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13801,22 +13801,22 @@
         <v>77</v>
       </c>
       <c r="O144" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R144" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S144" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="T144" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O145" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -13903,13 +13903,13 @@
         <v>5</v>
       </c>
       <c r="R145" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S145" t="n">
         <v>9</v>
       </c>
       <c r="T145" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13984,10 +13984,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O146" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13996,13 +13996,13 @@
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="S146" t="n">
         <v>3</v>
       </c>
       <c r="T146" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,10 +14077,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O147" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -14089,13 +14089,13 @@
         <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="S147" t="n">
         <v>6</v>
       </c>
       <c r="T147" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/25/2026 02:49 MDT</t>
+          <t>8/25/2026 03:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/25/2026 02:49 MDT</t>
+          <t>8/25/2026 03:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O148" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14182,13 +14182,13 @@
         <v>3</v>
       </c>
       <c r="R148" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T148" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/25/2026 02:59 MDT</t>
+          <t>8/25/2026 03:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/25/2026 02:59 MDT</t>
+          <t>8/25/2026 03:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14263,25 +14263,25 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O149" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T149" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/25/2026 02:57 MDT</t>
+          <t>8/25/2026 03:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/25/2026 02:57 MDT</t>
+          <t>8/25/2026 03:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O150" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -14374,7 +14374,7 @@
         <v>11</v>
       </c>
       <c r="T150" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,10 +14449,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O151" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -14461,13 +14461,13 @@
         <v>7</v>
       </c>
       <c r="R151" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S151" t="n">
         <v>9</v>
       </c>
       <c r="T151" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,25 +14542,25 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O152" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R152" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T152" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14638,7 +14638,7 @@
         <v>88</v>
       </c>
       <c r="O153" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -14647,13 +14647,13 @@
         <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="S153" t="n">
         <v>8</v>
       </c>
       <c r="T153" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/25/2026 02:53 MDT</t>
+          <t>8/25/2026 03:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,7 +14728,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O154" t="n">
         <v>39</v>
@@ -14740,13 +14740,13 @@
         <v>10</v>
       </c>
       <c r="R154" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S154" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T154" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/25/2026 02:52 MDT</t>
+          <t>8/25/2026 03:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14824,7 +14824,7 @@
         <v>84</v>
       </c>
       <c r="O155" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -14833,13 +14833,13 @@
         <v>2</v>
       </c>
       <c r="R155" t="n">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="S155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T155" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/25/2026 02:47 MDT</t>
+          <t>8/25/2026 03:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/25/2026 02:47 MDT</t>
+          <t>8/25/2026 03:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14914,10 +14914,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O156" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -14929,10 +14929,10 @@
         <v>200</v>
       </c>
       <c r="S156" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T156" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/25/2026 02:49 MDT</t>
+          <t>8/25/2026 03:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/25/2026 02:49 MDT</t>
+          <t>8/25/2026 03:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O157" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15019,13 +15019,13 @@
         <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S157" t="n">
         <v>7</v>
       </c>
       <c r="T157" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/25/2026 02:00 MDT</t>
+          <t>8/25/2026 03:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/25/2026 02:50 MDT</t>
+          <t>8/25/2026 03:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15103,7 +15103,7 @@
         <v>58</v>
       </c>
       <c r="O158" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -15112,13 +15112,13 @@
         <v>1</v>
       </c>
       <c r="R158" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="S158" t="n">
         <v>6</v>
       </c>
       <c r="T158" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/25/2026 03:42 MDT</t>
+          <t>8/25/2026 04:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/25/2026 03:42 MDT</t>
+          <t>8/25/2026 04:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/25/2026 03:42 MDT</t>
+          <t>8/25/2026 04:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -595,22 +595,22 @@
         <v>63</v>
       </c>
       <c r="O2" t="n">
+        <v>53</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
         <v>50</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>30</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/25/2026 03:42 MDT</t>
+          <t>8/25/2026 04:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/25/2026 03:42 MDT</t>
+          <t>8/25/2026 04:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/25/2026 03:42 MDT</t>
+          <t>8/25/2026 04:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -790,13 +790,13 @@
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O5" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -883,13 +883,13 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>346</v>
+        <v>275</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
         <v>47</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>66</v>
+        <v>254</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/25/2026 03:41 MDT</t>
+          <t>8/25/2026 04:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,25 +1057,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>146</v>
+        <v>299</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/25/2026 03:40 MDT</t>
+          <t>8/25/2026 04:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/25/2026 03:40 MDT</t>
+          <t>8/25/2026 04:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/25/2026 03:40 MDT</t>
+          <t>8/25/2026 04:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>321</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/25/2026 03:40 MDT</t>
+          <t>8/25/2026 04:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/25/2026 03:40 MDT</t>
+          <t>8/25/2026 04:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/25/2026 03:40 MDT</t>
+          <t>8/25/2026 04:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="S9" t="n">
         <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O12" t="n">
         <v>72</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/25/2026 03:39 MDT</t>
+          <t>8/25/2026 04:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O13" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S13" t="n">
         <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="O15" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>37</v>
+        <v>359</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1906,13 +1906,13 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O17" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,13 +1999,13 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O18" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>39</v>
+        <v>319</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2173,25 +2173,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O19" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,25 +2266,25 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O20" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/25/2026 03:38 MDT</t>
+          <t>8/25/2026 04:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,25 +2359,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O21" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,25 +2452,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>127</v>
+        <v>193</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>195</v>
+        <v>351</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2647,16 +2647,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S24" t="n">
         <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O25" t="n">
         <v>25</v>
@@ -2743,13 +2743,13 @@
         <v>15</v>
       </c>
       <c r="R25" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="S25" t="n">
         <v>23</v>
       </c>
       <c r="T25" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,25 +2824,25 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O27" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,25 +3010,25 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/25/2026 03:37 MDT</t>
+          <t>8/25/2026 04:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="S29" t="n">
         <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/25/2026 03:36 MDT</t>
+          <t>8/25/2026 04:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/25/2026 03:36 MDT</t>
+          <t>8/25/2026 04:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/25/2026 03:36 MDT</t>
+          <t>8/25/2026 04:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3199,13 +3199,13 @@
         <v>57</v>
       </c>
       <c r="O30" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
         <v>76</v>
@@ -3214,7 +3214,7 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/25/2026 03:36 MDT</t>
+          <t>8/25/2026 04:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/25/2026 03:36 MDT</t>
+          <t>8/25/2026 04:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/25/2026 03:36 MDT</t>
+          <t>8/25/2026 04:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="n">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/25/2026 03:35 MDT</t>
+          <t>8/25/2026 04:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/25/2026 03:35 MDT</t>
+          <t>8/25/2026 04:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/25/2026 03:35 MDT</t>
+          <t>8/25/2026 04:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3385,22 +3385,22 @@
         <v>55</v>
       </c>
       <c r="O32" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/25/2026 03:35 MDT</t>
+          <t>8/25/2026 04:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/25/2026 03:35 MDT</t>
+          <t>8/25/2026 04:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/25/2026 03:35 MDT</t>
+          <t>8/25/2026 04:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,25 +3475,25 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O33" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T33" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,25 +3568,25 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O34" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3664,22 +3664,22 @@
         <v>70</v>
       </c>
       <c r="O35" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>348</v>
+        <v>7</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
       </c>
       <c r="T35" t="n">
-        <v>30</v>
+        <v>354</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3766,13 +3766,13 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/25/2026 03:34 MDT</t>
+          <t>8/25/2026 04:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,25 +3847,25 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O37" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R37" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3952,13 +3952,13 @@
         <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4036,7 +4036,7 @@
         <v>56</v>
       </c>
       <c r="O39" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -4045,13 +4045,13 @@
         <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O40" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>272</v>
+        <v>350</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T40" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -4231,13 +4231,13 @@
         <v>15</v>
       </c>
       <c r="R41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S41" t="n">
         <v>21</v>
       </c>
       <c r="T41" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,25 +4312,25 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/25/2026 03:33 MDT</t>
+          <t>8/25/2026 04:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4408,7 +4408,7 @@
         <v>67</v>
       </c>
       <c r="O43" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -4417,13 +4417,13 @@
         <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T43" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/25/2026 03:32 MDT</t>
+          <t>8/25/2026 04:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/25/2026 03:32 MDT</t>
+          <t>8/25/2026 04:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/25/2026 03:32 MDT</t>
+          <t>8/25/2026 04:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O44" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="n">
         <v>8</v>
-      </c>
-      <c r="T44" t="n">
-        <v>47</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/25/2026 03:28 MDT</t>
+          <t>8/25/2026 04:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/25/2026 03:28 MDT</t>
+          <t>8/25/2026 04:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/25/2026 03:28 MDT</t>
+          <t>8/25/2026 04:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,25 +4591,25 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O45" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4687,7 +4687,7 @@
         <v>66</v>
       </c>
       <c r="O46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4696,13 +4696,13 @@
         <v>4</v>
       </c>
       <c r="R46" t="n">
+        <v>83</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="n">
         <v>87</v>
-      </c>
-      <c r="S46" t="n">
-        <v>6</v>
-      </c>
-      <c r="T46" t="n">
-        <v>78</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O47" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/25/2026 03:27 MDT</t>
+          <t>8/25/2026 04:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O48" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4882,13 +4882,13 @@
         <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T48" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4966,7 +4966,7 @@
         <v>85</v>
       </c>
       <c r="O49" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,25 +5056,25 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="S50" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T50" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/25/2026 03:26 MDT</t>
+          <t>8/25/2026 04:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O51" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>11</v>
+        <v>305</v>
       </c>
       <c r="S51" t="n">
         <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>30</v>
+        <v>353</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/25/2026 03:25 MDT</t>
+          <t>8/25/2026 04:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/25/2026 03:25 MDT</t>
+          <t>8/25/2026 04:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/25/2026 03:25 MDT</t>
+          <t>8/25/2026 04:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O52" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/25/2026 03:24 MDT</t>
+          <t>8/25/2026 04:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/25/2026 03:24 MDT</t>
+          <t>8/25/2026 04:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/25/2026 03:24 MDT</t>
+          <t>8/25/2026 04:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5353,7 +5353,7 @@
         <v>19</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5428,25 +5428,25 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O54" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="S54" t="n">
         <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O55" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T55" t="n">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O56" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -5626,13 +5626,13 @@
         <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T56" t="n">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/25/2026 03:23 MDT</t>
+          <t>8/25/2026 04:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O57" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -5719,13 +5719,13 @@
         <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T57" t="n">
-        <v>353</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/25/2026 03:22 MDT</t>
+          <t>8/25/2026 04:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/25/2026 03:22 MDT</t>
+          <t>8/25/2026 04:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/25/2026 03:22 MDT</t>
+          <t>8/25/2026 04:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,25 +5800,25 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O58" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="S58" t="n">
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/25/2026 03:22 MDT</t>
+          <t>8/25/2026 04:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/25/2026 03:22 MDT</t>
+          <t>8/25/2026 04:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/25/2026 03:22 MDT</t>
+          <t>8/25/2026 04:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5893,25 +5893,25 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O59" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T59" t="n">
-        <v>6</v>
+        <v>346</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/25/2026 03:20 MDT</t>
+          <t>8/25/2026 04:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/25/2026 03:20 MDT</t>
+          <t>8/25/2026 04:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/25/2026 03:20 MDT</t>
+          <t>8/25/2026 04:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5989,19 +5989,19 @@
         <v>73</v>
       </c>
       <c r="O60" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R60" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
         <v>329</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/25/2026 03:20 MDT</t>
+          <t>8/25/2026 04:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/25/2026 03:20 MDT</t>
+          <t>8/25/2026 04:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/25/2026 03:20 MDT</t>
+          <t>8/25/2026 04:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6079,25 +6079,25 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O61" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>278</v>
+        <v>26</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O62" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -6184,13 +6184,13 @@
         <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
       </c>
       <c r="T62" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O63" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
+        <v>19</v>
+      </c>
+      <c r="R63" t="n">
+        <v>14</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="n">
         <v>18</v>
-      </c>
-      <c r="R63" t="n">
-        <v>11</v>
-      </c>
-      <c r="S63" t="n">
-        <v>27</v>
-      </c>
-      <c r="T63" t="n">
-        <v>19</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,25 +6358,25 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O64" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
       </c>
       <c r="T64" t="n">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/25/2026 03:19 MDT</t>
+          <t>8/25/2026 04:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6463,13 +6463,13 @@
         <v>6</v>
       </c>
       <c r="R65" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S65" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/25/2026 03:17 MDT</t>
+          <t>8/25/2026 04:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/25/2026 03:17 MDT</t>
+          <t>8/25/2026 04:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/25/2026 03:17 MDT</t>
+          <t>8/25/2026 04:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6544,25 +6544,25 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O66" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R66" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T66" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6640,7 +6640,7 @@
         <v>61</v>
       </c>
       <c r="O67" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -6649,13 +6649,13 @@
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O68" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,25 +6823,25 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O69" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6916,25 +6916,25 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O70" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T70" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/25/2026 03:16 MDT</t>
+          <t>8/25/2026 04:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,25 +7009,25 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O71" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="n">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/25/2026 03:15 MDT</t>
+          <t>8/25/2026 04:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/25/2026 03:15 MDT</t>
+          <t>8/25/2026 04:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/25/2026 03:15 MDT</t>
+          <t>8/25/2026 04:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O72" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -7114,13 +7114,13 @@
         <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T72" t="n">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O73" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -7207,13 +7207,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,25 +7288,25 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O74" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>345</v>
+        <v>36</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T74" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O75" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -7393,13 +7393,13 @@
         <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T75" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,25 +7474,25 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O76" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R76" t="n">
-        <v>207</v>
+        <v>290</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T76" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7570,22 +7570,22 @@
         <v>72</v>
       </c>
       <c r="O77" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R77" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T77" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/25/2026 03:14 MDT</t>
+          <t>8/25/2026 04:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7669,16 +7669,16 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
       </c>
       <c r="T78" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O79" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -7765,13 +7765,13 @@
         <v>7</v>
       </c>
       <c r="R79" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T79" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O80" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>352</v>
+        <v>68</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T80" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O81" t="n">
         <v>37</v>
@@ -7951,13 +7951,13 @@
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="S81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T81" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O82" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -8044,13 +8044,13 @@
         <v>6</v>
       </c>
       <c r="R82" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="S82" t="n">
         <v>11</v>
       </c>
       <c r="T82" t="n">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/25/2026 03:13 MDT</t>
+          <t>8/25/2026 04:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O83" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="S83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T83" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/25/2026 03:12 MDT</t>
+          <t>8/25/2026 04:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/25/2026 03:12 MDT</t>
+          <t>8/25/2026 04:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/25/2026 03:12 MDT</t>
+          <t>8/25/2026 04:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,25 +8218,25 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O84" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="S84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T84" t="n">
-        <v>327</v>
+        <v>45</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,25 +8311,25 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O85" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>330</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8407,7 +8407,7 @@
         <v>68</v>
       </c>
       <c r="O86" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>247</v>
+        <v>325</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T86" t="n">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8500,22 +8500,22 @@
         <v>87</v>
       </c>
       <c r="O87" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R87" t="n">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T87" t="n">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,25 +8590,25 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O88" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="S88" t="n">
         <v>6</v>
       </c>
       <c r="T88" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O89" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="S89" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T89" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/25/2026 03:11 MDT</t>
+          <t>8/25/2026 04:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O90" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>3</v>
       </c>
       <c r="R90" t="n">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T90" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/25/2026 03:09 MDT</t>
+          <t>8/25/2026 04:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/25/2026 03:09 MDT</t>
+          <t>8/25/2026 04:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/25/2026 03:09 MDT</t>
+          <t>8/25/2026 04:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8872,22 +8872,22 @@
         <v>53</v>
       </c>
       <c r="O91" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
       </c>
       <c r="T91" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/25/2026 03:09 MDT</t>
+          <t>8/25/2026 04:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/25/2026 03:09 MDT</t>
+          <t>8/25/2026 04:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/25/2026 03:09 MDT</t>
+          <t>8/25/2026 04:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8965,22 +8965,22 @@
         <v>74</v>
       </c>
       <c r="O92" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T92" t="n">
-        <v>334</v>
+        <v>9</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O93" t="n">
         <v>66</v>
@@ -9067,13 +9067,13 @@
         <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T93" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O94" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -9160,13 +9160,13 @@
         <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
       </c>
       <c r="T94" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9241,25 +9241,25 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O95" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T95" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9334,10 +9334,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O96" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O97" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -9439,13 +9439,13 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>319</v>
+        <v>66</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T97" t="n">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9520,25 +9520,25 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O98" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T98" t="n">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O99" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -9625,13 +9625,13 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>340</v>
+        <v>191</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T99" t="n">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/25/2026 03:08 MDT</t>
+          <t>8/25/2026 04:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9709,22 +9709,22 @@
         <v>76</v>
       </c>
       <c r="O100" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R100" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9799,25 +9799,25 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O101" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T101" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9901,16 +9901,16 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>350</v>
+        <v>39</v>
       </c>
       <c r="S102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T102" t="n">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O103" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -9997,13 +9997,13 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S103" t="n">
         <v>7</v>
       </c>
       <c r="T103" t="n">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/25/2026 03:07 MDT</t>
+          <t>8/25/2026 04:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O104" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -10090,13 +10090,13 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10174,7 +10174,7 @@
         <v>58</v>
       </c>
       <c r="O105" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T105" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10273,13 +10273,13 @@
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R106" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="S106" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T106" t="n">
         <v>263</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/25/2026 03:06 MDT</t>
+          <t>8/25/2026 04:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O107" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10450,25 +10450,25 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O108" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R108" t="n">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="S108" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T108" t="n">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O109" t="n">
         <v>40</v>
@@ -10552,16 +10552,16 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R109" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,10 +10636,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O110" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -10648,13 +10648,13 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>39</v>
+        <v>310</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T110" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,25 +10729,25 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O111" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R111" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="S111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T111" t="n">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/25/2026 03:05 MDT</t>
+          <t>8/25/2026 04:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,10 +10822,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O112" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -10834,13 +10834,13 @@
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="S112" t="n">
         <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>337</v>
+        <v>12</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/25/2026 03:04 MDT</t>
+          <t>8/25/2026 04:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/25/2026 03:04 MDT</t>
+          <t>8/25/2026 04:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/25/2026 03:04 MDT</t>
+          <t>8/25/2026 04:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,25 +10915,25 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O113" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T113" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/25/2026 03:04 MDT</t>
+          <t>8/25/2026 04:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/25/2026 03:04 MDT</t>
+          <t>8/25/2026 04:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/25/2026 03:04 MDT</t>
+          <t>8/25/2026 04:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11011,22 +11011,22 @@
         <v>63</v>
       </c>
       <c r="O114" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T114" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,25 +11101,25 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O115" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="S115" t="n">
         <v>6</v>
       </c>
       <c r="T115" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,25 +11194,25 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O116" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R116" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T116" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O117" t="n">
         <v>28</v>
@@ -11296,16 +11296,16 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R117" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T117" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,25 +11380,25 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O118" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="S118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T118" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,25 +11473,25 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O119" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R119" t="n">
-        <v>335</v>
+        <v>5</v>
       </c>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T119" t="n">
-        <v>336</v>
+        <v>49</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O120" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/25/2026 03:03 MDT</t>
+          <t>8/25/2026 04:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,25 +11659,25 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O121" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R121" t="n">
-        <v>1</v>
+        <v>354</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
       </c>
       <c r="T121" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,25 +11752,25 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O122" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>316</v>
+        <v>31</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11845,25 +11845,25 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O123" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="S123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T123" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/25/2026 03:02 MDT</t>
+          <t>8/25/2026 04:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O124" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="S124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T124" t="n">
-        <v>295</v>
+        <v>119</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,25 +12031,25 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O125" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R125" t="n">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="S125" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T125" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,25 +12124,25 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O126" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R126" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T126" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="O127" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="S127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T127" t="n">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/25/2026 03:01 MDT</t>
+          <t>8/25/2026 04:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12319,16 +12319,16 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S128" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T128" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,10 +12403,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O129" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -12415,13 +12415,13 @@
         <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O130" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -12508,13 +12508,13 @@
         <v>3</v>
       </c>
       <c r="R130" t="n">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="S130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T130" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O131" t="n">
         <v>83</v>
@@ -12601,13 +12601,13 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="S131" t="n">
         <v>2</v>
       </c>
       <c r="T131" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,25 +12682,25 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="O132" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R132" t="n">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T132" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,25 +12775,25 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O133" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R133" t="n">
         <v>220</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T133" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O134" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -12880,13 +12880,13 @@
         <v>3</v>
       </c>
       <c r="R134" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T134" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12964,22 +12964,22 @@
         <v>67</v>
       </c>
       <c r="O135" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="S135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T135" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O136" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -13066,7 +13066,7 @@
         <v>7</v>
       </c>
       <c r="R136" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="S136" t="n">
         <v>9</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/25/2026 03:49 MDT</t>
+          <t>8/25/2026 04:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/25/2026 03:49 MDT</t>
+          <t>8/25/2026 04:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O137" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>5</v>
       </c>
       <c r="R137" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="S137" t="n">
         <v>7</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/25/2026 03:59 MDT</t>
+          <t>8/25/2026 04:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/25/2026 03:59 MDT</t>
+          <t>8/25/2026 04:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13243,7 +13243,7 @@
         <v>71</v>
       </c>
       <c r="O138" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
@@ -13258,7 +13258,7 @@
         <v>9</v>
       </c>
       <c r="T138" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/25/2026 03:48 MDT</t>
+          <t>8/25/2026 04:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/25/2026 03:48 MDT</t>
+          <t>8/25/2026 04:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O139" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -13345,13 +13345,13 @@
         <v>2</v>
       </c>
       <c r="R139" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="S139" t="n">
         <v>6</v>
       </c>
       <c r="T139" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/25/2026 03:59 MDT</t>
+          <t>8/25/2026 04:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/25/2026 03:59 MDT</t>
+          <t>8/25/2026 04:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,16 +13426,16 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O140" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R140" t="n">
         <v>220</v>
@@ -13444,7 +13444,7 @@
         <v>5</v>
       </c>
       <c r="T140" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/25/2026 03:48 MDT</t>
+          <t>8/25/2026 04:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/25/2026 03:48 MDT</t>
+          <t>8/25/2026 04:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13531,7 +13531,7 @@
         <v>6</v>
       </c>
       <c r="R141" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="S141" t="n">
         <v>8</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,25 +13612,25 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O142" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R142" t="n">
         <v>310</v>
       </c>
       <c r="S142" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T142" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,7 +13705,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O143" t="n">
         <v>43</v>
@@ -13717,13 +13717,13 @@
         <v>2</v>
       </c>
       <c r="R143" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/25/2026 03:48 MDT</t>
+          <t>8/25/2026 04:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/25/2026 03:48 MDT</t>
+          <t>8/25/2026 04:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13798,7 +13798,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O144" t="n">
         <v>40</v>
@@ -13810,13 +13810,13 @@
         <v>11</v>
       </c>
       <c r="R144" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S144" t="n">
         <v>19</v>
       </c>
       <c r="T144" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O145" t="n">
         <v>49</v>
@@ -13903,13 +13903,13 @@
         <v>5</v>
       </c>
       <c r="R145" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="S145" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T145" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13996,13 +13996,13 @@
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T146" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,10 +14077,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O147" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -14089,13 +14089,13 @@
         <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="S147" t="n">
         <v>6</v>
       </c>
       <c r="T147" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/25/2026 03:49 MDT</t>
+          <t>8/25/2026 04:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/25/2026 03:49 MDT</t>
+          <t>8/25/2026 04:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O148" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14188,7 +14188,7 @@
         <v>9</v>
       </c>
       <c r="T148" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/25/2026 03:59 MDT</t>
+          <t>8/25/2026 04:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/25/2026 03:59 MDT</t>
+          <t>8/25/2026 04:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14263,10 +14263,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O149" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
@@ -14278,10 +14278,10 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T149" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/25/2026 03:57 MDT</t>
+          <t>8/25/2026 04:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/25/2026 03:57 MDT</t>
+          <t>8/25/2026 04:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O150" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -14371,10 +14371,10 @@
         <v>20</v>
       </c>
       <c r="S150" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T150" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,22 +14449,22 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O151" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R151" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="S151" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T151" t="n">
         <v>37</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O152" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -14554,7 +14554,7 @@
         <v>5</v>
       </c>
       <c r="R152" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="S152" t="n">
         <v>7</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,10 +14635,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O153" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         <v>8</v>
       </c>
       <c r="T153" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/25/2026 03:53 MDT</t>
+          <t>8/25/2026 04:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,25 +14728,25 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O154" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R154" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S154" t="n">
         <v>17</v>
       </c>
       <c r="T154" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/25/2026 03:52 MDT</t>
+          <t>8/25/2026 04:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14821,25 +14821,25 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O155" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
       </c>
       <c r="T155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/25/2026 03:47 MDT</t>
+          <t>8/25/2026 04:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/25/2026 03:47 MDT</t>
+          <t>8/25/2026 04:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14923,16 +14923,16 @@
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="S156" t="n">
         <v>6</v>
       </c>
       <c r="T156" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/25/2026 03:49 MDT</t>
+          <t>8/25/2026 04:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/25/2026 03:49 MDT</t>
+          <t>8/25/2026 04:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O157" t="n">
         <v>71</v>
@@ -15019,7 +15019,7 @@
         <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S157" t="n">
         <v>7</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/25/2026 03:00 MDT</t>
+          <t>8/25/2026 04:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/25/2026 03:50 MDT</t>
+          <t>8/25/2026 04:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15100,10 +15100,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O158" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -15112,13 +15112,13 @@
         <v>1</v>
       </c>
       <c r="R158" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="S158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T158" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/25/2026 04:42 MDT</t>
+          <t>8/25/2026 05:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/25/2026 04:42 MDT</t>
+          <t>8/25/2026 05:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/25/2026 04:42 MDT</t>
+          <t>8/25/2026 05:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/25/2026 04:42 MDT</t>
+          <t>8/25/2026 05:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/25/2026 04:42 MDT</t>
+          <t>8/25/2026 05:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/25/2026 04:42 MDT</t>
+          <t>8/25/2026 05:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>31</v>
+        <v>350</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -880,16 +880,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/25/2026 04:41 MDT</t>
+          <t>8/25/2026 05:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,25 +1057,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>292</v>
+        <v>245</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/25/2026 04:40 MDT</t>
+          <t>8/25/2026 05:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/25/2026 04:40 MDT</t>
+          <t>8/25/2026 05:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/25/2026 04:40 MDT</t>
+          <t>8/25/2026 05:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>352</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/25/2026 04:40 MDT</t>
+          <t>8/25/2026 05:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/25/2026 04:40 MDT</t>
+          <t>8/25/2026 05:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/25/2026 04:40 MDT</t>
+          <t>8/25/2026 05:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T9" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T11" t="n">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1525,7 +1525,7 @@
         <v>52</v>
       </c>
       <c r="O12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/25/2026 04:39 MDT</t>
+          <t>8/25/2026 05:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1624,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="S13" t="n">
         <v>6</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1711,7 +1711,7 @@
         <v>52</v>
       </c>
       <c r="O14" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O15" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1903,16 +1903,16 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="O17" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>268</v>
+        <v>141</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>63</v>
       </c>
       <c r="O18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="S18" t="n">
         <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2176,22 +2176,22 @@
         <v>64</v>
       </c>
       <c r="O19" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,25 +2266,25 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="O20" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/25/2026 04:38 MDT</t>
+          <t>8/25/2026 05:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,25 +2359,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>265</v>
+        <v>118</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>251</v>
+        <v>100</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O22" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2464,13 +2464,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>194</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>193</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>351</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2641,7 +2641,7 @@
         <v>65</v>
       </c>
       <c r="O24" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,13 +2650,13 @@
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>346</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,25 +2731,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O25" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>162</v>
+        <v>321</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O26" t="n">
         <v>38</v>
@@ -2833,16 +2833,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
+        <v>18</v>
+      </c>
+      <c r="S27" t="n">
         <v>22</v>
       </c>
-      <c r="S27" t="n">
-        <v>19</v>
-      </c>
       <c r="T27" t="n">
-        <v>23</v>
+        <v>347</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3019,16 +3019,16 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T28" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/25/2026 04:37 MDT</t>
+          <t>8/25/2026 05:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>77</v>
       </c>
       <c r="O29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3115,13 +3115,13 @@
         <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/25/2026 04:36 MDT</t>
+          <t>8/25/2026 05:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/25/2026 04:36 MDT</t>
+          <t>8/25/2026 05:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/25/2026 04:36 MDT</t>
+          <t>8/25/2026 05:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,25 +3196,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O30" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/25/2026 04:36 MDT</t>
+          <t>8/25/2026 05:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/25/2026 04:36 MDT</t>
+          <t>8/25/2026 05:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/25/2026 04:36 MDT</t>
+          <t>8/25/2026 05:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T31" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/25/2026 04:35 MDT</t>
+          <t>8/25/2026 05:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/25/2026 04:35 MDT</t>
+          <t>8/25/2026 05:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/25/2026 04:35 MDT</t>
+          <t>8/25/2026 05:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3382,25 +3382,25 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O32" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="S32" t="n">
         <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/25/2026 04:35 MDT</t>
+          <t>8/25/2026 05:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/25/2026 04:35 MDT</t>
+          <t>8/25/2026 05:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/25/2026 04:35 MDT</t>
+          <t>8/25/2026 05:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,25 +3475,25 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O33" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3568,25 +3568,25 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O34" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
+        <v>122</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
         <v>106</v>
-      </c>
-      <c r="S34" t="n">
-        <v>6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>118</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O35" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3673,13 +3673,13 @@
         <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T35" t="n">
-        <v>354</v>
+        <v>52</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3754,25 +3754,25 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O36" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/25/2026 04:34 MDT</t>
+          <t>8/25/2026 05:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,25 +3847,25 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O37" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R37" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3943,22 +3943,22 @@
         <v>77</v>
       </c>
       <c r="O38" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O39" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -4045,13 +4045,13 @@
         <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O40" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="S40" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R41" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S41" t="n">
         <v>21</v>
       </c>
       <c r="T41" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,25 +4312,25 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O42" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/25/2026 04:33 MDT</t>
+          <t>8/25/2026 05:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4405,25 +4405,25 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O43" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="S43" t="n">
         <v>7</v>
       </c>
       <c r="T43" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/25/2026 04:32 MDT</t>
+          <t>8/25/2026 05:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/25/2026 04:32 MDT</t>
+          <t>8/25/2026 05:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/25/2026 04:32 MDT</t>
+          <t>8/25/2026 05:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>65</v>
       </c>
       <c r="O44" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -4510,13 +4510,13 @@
         <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/25/2026 04:28 MDT</t>
+          <t>8/25/2026 05:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/25/2026 04:28 MDT</t>
+          <t>8/25/2026 05:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/25/2026 04:28 MDT</t>
+          <t>8/25/2026 05:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O45" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4603,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4696,13 +4696,13 @@
         <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4777,25 +4777,25 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O47" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/25/2026 04:27 MDT</t>
+          <t>8/25/2026 05:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4873,22 +4873,22 @@
         <v>68</v>
       </c>
       <c r="O48" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4966,7 +4966,7 @@
         <v>85</v>
       </c>
       <c r="O49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O50" t="n">
         <v>21</v>
@@ -5065,16 +5065,16 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R50" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/25/2026 04:26 MDT</t>
+          <t>8/25/2026 05:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O51" t="n">
         <v>42</v>
@@ -5161,13 +5161,13 @@
         <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>305</v>
+        <v>3</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="n">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/25/2026 04:25 MDT</t>
+          <t>8/25/2026 05:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/25/2026 04:25 MDT</t>
+          <t>8/25/2026 05:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/25/2026 04:25 MDT</t>
+          <t>8/25/2026 05:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5242,25 +5242,25 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O52" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>316</v>
+      </c>
+      <c r="S52" t="n">
         <v>5</v>
       </c>
-      <c r="R52" t="n">
-        <v>305</v>
-      </c>
-      <c r="S52" t="n">
-        <v>6</v>
-      </c>
       <c r="T52" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/25/2026 04:24 MDT</t>
+          <t>8/25/2026 05:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/25/2026 04:24 MDT</t>
+          <t>8/25/2026 05:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/25/2026 04:24 MDT</t>
+          <t>8/25/2026 05:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5338,22 +5338,22 @@
         <v>68</v>
       </c>
       <c r="O53" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="S53" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T53" t="n">
-        <v>43</v>
+        <v>352</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5431,22 +5431,22 @@
         <v>88</v>
       </c>
       <c r="O54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O55" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>68</v>
+        <v>224</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5614,25 +5614,25 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O56" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/25/2026 04:23 MDT</t>
+          <t>8/25/2026 05:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5710,7 +5710,7 @@
         <v>66</v>
       </c>
       <c r="O57" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -5719,13 +5719,13 @@
         <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>353</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/25/2026 04:22 MDT</t>
+          <t>8/25/2026 05:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/25/2026 04:22 MDT</t>
+          <t>8/25/2026 05:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/25/2026 04:22 MDT</t>
+          <t>8/25/2026 05:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O58" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5812,13 +5812,13 @@
         <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="n">
-        <v>60</v>
+        <v>203</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/25/2026 04:22 MDT</t>
+          <t>8/25/2026 05:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/25/2026 04:22 MDT</t>
+          <t>8/25/2026 05:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/25/2026 04:22 MDT</t>
+          <t>8/25/2026 05:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5893,25 +5893,25 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T59" t="n">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/25/2026 04:20 MDT</t>
+          <t>8/25/2026 05:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/25/2026 04:20 MDT</t>
+          <t>8/25/2026 05:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/25/2026 04:20 MDT</t>
+          <t>8/25/2026 05:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5986,25 +5986,25 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O60" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T60" t="n">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/25/2026 04:20 MDT</t>
+          <t>8/25/2026 05:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/25/2026 04:20 MDT</t>
+          <t>8/25/2026 05:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/25/2026 04:20 MDT</t>
+          <t>8/25/2026 05:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6091,13 +6091,13 @@
         <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>26</v>
+        <v>359</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T61" t="n">
-        <v>25</v>
+        <v>359</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,25 +6172,25 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O62" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
       </c>
       <c r="T62" t="n">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O63" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R63" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="T63" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,25 +6358,25 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O64" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T64" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/25/2026 04:19 MDT</t>
+          <t>8/25/2026 05:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6460,16 +6460,16 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
         <v>22</v>
       </c>
       <c r="S65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/25/2026 04:17 MDT</t>
+          <t>8/25/2026 05:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/25/2026 04:17 MDT</t>
+          <t>8/25/2026 05:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/25/2026 04:17 MDT</t>
+          <t>8/25/2026 05:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6544,25 +6544,25 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O66" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6637,25 +6637,25 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O67" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T67" t="n">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O68" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6826,22 +6826,22 @@
         <v>60</v>
       </c>
       <c r="O69" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
       </c>
       <c r="T69" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6919,22 +6919,22 @@
         <v>90</v>
       </c>
       <c r="O70" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
+        <v>3</v>
+      </c>
+      <c r="R70" t="n">
+        <v>68</v>
+      </c>
+      <c r="S70" t="n">
         <v>4</v>
       </c>
-      <c r="R70" t="n">
-        <v>113</v>
-      </c>
-      <c r="S70" t="n">
-        <v>7</v>
-      </c>
       <c r="T70" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/25/2026 04:16 MDT</t>
+          <t>8/25/2026 05:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O71" t="n">
         <v>47</v>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
+        <v>3</v>
+      </c>
+      <c r="R71" t="n">
         <v>2</v>
       </c>
-      <c r="R71" t="n">
-        <v>346</v>
-      </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T71" t="n">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/25/2026 04:15 MDT</t>
+          <t>8/25/2026 05:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/25/2026 04:15 MDT</t>
+          <t>8/25/2026 05:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/25/2026 04:15 MDT</t>
+          <t>8/25/2026 05:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,25 +7102,25 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O72" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,25 +7195,25 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O73" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7288,25 +7288,25 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O74" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T74" t="n">
-        <v>293</v>
+        <v>34</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O75" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,25 +7474,25 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O76" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>290</v>
+        <v>342</v>
       </c>
       <c r="S76" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T76" t="n">
-        <v>203</v>
+        <v>292</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O77" t="n">
         <v>46</v>
@@ -7576,16 +7576,16 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
       </c>
       <c r="T77" t="n">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/25/2026 04:14 MDT</t>
+          <t>8/25/2026 05:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O78" t="n">
         <v>44</v>
@@ -7672,13 +7672,13 @@
         <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O79" t="n">
         <v>58</v>
@@ -7762,16 +7762,16 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R79" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T79" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O80" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>68</v>
+        <v>175</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T80" t="n">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7942,7 +7942,7 @@
         <v>68</v>
       </c>
       <c r="O81" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -7951,13 +7951,13 @@
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T81" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8032,25 +8032,25 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O82" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R82" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T82" t="n">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/25/2026 04:13 MDT</t>
+          <t>8/25/2026 05:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O83" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/25/2026 04:12 MDT</t>
+          <t>8/25/2026 05:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/25/2026 04:12 MDT</t>
+          <t>8/25/2026 05:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/25/2026 04:12 MDT</t>
+          <t>8/25/2026 05:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8221,22 +8221,22 @@
         <v>59</v>
       </c>
       <c r="O84" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
       </c>
       <c r="T84" t="n">
-        <v>45</v>
+        <v>359</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,25 +8311,25 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O85" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R85" t="n">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="S85" t="n">
         <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>330</v>
+        <v>14</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O86" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R86" t="n">
-        <v>325</v>
+        <v>164</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="n">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,25 +8497,25 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O87" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R87" t="n">
-        <v>325</v>
+        <v>23</v>
       </c>
       <c r="S87" t="n">
         <v>12</v>
       </c>
       <c r="T87" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8593,22 +8593,22 @@
         <v>52</v>
       </c>
       <c r="O88" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T88" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O89" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T89" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/25/2026 04:11 MDT</t>
+          <t>8/25/2026 05:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8785,16 +8785,16 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/25/2026 04:09 MDT</t>
+          <t>8/25/2026 05:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/25/2026 04:09 MDT</t>
+          <t>8/25/2026 05:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/25/2026 04:09 MDT</t>
+          <t>8/25/2026 05:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8869,25 +8869,25 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O91" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T91" t="n">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/25/2026 04:09 MDT</t>
+          <t>8/25/2026 05:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/25/2026 04:09 MDT</t>
+          <t>8/25/2026 05:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/25/2026 04:09 MDT</t>
+          <t>8/25/2026 05:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8965,7 +8965,7 @@
         <v>74</v>
       </c>
       <c r="O92" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -8974,13 +8974,13 @@
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T92" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O93" t="n">
         <v>66</v>
@@ -9064,16 +9064,16 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="S93" t="n">
         <v>6</v>
       </c>
       <c r="T93" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O94" t="n">
         <v>50</v>
@@ -9157,16 +9157,16 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9253,13 +9253,13 @@
         <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T95" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9334,16 +9334,16 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O96" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>56</v>
@@ -9352,7 +9352,7 @@
         <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9439,13 +9439,13 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="S97" t="n">
         <v>2</v>
       </c>
       <c r="T97" t="n">
-        <v>259</v>
+        <v>14</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9520,25 +9520,25 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O98" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T98" t="n">
-        <v>254</v>
+        <v>4</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O99" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -9625,13 +9625,13 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T99" t="n">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/25/2026 04:08 MDT</t>
+          <t>8/25/2026 05:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9706,25 +9706,25 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O100" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="S100" t="n">
         <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O101" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -9811,13 +9811,13 @@
         <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="S101" t="n">
         <v>7</v>
       </c>
       <c r="T101" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,25 +9892,25 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O102" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T102" t="n">
-        <v>338</v>
+        <v>118</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O103" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R103" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S103" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T103" t="n">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/25/2026 04:07 MDT</t>
+          <t>8/25/2026 05:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O104" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -10090,13 +10090,13 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>356</v>
+        <v>145</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10171,25 +10171,25 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O105" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
       </c>
       <c r="T105" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10267,22 +10267,22 @@
         <v>83</v>
       </c>
       <c r="O106" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R106" t="n">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="S106" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T106" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/25/2026 04:06 MDT</t>
+          <t>8/25/2026 05:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O107" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="S107" t="n">
         <v>2</v>
       </c>
       <c r="T107" t="n">
-        <v>71</v>
+        <v>303</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10459,16 +10459,16 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R108" t="n">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="S108" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T108" t="n">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O109" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R109" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="S109" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T109" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10636,11 +10636,11 @@
         </is>
       </c>
       <c r="N110" t="n">
+        <v>58</v>
+      </c>
+      <c r="O110" t="n">
         <v>59</v>
       </c>
-      <c r="O110" t="n">
-        <v>56</v>
-      </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
@@ -10648,13 +10648,13 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>310</v>
+        <v>177</v>
       </c>
       <c r="S110" t="n">
+        <v>4</v>
+      </c>
+      <c r="T110" t="n">
         <v>2</v>
-      </c>
-      <c r="T110" t="n">
-        <v>83</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10729,25 +10729,25 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O111" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T111" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/25/2026 04:05 MDT</t>
+          <t>8/25/2026 05:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O112" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>239</v>
+        <v>340</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T112" t="n">
-        <v>12</v>
+        <v>359</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/25/2026 04:04 MDT</t>
+          <t>8/25/2026 05:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/25/2026 04:04 MDT</t>
+          <t>8/25/2026 05:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/25/2026 04:04 MDT</t>
+          <t>8/25/2026 05:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10918,7 +10918,7 @@
         <v>56</v>
       </c>
       <c r="O113" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -10927,13 +10927,13 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T113" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/25/2026 04:04 MDT</t>
+          <t>8/25/2026 05:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/25/2026 04:04 MDT</t>
+          <t>8/25/2026 05:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/25/2026 04:04 MDT</t>
+          <t>8/25/2026 05:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11008,25 +11008,25 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O114" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T114" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11101,10 +11101,10 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O115" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -11113,13 +11113,13 @@
         <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="S115" t="n">
         <v>6</v>
       </c>
       <c r="T115" t="n">
-        <v>344</v>
+        <v>67</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,25 +11194,25 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O116" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="S116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T116" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11296,16 +11296,16 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R117" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S117" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T117" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,10 +11380,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O118" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -11392,13 +11392,13 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="S118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T118" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,10 +11473,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O119" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -11485,13 +11485,13 @@
         <v>2</v>
       </c>
       <c r="R119" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T119" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O120" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="S120" t="n">
         <v>2</v>
       </c>
       <c r="T120" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/25/2026 04:03 MDT</t>
+          <t>8/25/2026 05:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11668,16 +11668,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R121" t="n">
-        <v>354</v>
+        <v>2</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T121" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,25 +11752,25 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O122" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T122" t="n">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O123" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
@@ -11857,13 +11857,13 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T123" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/25/2026 04:02 MDT</t>
+          <t>8/25/2026 05:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11938,10 +11938,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O124" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="S124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T124" t="n">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12034,22 +12034,22 @@
         <v>64</v>
       </c>
       <c r="O125" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R125" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="S125" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T125" t="n">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O126" t="n">
         <v>24</v>
@@ -12136,13 +12136,13 @@
         <v>4</v>
       </c>
       <c r="R126" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T126" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O127" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R127" t="n">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="S127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T127" t="n">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/25/2026 04:01 MDT</t>
+          <t>8/25/2026 05:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12319,16 +12319,16 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R128" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S128" t="n">
         <v>17</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12403,10 +12403,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O129" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -12415,13 +12415,13 @@
         <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O130" t="n">
         <v>39</v>
@@ -12505,16 +12505,16 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R130" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T130" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O131" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -12601,13 +12601,13 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="S131" t="n">
         <v>2</v>
       </c>
       <c r="T131" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12694,13 +12694,13 @@
         <v>7</v>
       </c>
       <c r="R132" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S132" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T132" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12775,25 +12775,25 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O133" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R133" t="n">
         <v>220</v>
       </c>
       <c r="S133" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T133" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12883,10 +12883,10 @@
         <v>340</v>
       </c>
       <c r="S134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T134" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12973,13 +12973,13 @@
         <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>6</v>
       </c>
       <c r="T135" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O136" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -13066,7 +13066,7 @@
         <v>7</v>
       </c>
       <c r="R136" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="S136" t="n">
         <v>9</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/25/2026 04:49 MDT</t>
+          <t>8/25/2026 05:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/25/2026 04:49 MDT</t>
+          <t>8/25/2026 05:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O137" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>5</v>
       </c>
       <c r="R137" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="S137" t="n">
         <v>7</v>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/25/2026 04:59 MDT</t>
+          <t>8/25/2026 05:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/25/2026 04:59 MDT</t>
+          <t>8/25/2026 05:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O138" t="n">
         <v>31</v>
@@ -13249,16 +13249,16 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R138" t="n">
         <v>70</v>
       </c>
       <c r="S138" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T138" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/25/2026 04:48 MDT</t>
+          <t>8/25/2026 05:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/25/2026 04:48 MDT</t>
+          <t>8/25/2026 05:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13336,7 +13336,7 @@
         <v>88</v>
       </c>
       <c r="O139" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -13345,13 +13345,13 @@
         <v>2</v>
       </c>
       <c r="R139" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="S139" t="n">
         <v>6</v>
       </c>
       <c r="T139" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/25/2026 04:59 MDT</t>
+          <t>8/25/2026 05:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/25/2026 04:59 MDT</t>
+          <t>8/25/2026 05:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O140" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
@@ -13441,10 +13441,10 @@
         <v>220</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T140" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/25/2026 04:48 MDT</t>
+          <t>8/25/2026 05:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/25/2026 04:48 MDT</t>
+          <t>8/25/2026 05:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O141" t="n">
         <v>55</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O142" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -13627,10 +13627,10 @@
         <v>310</v>
       </c>
       <c r="S142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T142" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13705,25 +13705,25 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O143" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/25/2026 04:48 MDT</t>
+          <t>8/25/2026 05:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/25/2026 04:48 MDT</t>
+          <t>8/25/2026 05:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13798,16 +13798,16 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O144" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R144" t="n">
         <v>20</v>
@@ -13816,7 +13816,7 @@
         <v>19</v>
       </c>
       <c r="T144" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13891,25 +13891,25 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O145" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S145" t="n">
         <v>8</v>
       </c>
       <c r="T145" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13987,7 +13987,7 @@
         <v>62</v>
       </c>
       <c r="O146" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13996,13 +13996,13 @@
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="S146" t="n">
         <v>2</v>
       </c>
       <c r="T146" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14077,10 +14077,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O147" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -14089,10 +14089,10 @@
         <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="S147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T147" t="n">
         <v>18</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/25/2026 04:49 MDT</t>
+          <t>8/25/2026 05:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/25/2026 04:49 MDT</t>
+          <t>8/25/2026 05:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14173,7 +14173,7 @@
         <v>62</v>
       </c>
       <c r="O148" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -14188,7 +14188,7 @@
         <v>9</v>
       </c>
       <c r="T148" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/25/2026 04:59 MDT</t>
+          <t>8/25/2026 05:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/25/2026 04:59 MDT</t>
+          <t>8/25/2026 05:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O149" t="n">
         <v>67</v>
@@ -14281,7 +14281,7 @@
         <v>11</v>
       </c>
       <c r="T149" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/25/2026 04:57 MDT</t>
+          <t>8/25/2026 05:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/25/2026 04:57 MDT</t>
+          <t>8/25/2026 05:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14356,25 +14356,25 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O150" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R150" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S150" t="n">
         <v>9</v>
       </c>
       <c r="T150" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,10 +14449,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O151" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
         <v>6</v>
       </c>
       <c r="R151" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S151" t="n">
         <v>8</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O152" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14638,7 +14638,7 @@
         <v>86</v>
       </c>
       <c r="O153" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -14647,13 +14647,13 @@
         <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="S153" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T153" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/25/2026 04:53 MDT</t>
+          <t>8/25/2026 05:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14728,10 +14728,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O154" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -14740,13 +14740,13 @@
         <v>11</v>
       </c>
       <c r="R154" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S154" t="n">
         <v>17</v>
       </c>
       <c r="T154" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/25/2026 04:52 MDT</t>
+          <t>8/25/2026 05:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14833,13 +14833,13 @@
         <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
       </c>
       <c r="T155" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/25/2026 04:47 MDT</t>
+          <t>8/25/2026 05:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/25/2026 04:47 MDT</t>
+          <t>8/25/2026 05:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14914,10 +14914,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O156" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P156" t="n">
         <v>0</v>
@@ -14926,13 +14926,13 @@
         <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="S156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T156" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/25/2026 04:49 MDT</t>
+          <t>8/25/2026 05:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/25/2026 04:49 MDT</t>
+          <t>8/25/2026 05:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O157" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15019,7 +15019,7 @@
         <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S157" t="n">
         <v>7</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/25/2026 04:00 MDT</t>
+          <t>8/25/2026 05:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/25/2026 04:50 MDT</t>
+          <t>8/25/2026 05:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O158" t="n">
         <v>77</v>
@@ -15118,7 +15118,7 @@
         <v>5</v>
       </c>
       <c r="T158" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/25/2026 05:42 MDT</t>
+          <t>8/25/2026 06:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/25/2026 05:42 MDT</t>
+          <t>8/25/2026 06:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/25/2026 05:42 MDT</t>
+          <t>8/25/2026 06:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/25/2026 05:42 MDT</t>
+          <t>8/25/2026 06:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/25/2026 05:42 MDT</t>
+          <t>8/25/2026 06:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/25/2026 05:42 MDT</t>
+          <t>8/25/2026 06:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,28 +685,28 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>272</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>108</v>
+      </c>
+      <c r="U3" t="n">
         <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>300</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>350</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -781,25 +781,25 @@
         <v>58</v>
       </c>
       <c r="O4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -874,7 +874,7 @@
         <v>62</v>
       </c>
       <c r="O5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -883,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -967,7 +967,7 @@
         <v>59</v>
       </c>
       <c r="O6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/25/2026 05:41 MDT</t>
+          <t>8/25/2026 06:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,28 +1057,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O7" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>107</v>
+      </c>
+      <c r="S7" t="n">
         <v>7</v>
       </c>
-      <c r="R7" t="n">
-        <v>245</v>
-      </c>
-      <c r="S7" t="n">
-        <v>9</v>
-      </c>
       <c r="T7" t="n">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/25/2026 05:40 MDT</t>
+          <t>8/25/2026 06:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/25/2026 05:40 MDT</t>
+          <t>8/25/2026 06:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/25/2026 05:40 MDT</t>
+          <t>8/25/2026 06:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>357</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/25/2026 05:40 MDT</t>
+          <t>8/25/2026 06:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/25/2026 05:40 MDT</t>
+          <t>8/25/2026 06:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/25/2026 05:40 MDT</t>
+          <t>8/25/2026 06:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,28 +1243,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
+        <v>147</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19</v>
+      </c>
+      <c r="T9" t="n">
         <v>148</v>
       </c>
-      <c r="S9" t="n">
-        <v>17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>156</v>
-      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,28 +1336,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,28 +1429,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,25 +1522,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O12" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/25/2026 05:39 MDT</t>
+          <t>8/25/2026 06:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1627,13 +1627,13 @@
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O15" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>329</v>
+        <v>25</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T15" t="n">
-        <v>341</v>
+        <v>93</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,25 +1894,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O17" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,13 +1999,13 @@
         <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>63</v>
       </c>
       <c r="O18" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2092,16 +2092,16 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2182,16 +2182,16 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/25/2026 05:38 MDT</t>
+          <t>8/25/2026 06:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O21" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2371,16 +2371,16 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,28 +2452,28 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O22" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2548,25 +2548,25 @@
         <v>71</v>
       </c>
       <c r="O23" t="n">
+        <v>32</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
         <v>31</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>39</v>
-      </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2641,22 +2641,22 @@
         <v>65</v>
       </c>
       <c r="O24" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,28 +2731,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>135</v>
+      </c>
+      <c r="S25" t="n">
         <v>5</v>
       </c>
-      <c r="R25" t="n">
-        <v>321</v>
-      </c>
-      <c r="S25" t="n">
-        <v>22</v>
-      </c>
       <c r="T25" t="n">
-        <v>180</v>
+        <v>332</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2833,16 +2833,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2926,16 +2926,16 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T27" t="n">
-        <v>347</v>
+        <v>15</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O28" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3022,13 +3022,13 @@
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/25/2026 05:37 MDT</t>
+          <t>8/25/2026 06:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3115,13 +3115,13 @@
         <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/25/2026 05:36 MDT</t>
+          <t>8/25/2026 06:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/25/2026 05:36 MDT</t>
+          <t>8/25/2026 06:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/25/2026 05:36 MDT</t>
+          <t>8/25/2026 06:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,25 +3196,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O30" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/25/2026 05:36 MDT</t>
+          <t>8/25/2026 06:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/25/2026 05:36 MDT</t>
+          <t>8/25/2026 06:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/25/2026 05:36 MDT</t>
+          <t>8/25/2026 06:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,28 +3289,28 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R31" t="n">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T31" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/25/2026 05:35 MDT</t>
+          <t>8/25/2026 06:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/25/2026 05:35 MDT</t>
+          <t>8/25/2026 06:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/25/2026 05:35 MDT</t>
+          <t>8/25/2026 06:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O32" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -3397,10 +3397,10 @@
         <v>187</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/25/2026 05:35 MDT</t>
+          <t>8/25/2026 06:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/25/2026 05:35 MDT</t>
+          <t>8/25/2026 06:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/25/2026 05:35 MDT</t>
+          <t>8/25/2026 06:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,25 +3475,25 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O33" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
         <v>134</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3571,7 +3571,7 @@
         <v>49</v>
       </c>
       <c r="O34" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O35" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T35" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3754,25 +3754,25 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/25/2026 05:34 MDT</t>
+          <t>8/25/2026 06:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3850,22 +3850,22 @@
         <v>66</v>
       </c>
       <c r="O37" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3949,16 +3949,16 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4036,7 +4036,7 @@
         <v>57</v>
       </c>
       <c r="O39" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -4045,10 +4045,10 @@
         <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
         <v>132</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O40" t="n">
         <v>44</v>
@@ -4135,16 +4135,16 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R40" t="n">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T40" t="n">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O41" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R41" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="S41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T41" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4324,13 +4324,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10</v>
+        <v>145</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4376,27 +4376,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8/25/2026 05:33 MDT</t>
+          <t>8/25/2026 06:33 MDT</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4408,22 +4408,22 @@
         <v>68</v>
       </c>
       <c r="O43" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="S43" t="n">
         <v>7</v>
       </c>
       <c r="T43" t="n">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4469,27 +4469,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8/25/2026 05:32 MDT</t>
+          <t>8/25/2026 06:32 MDT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8/25/2026 05:32 MDT</t>
+          <t>8/25/2026 06:32 MDT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8/25/2026 05:32 MDT</t>
+          <t>8/25/2026 06:32 MDT</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O44" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4562,27 +4562,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8/25/2026 05:28 MDT</t>
+          <t>8/25/2026 06:28 MDT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8/25/2026 05:28 MDT</t>
+          <t>8/25/2026 06:28 MDT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/25/2026 05:28 MDT</t>
+          <t>8/25/2026 06:28 MDT</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O45" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -4603,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4696,13 +4696,13 @@
         <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="S46" t="n">
         <v>6</v>
       </c>
       <c r="T46" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4748,27 +4748,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4789,13 +4789,13 @@
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T47" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4841,27 +4841,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8/25/2026 05:27 MDT</t>
+          <t>8/25/2026 06:27 MDT</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4873,22 +4873,22 @@
         <v>68</v>
       </c>
       <c r="O48" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O49" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5027,27 +5027,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5056,25 +5056,25 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O50" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
+        <v>93</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="n">
         <v>111</v>
-      </c>
-      <c r="S50" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" t="n">
-        <v>124</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/25/2026 05:26 MDT</t>
+          <t>8/25/2026 06:26 MDT</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5149,25 +5149,25 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O51" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>3</v>
+        <v>354</v>
       </c>
       <c r="S51" t="n">
         <v>8</v>
       </c>
       <c r="T51" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5213,27 +5213,27 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8/25/2026 05:25 MDT</t>
+          <t>8/25/2026 06:25 MDT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8/25/2026 05:25 MDT</t>
+          <t>8/25/2026 06:25 MDT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>8/25/2026 05:25 MDT</t>
+          <t>8/25/2026 06:25 MDT</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5251,16 +5251,16 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T52" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5306,27 +5306,27 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8/25/2026 05:24 MDT</t>
+          <t>8/25/2026 06:24 MDT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8/25/2026 05:24 MDT</t>
+          <t>8/25/2026 06:24 MDT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>8/25/2026 05:24 MDT</t>
+          <t>8/25/2026 06:24 MDT</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O53" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -5347,13 +5347,13 @@
         <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>359</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5399,27 +5399,27 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5431,7 +5431,7 @@
         <v>88</v>
       </c>
       <c r="O54" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -5440,13 +5440,13 @@
         <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5492,27 +5492,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5521,25 +5521,25 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O55" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>224</v>
+        <v>164</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5585,27 +5585,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5623,16 +5623,16 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5678,27 +5678,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8/25/2026 05:23 MDT</t>
+          <t>8/25/2026 06:23 MDT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O57" t="n">
         <v>46</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T57" t="n">
-        <v>353</v>
+        <v>10</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8/25/2026 05:22 MDT</t>
+          <t>8/25/2026 06:22 MDT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8/25/2026 05:22 MDT</t>
+          <t>8/25/2026 06:22 MDT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/25/2026 05:22 MDT</t>
+          <t>8/25/2026 06:22 MDT</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5800,25 +5800,25 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O58" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5864,27 +5864,27 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8/25/2026 05:22 MDT</t>
+          <t>8/25/2026 06:22 MDT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8/25/2026 05:22 MDT</t>
+          <t>8/25/2026 06:22 MDT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>8/25/2026 05:22 MDT</t>
+          <t>8/25/2026 06:22 MDT</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O59" t="n">
         <v>36</v>
@@ -5902,16 +5902,16 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5957,27 +5957,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>8/25/2026 05:20 MDT</t>
+          <t>8/25/2026 06:20 MDT</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>8/25/2026 05:20 MDT</t>
+          <t>8/25/2026 06:20 MDT</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>8/25/2026 05:20 MDT</t>
+          <t>8/25/2026 06:20 MDT</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5998,13 +5998,13 @@
         <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="S60" t="n">
         <v>14</v>
       </c>
       <c r="T60" t="n">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6050,27 +6050,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>8/25/2026 05:20 MDT</t>
+          <t>8/25/2026 06:20 MDT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8/25/2026 05:20 MDT</t>
+          <t>8/25/2026 06:20 MDT</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>8/25/2026 05:20 MDT</t>
+          <t>8/25/2026 06:20 MDT</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6091,13 +6091,13 @@
         <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
       </c>
       <c r="T61" t="n">
-        <v>359</v>
+        <v>17</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O62" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -6184,13 +6184,13 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T62" t="n">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6236,27 +6236,27 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6265,25 +6265,25 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O63" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S63" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T63" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6358,25 +6358,25 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O64" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T64" t="n">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>8/25/2026 05:19 MDT</t>
+          <t>8/25/2026 06:19 MDT</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6466,7 +6466,7 @@
         <v>22</v>
       </c>
       <c r="S65" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T65" t="n">
         <v>5</v>
@@ -6515,27 +6515,27 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8/25/2026 05:17 MDT</t>
+          <t>8/25/2026 06:17 MDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8/25/2026 05:17 MDT</t>
+          <t>8/25/2026 06:17 MDT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>8/25/2026 05:17 MDT</t>
+          <t>8/25/2026 06:17 MDT</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O66" t="n">
         <v>54</v>
@@ -6553,16 +6553,16 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -6608,27 +6608,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6640,22 +6640,22 @@
         <v>60</v>
       </c>
       <c r="O67" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>281</v>
+        <v>12</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T67" t="n">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6701,27 +6701,27 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O68" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T68" t="n">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O69" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6887,27 +6887,27 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6925,16 +6925,16 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6980,27 +6980,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/25/2026 05:16 MDT</t>
+          <t>8/25/2026 06:16 MDT</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O71" t="n">
         <v>47</v>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T71" t="n">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -7073,27 +7073,27 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>8/25/2026 05:15 MDT</t>
+          <t>8/25/2026 06:15 MDT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>8/25/2026 05:15 MDT</t>
+          <t>8/25/2026 06:15 MDT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8/25/2026 05:15 MDT</t>
+          <t>8/25/2026 06:15 MDT</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7102,25 +7102,25 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O72" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T72" t="n">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7166,27 +7166,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O73" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -7207,13 +7207,13 @@
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T73" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -7259,27 +7259,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7291,22 +7291,22 @@
         <v>79</v>
       </c>
       <c r="O74" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T74" t="n">
-        <v>34</v>
+        <v>306</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7352,27 +7352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7381,25 +7381,25 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O75" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R75" t="n">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T75" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7445,27 +7445,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O76" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>342</v>
+        <v>93</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7538,27 +7538,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7567,16 +7567,16 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O77" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R77" t="n">
         <v>152</v>
@@ -7585,7 +7585,7 @@
         <v>8</v>
       </c>
       <c r="T77" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7631,27 +7631,27 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>8/25/2026 05:14 MDT</t>
+          <t>8/25/2026 06:14 MDT</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7660,25 +7660,25 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O78" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R78" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T78" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O79" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -7765,13 +7765,13 @@
         <v>8</v>
       </c>
       <c r="R79" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T79" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O80" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="S80" t="n">
         <v>6</v>
       </c>
       <c r="T80" t="n">
-        <v>261</v>
+        <v>155</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7942,7 +7942,7 @@
         <v>68</v>
       </c>
       <c r="O81" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -7951,10 +7951,10 @@
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T81" t="n">
         <v>97</v>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8041,16 +8041,16 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R82" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T82" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -8096,27 +8096,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/25/2026 05:13 MDT</t>
+          <t>8/25/2026 06:13 MDT</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O83" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="S83" t="n">
         <v>2</v>
       </c>
       <c r="T83" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -8189,27 +8189,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8/25/2026 05:12 MDT</t>
+          <t>8/25/2026 06:12 MDT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8/25/2026 05:12 MDT</t>
+          <t>8/25/2026 06:12 MDT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>8/25/2026 05:12 MDT</t>
+          <t>8/25/2026 06:12 MDT</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O84" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -8282,27 +8282,27 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8311,25 +8311,25 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O85" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="S85" t="n">
         <v>6</v>
       </c>
       <c r="T85" t="n">
-        <v>14</v>
+        <v>343</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -8375,27 +8375,27 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8404,25 +8404,25 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="O86" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R86" t="n">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -8468,27 +8468,27 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8497,25 +8497,25 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O87" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>351</v>
+      </c>
+      <c r="S87" t="n">
         <v>4</v>
       </c>
-      <c r="R87" t="n">
-        <v>23</v>
-      </c>
-      <c r="S87" t="n">
-        <v>12</v>
-      </c>
       <c r="T87" t="n">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8561,27 +8561,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8590,25 +8590,25 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O88" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T88" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8654,27 +8654,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8683,25 +8683,25 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O89" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
-        <v>349</v>
+        <v>27</v>
       </c>
       <c r="S89" t="n">
         <v>6</v>
       </c>
       <c r="T89" t="n">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8747,27 +8747,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>8/25/2026 05:11 MDT</t>
+          <t>8/25/2026 06:11 MDT</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O90" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T90" t="n">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -8840,27 +8840,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8/25/2026 05:09 MDT</t>
+          <t>8/25/2026 06:09 MDT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>8/25/2026 05:09 MDT</t>
+          <t>8/25/2026 06:09 MDT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>8/25/2026 05:09 MDT</t>
+          <t>8/25/2026 06:09 MDT</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O91" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -8881,13 +8881,13 @@
         <v>3</v>
       </c>
       <c r="R91" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T91" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8933,27 +8933,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8/25/2026 05:09 MDT</t>
+          <t>8/25/2026 06:09 MDT</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>8/25/2026 05:09 MDT</t>
+          <t>8/25/2026 06:09 MDT</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>8/25/2026 05:09 MDT</t>
+          <t>8/25/2026 06:09 MDT</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O92" t="n">
         <v>33</v>
@@ -8974,13 +8974,13 @@
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="S92" t="n">
         <v>6</v>
       </c>
       <c r="T92" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9026,27 +9026,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9055,22 +9055,22 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O93" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T93" t="n">
         <v>195</v>
@@ -9119,27 +9119,27 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9148,25 +9148,25 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O94" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
       </c>
       <c r="T94" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9212,27 +9212,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="O95" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -9253,13 +9253,13 @@
         <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T95" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9305,27 +9305,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9337,7 +9337,7 @@
         <v>48</v>
       </c>
       <c r="O96" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
       </c>
       <c r="T96" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9398,27 +9398,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9427,25 +9427,25 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O97" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9491,27 +9491,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -9523,7 +9523,7 @@
         <v>57</v>
       </c>
       <c r="O98" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
@@ -9532,13 +9532,13 @@
         <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T98" t="n">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9584,27 +9584,27 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9616,19 +9616,19 @@
         <v>59</v>
       </c>
       <c r="O99" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T99" t="n">
         <v>278</v>
@@ -9677,27 +9677,27 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>8/25/2026 05:08 MDT</t>
+          <t>8/25/2026 06:08 MDT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9706,25 +9706,25 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O100" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
         <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9770,27 +9770,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9808,16 +9808,16 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R101" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S101" t="n">
         <v>7</v>
       </c>
       <c r="T101" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9863,27 +9863,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9892,25 +9892,25 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O102" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T102" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9956,27 +9956,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9985,25 +9985,25 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O103" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R103" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="S103" t="n">
         <v>6</v>
       </c>
       <c r="T103" t="n">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10049,27 +10049,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>8/25/2026 05:07 MDT</t>
+          <t>8/25/2026 06:07 MDT</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O104" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -10090,13 +10090,13 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
       </c>
       <c r="T104" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10171,10 +10171,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O105" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -10183,13 +10183,13 @@
         <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
       </c>
       <c r="T105" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10235,27 +10235,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10267,22 +10267,22 @@
         <v>83</v>
       </c>
       <c r="O106" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R106" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S106" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T106" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10328,27 +10328,27 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>8/25/2026 05:06 MDT</t>
+          <t>8/25/2026 06:06 MDT</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O107" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>303</v>
+        <v>67</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10421,27 +10421,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10450,25 +10450,25 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O108" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R108" t="n">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="S108" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T108" t="n">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10514,27 +10514,27 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10543,25 +10543,25 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O109" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R109" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="S109" t="n">
         <v>12</v>
       </c>
       <c r="T109" t="n">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10607,27 +10607,27 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -10648,13 +10648,13 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T110" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10700,27 +10700,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10738,16 +10738,16 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R111" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="S111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T111" t="n">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10793,27 +10793,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>8/25/2026 05:05 MDT</t>
+          <t>8/25/2026 06:05 MDT</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10822,25 +10822,25 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O112" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>340</v>
+        <v>72</v>
       </c>
       <c r="S112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T112" t="n">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10886,27 +10886,27 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>8/25/2026 05:04 MDT</t>
+          <t>8/25/2026 06:04 MDT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8/25/2026 05:04 MDT</t>
+          <t>8/25/2026 06:04 MDT</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8/25/2026 05:04 MDT</t>
+          <t>8/25/2026 06:04 MDT</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -10915,25 +10915,25 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O113" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="S113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T113" t="n">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10979,27 +10979,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>8/25/2026 05:04 MDT</t>
+          <t>8/25/2026 06:04 MDT</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8/25/2026 05:04 MDT</t>
+          <t>8/25/2026 06:04 MDT</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>8/25/2026 05:04 MDT</t>
+          <t>8/25/2026 06:04 MDT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11008,25 +11008,25 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O114" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T114" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11072,27 +11072,27 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11104,22 +11104,22 @@
         <v>63</v>
       </c>
       <c r="O115" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>346</v>
+        <v>4</v>
       </c>
       <c r="S115" t="n">
+        <v>8</v>
+      </c>
+      <c r="T115" t="n">
         <v>6</v>
-      </c>
-      <c r="T115" t="n">
-        <v>67</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11165,27 +11165,27 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O116" t="n">
         <v>27</v>
@@ -11203,16 +11203,16 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R116" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
       </c>
       <c r="T116" t="n">
-        <v>56</v>
+        <v>353</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11258,27 +11258,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11287,10 +11287,10 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O117" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -11299,13 +11299,13 @@
         <v>19</v>
       </c>
       <c r="R117" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S117" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T117" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11380,25 +11380,25 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O118" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>322</v>
+        <v>172</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T118" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11473,25 +11473,25 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O119" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="S119" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T119" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11537,27 +11537,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O120" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11578,13 +11578,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>288</v>
+        <v>167</v>
       </c>
       <c r="S120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11630,27 +11630,27 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>8/25/2026 05:03 MDT</t>
+          <t>8/25/2026 06:03 MDT</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O121" t="n">
         <v>47</v>
@@ -11668,16 +11668,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S121" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T121" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -11723,27 +11723,27 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11752,10 +11752,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O122" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -11764,13 +11764,13 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T122" t="n">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11816,27 +11816,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11848,7 +11848,7 @@
         <v>52</v>
       </c>
       <c r="O123" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P123" t="n">
         <v>0</v>
@@ -11860,10 +11860,10 @@
         <v>58</v>
       </c>
       <c r="S123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11909,27 +11909,27 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>8/25/2026 05:02 MDT</t>
+          <t>8/25/2026 06:02 MDT</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11950,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="S124" t="n">
         <v>2</v>
       </c>
       <c r="T124" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -12002,27 +12002,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12031,10 +12031,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O125" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -12043,13 +12043,13 @@
         <v>6</v>
       </c>
       <c r="R125" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
       </c>
       <c r="T125" t="n">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12095,27 +12095,27 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O126" t="n">
         <v>24</v>
@@ -12133,16 +12133,16 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R126" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S126" t="n">
         <v>6</v>
       </c>
       <c r="T126" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12188,27 +12188,27 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12217,25 +12217,25 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O127" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R127" t="n">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T127" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12281,27 +12281,27 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>8/25/2026 05:01 MDT</t>
+          <t>8/25/2026 06:01 MDT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -12313,22 +12313,22 @@
         <v>84</v>
       </c>
       <c r="O128" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S128" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T128" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12374,27 +12374,27 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12406,22 +12406,22 @@
         <v>61</v>
       </c>
       <c r="O129" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R129" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="S129" t="n">
         <v>4</v>
       </c>
       <c r="T129" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12467,27 +12467,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12496,25 +12496,25 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O130" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R130" t="n">
-        <v>199</v>
+        <v>285</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
       </c>
       <c r="T130" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -12560,27 +12560,27 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O131" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -12601,13 +12601,13 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="S131" t="n">
         <v>2</v>
       </c>
       <c r="T131" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12682,25 +12682,25 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="O132" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>237</v>
+        <v>48</v>
       </c>
       <c r="S132" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T132" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -12746,27 +12746,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12784,13 +12784,13 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R133" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="S133" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T133" t="n">
         <v>11</v>
@@ -12839,27 +12839,27 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O134" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -12886,7 +12886,7 @@
         <v>7</v>
       </c>
       <c r="T134" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -12932,27 +12932,27 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -12970,16 +12970,16 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S135" t="n">
         <v>6</v>
       </c>
       <c r="T135" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -13025,27 +13025,27 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O136" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -13072,7 +13072,7 @@
         <v>9</v>
       </c>
       <c r="T136" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -13118,27 +13118,27 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>8/25/2026 05:49 MDT</t>
+          <t>8/25/2026 06:49 MDT</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>8/25/2026 05:49 MDT</t>
+          <t>8/25/2026 06:49 MDT</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13211,27 +13211,27 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>8/25/2026 05:59 MDT</t>
+          <t>8/25/2026 06:59 MDT</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>8/25/2026 05:59 MDT</t>
+          <t>8/25/2026 06:59 MDT</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13240,25 +13240,25 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O138" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P138" t="n">
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R138" t="n">
         <v>70</v>
       </c>
       <c r="S138" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T138" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -13304,27 +13304,27 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>8/25/2026 05:48 MDT</t>
+          <t>8/25/2026 06:48 MDT</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>8/25/2026 05:48 MDT</t>
+          <t>8/25/2026 06:48 MDT</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O139" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -13345,13 +13345,13 @@
         <v>2</v>
       </c>
       <c r="R139" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13397,27 +13397,27 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>8/25/2026 05:59 MDT</t>
+          <t>8/25/2026 06:59 MDT</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>8/25/2026 05:59 MDT</t>
+          <t>8/25/2026 06:59 MDT</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13444,7 +13444,7 @@
         <v>3</v>
       </c>
       <c r="T140" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13490,27 +13490,27 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>8/25/2026 05:48 MDT</t>
+          <t>8/25/2026 06:48 MDT</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>8/25/2026 05:48 MDT</t>
+          <t>8/25/2026 06:48 MDT</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13519,25 +13519,25 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O141" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R141" t="n">
         <v>230</v>
       </c>
       <c r="S141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T141" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13612,10 +13612,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O142" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -13624,13 +13624,13 @@
         <v>3</v>
       </c>
       <c r="R142" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="S142" t="n">
         <v>7</v>
       </c>
       <c r="T142" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13676,27 +13676,27 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13717,13 +13717,13 @@
         <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
       </c>
       <c r="T143" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13769,27 +13769,27 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>8/25/2026 05:48 MDT</t>
+          <t>8/25/2026 06:48 MDT</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>8/25/2026 05:48 MDT</t>
+          <t>8/25/2026 06:48 MDT</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13801,7 +13801,7 @@
         <v>75</v>
       </c>
       <c r="O144" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -13813,10 +13813,10 @@
         <v>20</v>
       </c>
       <c r="S144" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T144" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13862,27 +13862,27 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O145" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -13903,13 +13903,13 @@
         <v>3</v>
       </c>
       <c r="R145" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="S145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T145" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13955,27 +13955,27 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13984,10 +13984,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O146" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -13996,13 +13996,13 @@
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="S146" t="n">
         <v>2</v>
       </c>
       <c r="T146" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -14048,27 +14048,27 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -14095,7 +14095,7 @@
         <v>5</v>
       </c>
       <c r="T147" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14141,27 +14141,27 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>8/25/2026 05:49 MDT</t>
+          <t>8/25/2026 06:49 MDT</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>8/25/2026 05:49 MDT</t>
+          <t>8/25/2026 06:49 MDT</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -14182,13 +14182,13 @@
         <v>3</v>
       </c>
       <c r="R148" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S148" t="n">
         <v>9</v>
       </c>
       <c r="T148" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14234,27 +14234,27 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>8/25/2026 05:59 MDT</t>
+          <t>8/25/2026 06:59 MDT</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>8/25/2026 05:59 MDT</t>
+          <t>8/25/2026 06:59 MDT</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -14281,7 +14281,7 @@
         <v>11</v>
       </c>
       <c r="T149" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14327,27 +14327,27 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>8/25/2026 05:57 MDT</t>
+          <t>8/25/2026 06:57 MDT</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>8/25/2026 05:57 MDT</t>
+          <t>8/25/2026 06:57 MDT</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -14359,7 +14359,7 @@
         <v>67</v>
       </c>
       <c r="O150" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -14371,10 +14371,10 @@
         <v>30</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T150" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14420,27 +14420,27 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -14449,10 +14449,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O151" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -14461,13 +14461,13 @@
         <v>6</v>
       </c>
       <c r="R151" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="S151" t="n">
         <v>8</v>
       </c>
       <c r="T151" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -14513,27 +14513,27 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -14542,10 +14542,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O152" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
@@ -14560,7 +14560,7 @@
         <v>7</v>
       </c>
       <c r="T152" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14635,7 +14635,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O153" t="n">
         <v>37</v>
@@ -14647,13 +14647,13 @@
         <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="S153" t="n">
         <v>7</v>
       </c>
       <c r="T153" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14699,27 +14699,27 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>8/25/2026 05:53 MDT</t>
+          <t>8/25/2026 06:53 MDT</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14731,7 +14731,7 @@
         <v>78</v>
       </c>
       <c r="O154" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -14743,10 +14743,10 @@
         <v>20</v>
       </c>
       <c r="S154" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T154" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14792,27 +14792,27 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>8/25/2026 05:52 MDT</t>
+          <t>8/25/2026 06:52 MDT</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O155" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P155" t="n">
         <v>0</v>
@@ -14839,7 +14839,7 @@
         <v>5</v>
       </c>
       <c r="T155" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -14885,27 +14885,27 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>8/25/2026 05:47 MDT</t>
+          <t>8/25/2026 06:47 MDT</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>8/25/2026 05:47 MDT</t>
+          <t>8/25/2026 06:47 MDT</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14926,13 +14926,13 @@
         <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
       </c>
       <c r="T156" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14978,27 +14978,27 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>8/25/2026 05:49 MDT</t>
+          <t>8/25/2026 06:49 MDT</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>8/25/2026 05:49 MDT</t>
+          <t>8/25/2026 06:49 MDT</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15007,10 +15007,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O157" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -15025,7 +15025,7 @@
         <v>7</v>
       </c>
       <c r="T157" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -15071,27 +15071,27 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>8/25/2026 05:00 MDT</t>
+          <t>8/25/2026 06:00 MDT</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>8/25/2026 06:00 MDT</t>
+          <t>8/25/2026 07:00 MDT</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>8/25/2026 05:50 MDT</t>
+          <t>8/25/2026 06:50 MDT</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -15112,13 +15112,13 @@
         <v>1</v>
       </c>
       <c r="R158" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
       </c>
       <c r="T158" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>

--- a/data/fems_latest_weatherObs.xlsx
+++ b/data/fems_latest_weatherObs.xlsx
@@ -563,27 +563,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8/25/2026 22:42 MDT</t>
+          <t>8/25/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8/25/2026 22:42 MDT</t>
+          <t>8/25/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8/25/2026 22:42 MDT</t>
+          <t>8/25/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -656,27 +656,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8/25/2026 22:42 MDT</t>
+          <t>8/25/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8/25/2026 22:42 MDT</t>
+          <t>8/25/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8/25/2026 22:42 MDT</t>
+          <t>8/25/2026 23:42 MDT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="O3" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>37</v>
+        <v>359</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -749,27 +749,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -842,27 +842,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -883,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -935,27 +935,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -967,7 +967,7 @@
         <v>64</v>
       </c>
       <c r="O6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8/25/2026 22:41 MDT</t>
+          <t>8/25/2026 23:41 MDT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1069,13 +1069,13 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8/25/2026 22:40 MDT</t>
+          <t>8/25/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8/25/2026 22:40 MDT</t>
+          <t>8/25/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8/25/2026 22:40 MDT</t>
+          <t>8/25/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1150,25 +1150,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>85</v>
+        <v>319</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1214,27 +1214,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8/25/2026 22:40 MDT</t>
+          <t>8/25/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8/25/2026 22:40 MDT</t>
+          <t>8/25/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8/25/2026 22:40 MDT</t>
+          <t>8/25/2026 23:40 MDT</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1243,25 +1243,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1336,25 +1336,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1522,25 +1522,25 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O12" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="T12" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1586,27 +1586,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8/25/2026 22:39 MDT</t>
+          <t>8/25/2026 23:39 MDT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1615,25 +1615,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
+        <v>66</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
         <v>69</v>
-      </c>
-      <c r="S13" t="n">
-        <v>8</v>
-      </c>
-      <c r="T13" t="n">
-        <v>64</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>54</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1772,27 +1772,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O15" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>307</v>
+        <v>163</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1865,27 +1865,27 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1894,25 +1894,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O17" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>299</v>
+        <v>163</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2051,27 +2051,27 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>69</v>
       </c>
       <c r="O18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2144,27 +2144,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2185,13 +2185,13 @@
         <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O20" t="n">
         <v>55</v>
@@ -2278,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2330,27 +2330,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8/25/2026 22:38 MDT</t>
+          <t>8/25/2026 23:38 MDT</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2359,25 +2359,25 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O21" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>208</v>
+        <v>281</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2423,27 +2423,27 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2464,13 +2464,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>326</v>
+        <v>203</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O23" t="n">
         <v>18</v>
@@ -2554,16 +2554,16 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2609,27 +2609,27 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2641,22 +2641,22 @@
         <v>71</v>
       </c>
       <c r="O24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2731,25 +2731,25 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2795,27 +2795,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2833,16 +2833,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="S26" t="n">
         <v>12</v>
       </c>
       <c r="T26" t="n">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T27" t="n">
-        <v>342</v>
+        <v>24</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3010,25 +3010,25 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3074,27 +3074,27 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8/25/2026 22:37 MDT</t>
+          <t>8/25/2026 23:37 MDT</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3115,13 +3115,13 @@
         <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T29" t="n">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8/25/2026 22:36 MDT</t>
+          <t>8/25/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8/25/2026 22:36 MDT</t>
+          <t>8/25/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/25/2026 22:36 MDT</t>
+          <t>8/25/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3196,25 +3196,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O30" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8/25/2026 22:36 MDT</t>
+          <t>8/25/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8/25/2026 22:36 MDT</t>
+          <t>8/25/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8/25/2026 22:36 MDT</t>
+          <t>8/25/2026 23:36 MDT</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3289,25 +3289,25 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3353,27 +3353,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8/25/2026 22:35 MDT</t>
+          <t>8/25/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8/25/2026 22:35 MDT</t>
+          <t>8/25/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/25/2026 22:35 MDT</t>
+          <t>8/25/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3382,25 +3382,25 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O32" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="n">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3446,27 +3446,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8/25/2026 22:35 MDT</t>
+          <t>8/25/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8/25/2026 22:35 MDT</t>
+          <t>8/25/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8/25/2026 22:35 MDT</t>
+          <t>8/25/2026 23:35 MDT</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="O33" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3487,13 +3487,13 @@
         <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3539,27 +3539,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3571,22 +3571,22 @@
         <v>74</v>
       </c>
       <c r="O34" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="S34" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T34" t="n">
-        <v>231</v>
+        <v>129</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3661,25 +3661,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T35" t="n">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3725,27 +3725,27 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3754,25 +3754,25 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O36" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8/25/2026 22:34 MDT</t>
+          <t>8/25/2026 23:34 MDT</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3847,25 +3847,25 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O37" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3911,27 +3911,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3943,22 +3943,22 @@
         <v>83</v>
       </c>
       <c r="O38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4033,25 +4033,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O39" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4126,25 +4126,25 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O40" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R40" t="n">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="S40" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="T40" t="n">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4219,25 +4219,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R41" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T41" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4283,27 +4283,27 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8/25/2026 23:00 MDT</t>
+          <t>8/26/2026 00:00 MDT</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>8/25/2026 22:33 MDT</t>
+          <t>8/25/2026 23:33 MDT</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>68</v>
+  